--- a/restos.xlsx
+++ b/restos.xlsx
@@ -60326,13 +60326,13 @@
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{23EA01ED-053D-4A51-93E4-68E532926117}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{EADAF7AD-82E8-4364-B519-FEEA3E22D1E6}"/>
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{3AC91BDD-72DE-47AE-9584-6C048D3119FE}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{C990C6D6-9D56-47CA-B805-F4D359F8C9EE}"/>
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{E733CADE-6373-4FB5-B0F7-9779E5321D27}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{2A7AAAED-DD66-489A-B89C-29F89232DB84}"/>
 </file>
--- a/restos.xlsx
+++ b/restos.xlsx
@@ -60683,13 +60683,13 @@
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{A698672E-1CB2-4356-9B67-13E7DF78E028}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{E748F3B5-3087-4978-8AE1-9776FB7B9F66}"/>
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{641FF255-129A-44D7-BFE6-C24AA0CB1497}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{AC99A43A-A5AA-46BC-9ED7-5DE2BB25D1FC}"/>
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{F13CD093-32AB-4769-9172-DCDB99602E1B}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{C5DC1E0C-A011-4808-AF8C-96D75C943508}"/>
 </file>
--- a/restos.xlsx
+++ b/restos.xlsx
@@ -60683,13 +60683,13 @@
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{E748F3B5-3087-4978-8AE1-9776FB7B9F66}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{C4ADCE4B-0DC9-4D46-8A22-45ADAA194FDA}"/>
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{AC99A43A-A5AA-46BC-9ED7-5DE2BB25D1FC}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{1E15E26E-D1A0-4B25-B4DC-B7CFC71348FD}"/>
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{C5DC1E0C-A011-4808-AF8C-96D75C943508}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{A196DEBF-008E-4258-A13F-0F6EE9609A88}"/>
 </file>
--- a/restos.xlsx
+++ b/restos.xlsx
@@ -60683,13 +60683,13 @@
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{C4ADCE4B-0DC9-4D46-8A22-45ADAA194FDA}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{8C0F3F13-E496-475D-AC73-C928DD2FDC37}"/>
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{1E15E26E-D1A0-4B25-B4DC-B7CFC71348FD}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{DF3EE39D-D1BA-47E2-8AD2-1DE61C79228C}"/>
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{A196DEBF-008E-4258-A13F-0F6EE9609A88}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{77FF291D-97FC-44FE-846E-E1775F14024D}"/>
 </file>
--- a/restos.xlsx
+++ b/restos.xlsx
@@ -60683,13 +60683,13 @@
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{8C0F3F13-E496-475D-AC73-C928DD2FDC37}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{B6D48770-06EC-4F51-AE4D-0D55B5707C19}"/>
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{DF3EE39D-D1BA-47E2-8AD2-1DE61C79228C}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{81E30BF2-94C3-4C94-8D4E-4AF9A72BC734}"/>
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{77FF291D-97FC-44FE-846E-E1775F14024D}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{FAAAEDB3-3EA1-4571-BBEB-A3A43A5B6162}"/>
 </file>
--- a/restos.xlsx
+++ b/restos.xlsx
@@ -61505,13 +61505,13 @@
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{7A86DF94-1E9D-4DC9-BFD3-0F92A7901C0A}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{FA80FD38-B84B-49F0-86DA-0CDE72C392D9}"/>
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{8A26A449-EEF4-49BF-9F4D-B481C72727E9}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{98B119D4-7557-4F68-9DEC-E316D65F418E}"/>
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{EA82EEC2-642F-4FE8-A2D5-4B681A9065D5}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{145E4A7E-DD6D-49F3-BE61-737459A85A9A}"/>
 </file>
--- a/restos.xlsx
+++ b/restos.xlsx
@@ -61505,13 +61505,13 @@
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{FA80FD38-B84B-49F0-86DA-0CDE72C392D9}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{75442760-8117-495E-804B-303B44F8623A}"/>
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{98B119D4-7557-4F68-9DEC-E316D65F418E}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{832A9333-2932-4559-B76F-0528314DC7E4}"/>
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{145E4A7E-DD6D-49F3-BE61-737459A85A9A}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{458E8170-36D8-4FCE-8677-8753188A5786}"/>
 </file>
--- a/restos.xlsx
+++ b/restos.xlsx
@@ -61505,13 +61505,13 @@
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{75442760-8117-495E-804B-303B44F8623A}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{F09DBD24-4E3F-4BAC-9533-BC6CBF49BC45}"/>
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{832A9333-2932-4559-B76F-0528314DC7E4}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{37969524-FACC-4388-8083-0D04C67BE82A}"/>
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{458E8170-36D8-4FCE-8677-8753188A5786}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{52D3F2FC-E237-4B70-843B-B6900CD12BCE}"/>
 </file>
--- a/restos.xlsx
+++ b/restos.xlsx
@@ -61505,13 +61505,13 @@
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{F09DBD24-4E3F-4BAC-9533-BC6CBF49BC45}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{527FA720-A938-4D16-83B1-40636B202FCE}"/>
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{37969524-FACC-4388-8083-0D04C67BE82A}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{8450B8DB-13E1-415F-ADA3-85A0F5094761}"/>
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{52D3F2FC-E237-4B70-843B-B6900CD12BCE}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{A5609E2A-0A58-44CE-8D1D-31A6CE8AA2BF}"/>
 </file>
--- a/restos.xlsx
+++ b/restos.xlsx
@@ -61505,13 +61505,13 @@
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{527FA720-A938-4D16-83B1-40636B202FCE}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{AD641857-6550-423D-B06B-549BCAB19E75}"/>
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{8450B8DB-13E1-415F-ADA3-85A0F5094761}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{316A4DDC-DA4B-45AD-8A2F-5F7E162B8DAB}"/>
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{A5609E2A-0A58-44CE-8D1D-31A6CE8AA2BF}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{91889D9A-4114-46E8-8F1C-5774C12760D2}"/>
 </file>
--- a/restos.xlsx
+++ b/restos.xlsx
@@ -541,7 +541,7 @@
     <t>LOCACAO DE SERVICOS DE CONSERVACAO E LIMPEZA REALIZADOS PELA MGS</t>
   </si>
   <si>
-    <t>Pendente de transmissão aos bancos</t>
+    <t>Transmitida ao banco - Pendente de Confirmação</t>
   </si>
   <si>
     <t>LOCACAO DE SERVICOS DE APOIO ADMINISTRATIVO REALIZADOS PELA MGS</t>
@@ -1454,7 +1454,7 @@
     <col min="2" max="19" width="10.7163133333333" customWidth="1"/>
     <col min="20" max="20" width="20.9645" customWidth="1"/>
     <col min="21" max="22" width="10.7163133333333" customWidth="1"/>
-    <col min="23" max="23" width="34.2738333333333" customWidth="1"/>
+    <col min="23" max="23" width="42.2594333333333" customWidth="1"/>
     <col min="24" max="32" width="10.7163133333333" customWidth="1"/>
     <col min="33" max="33" width="22.4855666666667" customWidth="1"/>
     <col min="34" max="34" width="18.4927666666667" customWidth="1"/>
@@ -17914,7 +17914,7 @@
         <v>47</v>
       </c>
       <c r="AC146" s="4" t="s">
-        <v>47</v>
+        <v>153</v>
       </c>
       <c r="AD146" s="3">
         <v>10</v>
@@ -18033,7 +18033,7 @@
         <v>47</v>
       </c>
       <c r="AC147" s="4" t="s">
-        <v>47</v>
+        <v>153</v>
       </c>
       <c r="AD147" s="3">
         <v>10</v>
@@ -45504,7 +45504,7 @@
         <v>47</v>
       </c>
       <c r="AC384" s="4" t="s">
-        <v>47</v>
+        <v>153</v>
       </c>
       <c r="AD384" s="3">
         <v>10</v>
@@ -57183,7 +57183,7 @@
         <v>47</v>
       </c>
       <c r="AC485" s="4" t="s">
-        <v>47</v>
+        <v>153</v>
       </c>
       <c r="AD485" s="3">
         <v>10</v>
@@ -57536,7 +57536,7 @@
         <v>47</v>
       </c>
       <c r="AC488" s="4" t="s">
-        <v>47</v>
+        <v>153</v>
       </c>
       <c r="AD488" s="3">
         <v>10</v>
@@ -62450,13 +62450,13 @@
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{2E9B660B-D1C3-48FB-ABB7-1A345DF9A033}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{B7D980F0-49E0-484D-BC39-FEED4E302613}"/>
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{613CDDF1-417D-4870-8D2A-CD11B329E987}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{E5115218-B91C-40C4-ADB0-932021E03605}"/>
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{25A07257-D7A6-4180-957A-6C8D6A1A2425}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{B4D43860-CBC4-42A4-9D22-EF79DAB11C93}"/>
 </file>
--- a/restos.xlsx
+++ b/restos.xlsx
@@ -8,7 +8,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4761" uniqueCount="444">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4761" uniqueCount="443">
   <si>
     <t>Ano de Exercício</t>
   </si>
@@ -539,9 +539,6 @@
   </si>
   <si>
     <t>LOCACAO DE SERVICOS DE CONSERVACAO E LIMPEZA REALIZADOS PELA MGS</t>
-  </si>
-  <si>
-    <t>Transmitida ao banco - Pendente de Confirmação</t>
   </si>
   <si>
     <t>LOCACAO DE SERVICOS DE APOIO ADMINISTRATIVO REALIZADOS PELA MGS</t>
@@ -1454,7 +1451,7 @@
     <col min="2" max="19" width="10.7163133333333" customWidth="1"/>
     <col min="20" max="20" width="20.9645" customWidth="1"/>
     <col min="21" max="22" width="10.7163133333333" customWidth="1"/>
-    <col min="23" max="23" width="42.2594333333333" customWidth="1"/>
+    <col min="23" max="23" width="34.2738333333333" customWidth="1"/>
     <col min="24" max="32" width="10.7163133333333" customWidth="1"/>
     <col min="33" max="33" width="22.4855666666667" customWidth="1"/>
     <col min="34" max="34" width="18.4927666666667" customWidth="1"/>
@@ -1470,7 +1467,7 @@
     <row r="1" s="1" customFormat="1" ht="8.5328" customHeight="1"/>
     <row r="2" s="1" customFormat="1" ht="31.4647" customHeight="1">
       <c r="D2" s="7" t="s">
-        <v>443</v>
+        <v>442</v>
       </c>
       <c r="E2" s="7"/>
       <c r="F2" s="7"/>
@@ -17896,7 +17893,7 @@
         <v>46311</v>
       </c>
       <c r="W146" s="4" t="s">
-        <v>177</v>
+        <v>135</v>
       </c>
       <c r="X146" s="5">
         <v>238.82</v>
@@ -18015,7 +18012,7 @@
         <v>46311</v>
       </c>
       <c r="W147" s="4" t="s">
-        <v>177</v>
+        <v>135</v>
       </c>
       <c r="X147" s="5">
         <v>2277.49</v>
@@ -19487,7 +19484,7 @@
         <v>2025</v>
       </c>
       <c r="J160" s="4" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="K160" s="3">
         <v>9.287509e6</v>
@@ -19602,7 +19599,7 @@
         <v>2025</v>
       </c>
       <c r="J161" s="4" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="K161" s="3">
         <v>9.287509e6</v>
@@ -19955,7 +19952,7 @@
         <v>2024</v>
       </c>
       <c r="J164" s="4" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="K164" s="3">
         <v>9.287509e6</v>
@@ -20070,7 +20067,7 @@
         <v>2024</v>
       </c>
       <c r="J165" s="4" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="K165" s="3">
         <v>9.287509e6</v>
@@ -21004,7 +21001,7 @@
         <v>2025</v>
       </c>
       <c r="J173" s="4" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="K173" s="3">
         <v>9.287509e6</v>
@@ -21119,7 +21116,7 @@
         <v>2025</v>
       </c>
       <c r="J174" s="4" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="K174" s="3">
         <v>9.287509e6</v>
@@ -21238,7 +21235,7 @@
         <v>2025</v>
       </c>
       <c r="J175" s="4" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="K175" s="3">
         <v>9.287509e6</v>
@@ -21357,7 +21354,7 @@
         <v>2025</v>
       </c>
       <c r="J176" s="4" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="K176" s="3">
         <v>9.287509e6</v>
@@ -21476,7 +21473,7 @@
         <v>2025</v>
       </c>
       <c r="J177" s="4" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="K177" s="3">
         <v>9.287509e6</v>
@@ -22176,7 +22173,7 @@
         <v>2025</v>
       </c>
       <c r="J183" s="4" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="K183" s="3">
         <v>9.287509e6</v>
@@ -22289,7 +22286,7 @@
         <v>2025</v>
       </c>
       <c r="J184" s="4" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="K184" s="3">
         <v>9.287509e6</v>
@@ -22406,7 +22403,7 @@
         <v>2025</v>
       </c>
       <c r="J185" s="4" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="K185" s="3">
         <v>9.287509e6</v>
@@ -22523,7 +22520,7 @@
         <v>2025</v>
       </c>
       <c r="J186" s="4" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="K186" s="3">
         <v>9.287509e6</v>
@@ -22640,7 +22637,7 @@
         <v>2025</v>
       </c>
       <c r="J187" s="4" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="K187" s="3">
         <v>9.287509e6</v>
@@ -22757,7 +22754,7 @@
         <v>2024</v>
       </c>
       <c r="J188" s="4" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="K188" s="3">
         <v>9.287509e6</v>
@@ -22855,13 +22852,13 @@
         <v>99</v>
       </c>
       <c r="E189" s="4" t="s">
+        <v>178</v>
+      </c>
+      <c r="F189" s="4" t="s">
         <v>179</v>
       </c>
-      <c r="F189" s="4" t="s">
+      <c r="G189" s="4" t="s">
         <v>180</v>
-      </c>
-      <c r="G189" s="4" t="s">
-        <v>181</v>
       </c>
       <c r="H189" s="3">
         <v>1613</v>
@@ -22970,13 +22967,13 @@
         <v>99</v>
       </c>
       <c r="E190" s="4" t="s">
+        <v>178</v>
+      </c>
+      <c r="F190" s="4" t="s">
         <v>179</v>
       </c>
-      <c r="F190" s="4" t="s">
+      <c r="G190" s="4" t="s">
         <v>180</v>
-      </c>
-      <c r="G190" s="4" t="s">
-        <v>181</v>
       </c>
       <c r="H190" s="3">
         <v>1626</v>
@@ -23085,13 +23082,13 @@
         <v>99</v>
       </c>
       <c r="E191" s="4" t="s">
+        <v>178</v>
+      </c>
+      <c r="F191" s="4" t="s">
         <v>179</v>
       </c>
-      <c r="F191" s="4" t="s">
+      <c r="G191" s="4" t="s">
         <v>180</v>
-      </c>
-      <c r="G191" s="4" t="s">
-        <v>181</v>
       </c>
       <c r="H191" s="3">
         <v>1641</v>
@@ -23200,13 +23197,13 @@
         <v>99</v>
       </c>
       <c r="E192" s="4" t="s">
+        <v>178</v>
+      </c>
+      <c r="F192" s="4" t="s">
         <v>179</v>
       </c>
-      <c r="F192" s="4" t="s">
+      <c r="G192" s="4" t="s">
         <v>180</v>
-      </c>
-      <c r="G192" s="4" t="s">
-        <v>181</v>
       </c>
       <c r="H192" s="3">
         <v>1656</v>
@@ -24340,13 +24337,13 @@
         <v>99</v>
       </c>
       <c r="E202" s="4" t="s">
+        <v>181</v>
+      </c>
+      <c r="F202" s="4" t="s">
         <v>182</v>
       </c>
-      <c r="F202" s="4" t="s">
+      <c r="G202" s="4" t="s">
         <v>183</v>
-      </c>
-      <c r="G202" s="4" t="s">
-        <v>184</v>
       </c>
       <c r="H202" s="3">
         <v>64</v>
@@ -24355,7 +24352,7 @@
         <v>2025</v>
       </c>
       <c r="J202" s="4" t="s">
-        <v>185</v>
+        <v>184</v>
       </c>
       <c r="K202" s="3">
         <v>9.379456e6</v>
@@ -24453,13 +24450,13 @@
         <v>99</v>
       </c>
       <c r="E203" s="4" t="s">
+        <v>181</v>
+      </c>
+      <c r="F203" s="4" t="s">
         <v>182</v>
       </c>
-      <c r="F203" s="4" t="s">
+      <c r="G203" s="4" t="s">
         <v>183</v>
-      </c>
-      <c r="G203" s="4" t="s">
-        <v>184</v>
       </c>
       <c r="H203" s="3">
         <v>64</v>
@@ -24468,7 +24465,7 @@
         <v>2025</v>
       </c>
       <c r="J203" s="4" t="s">
-        <v>185</v>
+        <v>184</v>
       </c>
       <c r="K203" s="3">
         <v>9.379456e6</v>
@@ -24520,7 +24517,7 @@
         <v>0</v>
       </c>
       <c r="AB203" s="4" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
       <c r="AC203" s="4" t="s">
         <v>136</v>
@@ -24570,10 +24567,10 @@
         <v>99</v>
       </c>
       <c r="E204" s="4" t="s">
+        <v>186</v>
+      </c>
+      <c r="F204" s="4" t="s">
         <v>187</v>
-      </c>
-      <c r="F204" s="4" t="s">
-        <v>188</v>
       </c>
       <c r="G204" s="4" t="s">
         <v>96</v>
@@ -24585,7 +24582,7 @@
         <v>2024</v>
       </c>
       <c r="J204" s="4" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
       <c r="K204" s="3">
         <v>0</v>
@@ -24685,10 +24682,10 @@
         <v>99</v>
       </c>
       <c r="E205" s="4" t="s">
+        <v>186</v>
+      </c>
+      <c r="F205" s="4" t="s">
         <v>187</v>
-      </c>
-      <c r="F205" s="4" t="s">
-        <v>188</v>
       </c>
       <c r="G205" s="4" t="s">
         <v>96</v>
@@ -24700,7 +24697,7 @@
         <v>2024</v>
       </c>
       <c r="J205" s="4" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
       <c r="K205" s="3">
         <v>0</v>
@@ -24800,10 +24797,10 @@
         <v>99</v>
       </c>
       <c r="E206" s="4" t="s">
+        <v>186</v>
+      </c>
+      <c r="F206" s="4" t="s">
         <v>187</v>
-      </c>
-      <c r="F206" s="4" t="s">
-        <v>188</v>
       </c>
       <c r="G206" s="4" t="s">
         <v>96</v>
@@ -24815,7 +24812,7 @@
         <v>2024</v>
       </c>
       <c r="J206" s="4" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
       <c r="K206" s="3">
         <v>0</v>
@@ -24915,10 +24912,10 @@
         <v>99</v>
       </c>
       <c r="E207" s="4" t="s">
+        <v>186</v>
+      </c>
+      <c r="F207" s="4" t="s">
         <v>187</v>
-      </c>
-      <c r="F207" s="4" t="s">
-        <v>188</v>
       </c>
       <c r="G207" s="4" t="s">
         <v>96</v>
@@ -24930,7 +24927,7 @@
         <v>2024</v>
       </c>
       <c r="J207" s="4" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
       <c r="K207" s="3">
         <v>0</v>
@@ -25329,7 +25326,7 @@
         <v>0</v>
       </c>
       <c r="AB210" s="4" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
       <c r="AC210" s="4" t="s">
         <v>153</v>
@@ -25379,13 +25376,13 @@
         <v>99</v>
       </c>
       <c r="E211" s="4" t="s">
+        <v>190</v>
+      </c>
+      <c r="F211" s="4" t="s">
         <v>191</v>
       </c>
-      <c r="F211" s="4" t="s">
+      <c r="G211" s="4" t="s">
         <v>192</v>
-      </c>
-      <c r="G211" s="4" t="s">
-        <v>193</v>
       </c>
       <c r="H211" s="3">
         <v>44</v>
@@ -25494,13 +25491,13 @@
         <v>99</v>
       </c>
       <c r="E212" s="4" t="s">
+        <v>190</v>
+      </c>
+      <c r="F212" s="4" t="s">
         <v>191</v>
       </c>
-      <c r="F212" s="4" t="s">
+      <c r="G212" s="4" t="s">
         <v>192</v>
-      </c>
-      <c r="G212" s="4" t="s">
-        <v>193</v>
       </c>
       <c r="H212" s="3">
         <v>44</v>
@@ -25563,7 +25560,7 @@
         <v>0</v>
       </c>
       <c r="AB212" s="4" t="s">
-        <v>194</v>
+        <v>193</v>
       </c>
       <c r="AC212" s="4" t="s">
         <v>153</v>
@@ -25613,13 +25610,13 @@
         <v>99</v>
       </c>
       <c r="E213" s="4" t="s">
+        <v>194</v>
+      </c>
+      <c r="F213" s="4" t="s">
         <v>195</v>
       </c>
-      <c r="F213" s="4" t="s">
+      <c r="G213" s="4" t="s">
         <v>196</v>
-      </c>
-      <c r="G213" s="4" t="s">
-        <v>197</v>
       </c>
       <c r="H213" s="3">
         <v>41</v>
@@ -25726,13 +25723,13 @@
         <v>99</v>
       </c>
       <c r="E214" s="4" t="s">
+        <v>194</v>
+      </c>
+      <c r="F214" s="4" t="s">
         <v>195</v>
       </c>
-      <c r="F214" s="4" t="s">
+      <c r="G214" s="4" t="s">
         <v>196</v>
-      </c>
-      <c r="G214" s="4" t="s">
-        <v>197</v>
       </c>
       <c r="H214" s="3">
         <v>41</v>
@@ -25839,13 +25836,13 @@
         <v>99</v>
       </c>
       <c r="E215" s="4" t="s">
+        <v>194</v>
+      </c>
+      <c r="F215" s="4" t="s">
         <v>195</v>
       </c>
-      <c r="F215" s="4" t="s">
+      <c r="G215" s="4" t="s">
         <v>196</v>
-      </c>
-      <c r="G215" s="4" t="s">
-        <v>197</v>
       </c>
       <c r="H215" s="3">
         <v>41</v>
@@ -25906,7 +25903,7 @@
         <v>0</v>
       </c>
       <c r="AB215" s="4" t="s">
-        <v>198</v>
+        <v>197</v>
       </c>
       <c r="AC215" s="4" t="s">
         <v>136</v>
@@ -25956,10 +25953,10 @@
         <v>99</v>
       </c>
       <c r="E216" s="4" t="s">
+        <v>198</v>
+      </c>
+      <c r="F216" s="4" t="s">
         <v>199</v>
-      </c>
-      <c r="F216" s="4" t="s">
-        <v>200</v>
       </c>
       <c r="G216" s="4" t="s">
         <v>115</v>
@@ -26069,10 +26066,10 @@
         <v>99</v>
       </c>
       <c r="E217" s="4" t="s">
+        <v>198</v>
+      </c>
+      <c r="F217" s="4" t="s">
         <v>199</v>
-      </c>
-      <c r="F217" s="4" t="s">
-        <v>200</v>
       </c>
       <c r="G217" s="4" t="s">
         <v>115</v>
@@ -26186,10 +26183,10 @@
         <v>99</v>
       </c>
       <c r="E218" s="4" t="s">
+        <v>198</v>
+      </c>
+      <c r="F218" s="4" t="s">
         <v>199</v>
-      </c>
-      <c r="F218" s="4" t="s">
-        <v>200</v>
       </c>
       <c r="G218" s="4" t="s">
         <v>115</v>
@@ -26303,10 +26300,10 @@
         <v>99</v>
       </c>
       <c r="E219" s="4" t="s">
+        <v>198</v>
+      </c>
+      <c r="F219" s="4" t="s">
         <v>199</v>
-      </c>
-      <c r="F219" s="4" t="s">
-        <v>200</v>
       </c>
       <c r="G219" s="4" t="s">
         <v>115</v>
@@ -26420,13 +26417,13 @@
         <v>99</v>
       </c>
       <c r="E220" s="4" t="s">
+        <v>200</v>
+      </c>
+      <c r="F220" s="4" t="s">
         <v>201</v>
       </c>
-      <c r="F220" s="4" t="s">
+      <c r="G220" s="4" t="s">
         <v>202</v>
-      </c>
-      <c r="G220" s="4" t="s">
-        <v>203</v>
       </c>
       <c r="H220" s="3">
         <v>65</v>
@@ -26435,7 +26432,7 @@
         <v>2025</v>
       </c>
       <c r="J220" s="4" t="s">
-        <v>204</v>
+        <v>203</v>
       </c>
       <c r="K220" s="3">
         <v>9.396057e6</v>
@@ -26533,13 +26530,13 @@
         <v>99</v>
       </c>
       <c r="E221" s="4" t="s">
+        <v>200</v>
+      </c>
+      <c r="F221" s="4" t="s">
         <v>201</v>
       </c>
-      <c r="F221" s="4" t="s">
+      <c r="G221" s="4" t="s">
         <v>202</v>
-      </c>
-      <c r="G221" s="4" t="s">
-        <v>203</v>
       </c>
       <c r="H221" s="3">
         <v>65</v>
@@ -26548,7 +26545,7 @@
         <v>2025</v>
       </c>
       <c r="J221" s="4" t="s">
-        <v>204</v>
+        <v>203</v>
       </c>
       <c r="K221" s="3">
         <v>9.396057e6</v>
@@ -26646,13 +26643,13 @@
         <v>99</v>
       </c>
       <c r="E222" s="4" t="s">
+        <v>200</v>
+      </c>
+      <c r="F222" s="4" t="s">
         <v>201</v>
       </c>
-      <c r="F222" s="4" t="s">
+      <c r="G222" s="4" t="s">
         <v>202</v>
-      </c>
-      <c r="G222" s="4" t="s">
-        <v>203</v>
       </c>
       <c r="H222" s="3">
         <v>1126</v>
@@ -26661,7 +26658,7 @@
         <v>2025</v>
       </c>
       <c r="J222" s="4" t="s">
-        <v>204</v>
+        <v>203</v>
       </c>
       <c r="K222" s="3">
         <v>9.396057e6</v>
@@ -26761,13 +26758,13 @@
         <v>99</v>
       </c>
       <c r="E223" s="4" t="s">
+        <v>200</v>
+      </c>
+      <c r="F223" s="4" t="s">
         <v>201</v>
       </c>
-      <c r="F223" s="4" t="s">
+      <c r="G223" s="4" t="s">
         <v>202</v>
-      </c>
-      <c r="G223" s="4" t="s">
-        <v>203</v>
       </c>
       <c r="H223" s="3">
         <v>1126</v>
@@ -26776,7 +26773,7 @@
         <v>2025</v>
       </c>
       <c r="J223" s="4" t="s">
-        <v>204</v>
+        <v>203</v>
       </c>
       <c r="K223" s="3">
         <v>9.396057e6</v>
@@ -26876,13 +26873,13 @@
         <v>99</v>
       </c>
       <c r="E224" s="4" t="s">
+        <v>200</v>
+      </c>
+      <c r="F224" s="4" t="s">
         <v>201</v>
       </c>
-      <c r="F224" s="4" t="s">
+      <c r="G224" s="4" t="s">
         <v>202</v>
-      </c>
-      <c r="G224" s="4" t="s">
-        <v>203</v>
       </c>
       <c r="H224" s="3">
         <v>1654</v>
@@ -26891,7 +26888,7 @@
         <v>2025</v>
       </c>
       <c r="J224" s="4" t="s">
-        <v>204</v>
+        <v>203</v>
       </c>
       <c r="K224" s="3">
         <v>9.479122e6</v>
@@ -26991,13 +26988,13 @@
         <v>99</v>
       </c>
       <c r="E225" s="4" t="s">
+        <v>200</v>
+      </c>
+      <c r="F225" s="4" t="s">
         <v>201</v>
       </c>
-      <c r="F225" s="4" t="s">
+      <c r="G225" s="4" t="s">
         <v>202</v>
-      </c>
-      <c r="G225" s="4" t="s">
-        <v>203</v>
       </c>
       <c r="H225" s="3">
         <v>1654</v>
@@ -27006,7 +27003,7 @@
         <v>2025</v>
       </c>
       <c r="J225" s="4" t="s">
-        <v>204</v>
+        <v>203</v>
       </c>
       <c r="K225" s="3">
         <v>9.479122e6</v>
@@ -27060,7 +27057,7 @@
         <v>0</v>
       </c>
       <c r="AB225" s="4" t="s">
-        <v>205</v>
+        <v>204</v>
       </c>
       <c r="AC225" s="4" t="s">
         <v>153</v>
@@ -27110,13 +27107,13 @@
         <v>99</v>
       </c>
       <c r="E226" s="4" t="s">
+        <v>205</v>
+      </c>
+      <c r="F226" s="4" t="s">
         <v>206</v>
       </c>
-      <c r="F226" s="4" t="s">
+      <c r="G226" s="4" t="s">
         <v>207</v>
-      </c>
-      <c r="G226" s="4" t="s">
-        <v>208</v>
       </c>
       <c r="H226" s="3">
         <v>37</v>
@@ -27223,13 +27220,13 @@
         <v>99</v>
       </c>
       <c r="E227" s="4" t="s">
+        <v>205</v>
+      </c>
+      <c r="F227" s="4" t="s">
         <v>206</v>
       </c>
-      <c r="F227" s="4" t="s">
+      <c r="G227" s="4" t="s">
         <v>207</v>
-      </c>
-      <c r="G227" s="4" t="s">
-        <v>208</v>
       </c>
       <c r="H227" s="3">
         <v>37</v>
@@ -27336,13 +27333,13 @@
         <v>99</v>
       </c>
       <c r="E228" s="4" t="s">
+        <v>205</v>
+      </c>
+      <c r="F228" s="4" t="s">
         <v>206</v>
       </c>
-      <c r="F228" s="4" t="s">
+      <c r="G228" s="4" t="s">
         <v>207</v>
-      </c>
-      <c r="G228" s="4" t="s">
-        <v>208</v>
       </c>
       <c r="H228" s="3">
         <v>48</v>
@@ -27451,13 +27448,13 @@
         <v>99</v>
       </c>
       <c r="E229" s="4" t="s">
+        <v>205</v>
+      </c>
+      <c r="F229" s="4" t="s">
         <v>206</v>
       </c>
-      <c r="F229" s="4" t="s">
+      <c r="G229" s="4" t="s">
         <v>207</v>
-      </c>
-      <c r="G229" s="4" t="s">
-        <v>208</v>
       </c>
       <c r="H229" s="3">
         <v>48</v>
@@ -27520,7 +27517,7 @@
         <v>0</v>
       </c>
       <c r="AB229" s="4" t="s">
-        <v>209</v>
+        <v>208</v>
       </c>
       <c r="AC229" s="4" t="s">
         <v>153</v>
@@ -27567,13 +27564,13 @@
         <v>4430</v>
       </c>
       <c r="D230" s="4" t="s">
+        <v>209</v>
+      </c>
+      <c r="E230" s="4" t="s">
         <v>210</v>
       </c>
-      <c r="E230" s="4" t="s">
+      <c r="F230" s="4" t="s">
         <v>211</v>
-      </c>
-      <c r="F230" s="4" t="s">
-        <v>212</v>
       </c>
       <c r="G230" s="4" t="s">
         <v>96</v>
@@ -27682,13 +27679,13 @@
         <v>4430</v>
       </c>
       <c r="D231" s="4" t="s">
+        <v>209</v>
+      </c>
+      <c r="E231" s="4" t="s">
         <v>210</v>
       </c>
-      <c r="E231" s="4" t="s">
+      <c r="F231" s="4" t="s">
         <v>211</v>
-      </c>
-      <c r="F231" s="4" t="s">
-        <v>212</v>
       </c>
       <c r="G231" s="4" t="s">
         <v>96</v>
@@ -27797,13 +27794,13 @@
         <v>4430</v>
       </c>
       <c r="D232" s="4" t="s">
+        <v>209</v>
+      </c>
+      <c r="E232" s="4" t="s">
         <v>210</v>
       </c>
-      <c r="E232" s="4" t="s">
+      <c r="F232" s="4" t="s">
         <v>211</v>
-      </c>
-      <c r="F232" s="4" t="s">
-        <v>212</v>
       </c>
       <c r="G232" s="4" t="s">
         <v>96</v>
@@ -27869,7 +27866,7 @@
         <v>0</v>
       </c>
       <c r="AB232" s="4" t="s">
-        <v>213</v>
+        <v>212</v>
       </c>
       <c r="AC232" s="4" t="s">
         <v>153</v>
@@ -27916,16 +27913,16 @@
         <v>4430</v>
       </c>
       <c r="D233" s="4" t="s">
-        <v>210</v>
+        <v>209</v>
       </c>
       <c r="E233" s="4" t="s">
+        <v>213</v>
+      </c>
+      <c r="F233" s="4" t="s">
         <v>214</v>
       </c>
-      <c r="F233" s="4" t="s">
+      <c r="G233" s="4" t="s">
         <v>215</v>
-      </c>
-      <c r="G233" s="4" t="s">
-        <v>216</v>
       </c>
       <c r="H233" s="3">
         <v>1156</v>
@@ -28031,16 +28028,16 @@
         <v>4430</v>
       </c>
       <c r="D234" s="4" t="s">
-        <v>210</v>
+        <v>209</v>
       </c>
       <c r="E234" s="4" t="s">
+        <v>213</v>
+      </c>
+      <c r="F234" s="4" t="s">
         <v>214</v>
       </c>
-      <c r="F234" s="4" t="s">
+      <c r="G234" s="4" t="s">
         <v>215</v>
-      </c>
-      <c r="G234" s="4" t="s">
-        <v>216</v>
       </c>
       <c r="H234" s="3">
         <v>1156</v>
@@ -28146,16 +28143,16 @@
         <v>4430</v>
       </c>
       <c r="D235" s="4" t="s">
-        <v>210</v>
+        <v>209</v>
       </c>
       <c r="E235" s="4" t="s">
+        <v>216</v>
+      </c>
+      <c r="F235" s="4" t="s">
         <v>217</v>
       </c>
-      <c r="F235" s="4" t="s">
+      <c r="G235" s="4" t="s">
         <v>218</v>
-      </c>
-      <c r="G235" s="4" t="s">
-        <v>219</v>
       </c>
       <c r="H235" s="3">
         <v>1054</v>
@@ -28261,16 +28258,16 @@
         <v>4430</v>
       </c>
       <c r="D236" s="4" t="s">
-        <v>210</v>
+        <v>209</v>
       </c>
       <c r="E236" s="4" t="s">
+        <v>216</v>
+      </c>
+      <c r="F236" s="4" t="s">
         <v>217</v>
       </c>
-      <c r="F236" s="4" t="s">
+      <c r="G236" s="4" t="s">
         <v>218</v>
-      </c>
-      <c r="G236" s="4" t="s">
-        <v>219</v>
       </c>
       <c r="H236" s="3">
         <v>1054</v>
@@ -28376,16 +28373,16 @@
         <v>4430</v>
       </c>
       <c r="D237" s="4" t="s">
-        <v>210</v>
+        <v>209</v>
       </c>
       <c r="E237" s="4" t="s">
+        <v>216</v>
+      </c>
+      <c r="F237" s="4" t="s">
         <v>217</v>
       </c>
-      <c r="F237" s="4" t="s">
+      <c r="G237" s="4" t="s">
         <v>218</v>
-      </c>
-      <c r="G237" s="4" t="s">
-        <v>219</v>
       </c>
       <c r="H237" s="3">
         <v>1054</v>
@@ -28448,7 +28445,7 @@
         <v>0</v>
       </c>
       <c r="AB237" s="4" t="s">
-        <v>220</v>
+        <v>219</v>
       </c>
       <c r="AC237" s="4" t="s">
         <v>153</v>
@@ -28495,16 +28492,16 @@
         <v>4430</v>
       </c>
       <c r="D238" s="4" t="s">
-        <v>210</v>
+        <v>209</v>
       </c>
       <c r="E238" s="4" t="s">
+        <v>220</v>
+      </c>
+      <c r="F238" s="4" t="s">
         <v>221</v>
       </c>
-      <c r="F238" s="4" t="s">
+      <c r="G238" s="4" t="s">
         <v>222</v>
-      </c>
-      <c r="G238" s="4" t="s">
-        <v>223</v>
       </c>
       <c r="H238" s="3">
         <v>1055</v>
@@ -28610,16 +28607,16 @@
         <v>4431</v>
       </c>
       <c r="D239" s="4" t="s">
+        <v>223</v>
+      </c>
+      <c r="E239" s="4" t="s">
         <v>224</v>
       </c>
-      <c r="E239" s="4" t="s">
+      <c r="F239" s="4" t="s">
         <v>225</v>
       </c>
-      <c r="F239" s="4" t="s">
+      <c r="G239" s="4" t="s">
         <v>226</v>
-      </c>
-      <c r="G239" s="4" t="s">
-        <v>227</v>
       </c>
       <c r="H239" s="3">
         <v>716</v>
@@ -28725,16 +28722,16 @@
         <v>4431</v>
       </c>
       <c r="D240" s="4" t="s">
+        <v>223</v>
+      </c>
+      <c r="E240" s="4" t="s">
         <v>224</v>
       </c>
-      <c r="E240" s="4" t="s">
+      <c r="F240" s="4" t="s">
         <v>225</v>
       </c>
-      <c r="F240" s="4" t="s">
+      <c r="G240" s="4" t="s">
         <v>226</v>
-      </c>
-      <c r="G240" s="4" t="s">
-        <v>227</v>
       </c>
       <c r="H240" s="3">
         <v>716</v>
@@ -28840,16 +28837,16 @@
         <v>4431</v>
       </c>
       <c r="D241" s="4" t="s">
-        <v>224</v>
+        <v>223</v>
       </c>
       <c r="E241" s="4" t="s">
+        <v>227</v>
+      </c>
+      <c r="F241" s="4" t="s">
         <v>228</v>
       </c>
-      <c r="F241" s="4" t="s">
+      <c r="G241" s="4" t="s">
         <v>229</v>
-      </c>
-      <c r="G241" s="4" t="s">
-        <v>230</v>
       </c>
       <c r="H241" s="3">
         <v>882</v>
@@ -28955,16 +28952,16 @@
         <v>4431</v>
       </c>
       <c r="D242" s="4" t="s">
-        <v>224</v>
+        <v>223</v>
       </c>
       <c r="E242" s="4" t="s">
+        <v>230</v>
+      </c>
+      <c r="F242" s="4" t="s">
         <v>231</v>
       </c>
-      <c r="F242" s="4" t="s">
+      <c r="G242" s="4" t="s">
         <v>232</v>
-      </c>
-      <c r="G242" s="4" t="s">
-        <v>233</v>
       </c>
       <c r="H242" s="3">
         <v>885</v>
@@ -29070,16 +29067,16 @@
         <v>4431</v>
       </c>
       <c r="D243" s="4" t="s">
-        <v>224</v>
+        <v>223</v>
       </c>
       <c r="E243" s="4" t="s">
+        <v>230</v>
+      </c>
+      <c r="F243" s="4" t="s">
         <v>231</v>
       </c>
-      <c r="F243" s="4" t="s">
+      <c r="G243" s="4" t="s">
         <v>232</v>
-      </c>
-      <c r="G243" s="4" t="s">
-        <v>233</v>
       </c>
       <c r="H243" s="3">
         <v>885</v>
@@ -29142,7 +29139,7 @@
         <v>0</v>
       </c>
       <c r="AB243" s="4" t="s">
-        <v>234</v>
+        <v>233</v>
       </c>
       <c r="AC243" s="4" t="s">
         <v>153</v>
@@ -29189,16 +29186,16 @@
         <v>4431</v>
       </c>
       <c r="D244" s="4" t="s">
-        <v>224</v>
+        <v>223</v>
       </c>
       <c r="E244" s="4" t="s">
+        <v>234</v>
+      </c>
+      <c r="F244" s="4" t="s">
         <v>235</v>
       </c>
-      <c r="F244" s="4" t="s">
+      <c r="G244" s="4" t="s">
         <v>236</v>
-      </c>
-      <c r="G244" s="4" t="s">
-        <v>237</v>
       </c>
       <c r="H244" s="3">
         <v>274</v>
@@ -29304,16 +29301,16 @@
         <v>4431</v>
       </c>
       <c r="D245" s="4" t="s">
-        <v>224</v>
+        <v>223</v>
       </c>
       <c r="E245" s="4" t="s">
+        <v>234</v>
+      </c>
+      <c r="F245" s="4" t="s">
         <v>235</v>
       </c>
-      <c r="F245" s="4" t="s">
+      <c r="G245" s="4" t="s">
         <v>236</v>
-      </c>
-      <c r="G245" s="4" t="s">
-        <v>237</v>
       </c>
       <c r="H245" s="3">
         <v>274</v>
@@ -29376,7 +29373,7 @@
         <v>0</v>
       </c>
       <c r="AB245" s="4" t="s">
-        <v>238</v>
+        <v>237</v>
       </c>
       <c r="AC245" s="4" t="s">
         <v>153</v>
@@ -29423,16 +29420,16 @@
         <v>4431</v>
       </c>
       <c r="D246" s="4" t="s">
-        <v>224</v>
+        <v>223</v>
       </c>
       <c r="E246" s="4" t="s">
+        <v>238</v>
+      </c>
+      <c r="F246" s="4" t="s">
         <v>239</v>
       </c>
-      <c r="F246" s="4" t="s">
+      <c r="G246" s="4" t="s">
         <v>240</v>
-      </c>
-      <c r="G246" s="4" t="s">
-        <v>241</v>
       </c>
       <c r="H246" s="3">
         <v>157</v>
@@ -29538,16 +29535,16 @@
         <v>4431</v>
       </c>
       <c r="D247" s="4" t="s">
-        <v>224</v>
+        <v>223</v>
       </c>
       <c r="E247" s="4" t="s">
+        <v>241</v>
+      </c>
+      <c r="F247" s="4" t="s">
         <v>242</v>
       </c>
-      <c r="F247" s="4" t="s">
+      <c r="G247" s="4" t="s">
         <v>243</v>
-      </c>
-      <c r="G247" s="4" t="s">
-        <v>244</v>
       </c>
       <c r="H247" s="3">
         <v>250</v>
@@ -29653,16 +29650,16 @@
         <v>4431</v>
       </c>
       <c r="D248" s="4" t="s">
-        <v>224</v>
+        <v>223</v>
       </c>
       <c r="E248" s="4" t="s">
+        <v>241</v>
+      </c>
+      <c r="F248" s="4" t="s">
         <v>242</v>
       </c>
-      <c r="F248" s="4" t="s">
+      <c r="G248" s="4" t="s">
         <v>243</v>
-      </c>
-      <c r="G248" s="4" t="s">
-        <v>244</v>
       </c>
       <c r="H248" s="3">
         <v>250</v>
@@ -29725,7 +29722,7 @@
         <v>0</v>
       </c>
       <c r="AB248" s="4" t="s">
-        <v>245</v>
+        <v>244</v>
       </c>
       <c r="AC248" s="4" t="s">
         <v>153</v>
@@ -29772,16 +29769,16 @@
         <v>4431</v>
       </c>
       <c r="D249" s="4" t="s">
-        <v>224</v>
+        <v>223</v>
       </c>
       <c r="E249" s="4" t="s">
+        <v>245</v>
+      </c>
+      <c r="F249" s="4" t="s">
         <v>246</v>
       </c>
-      <c r="F249" s="4" t="s">
+      <c r="G249" s="4" t="s">
         <v>247</v>
-      </c>
-      <c r="G249" s="4" t="s">
-        <v>248</v>
       </c>
       <c r="H249" s="3">
         <v>146</v>
@@ -29887,16 +29884,16 @@
         <v>4431</v>
       </c>
       <c r="D250" s="4" t="s">
-        <v>224</v>
+        <v>223</v>
       </c>
       <c r="E250" s="4" t="s">
+        <v>245</v>
+      </c>
+      <c r="F250" s="4" t="s">
         <v>246</v>
       </c>
-      <c r="F250" s="4" t="s">
+      <c r="G250" s="4" t="s">
         <v>247</v>
-      </c>
-      <c r="G250" s="4" t="s">
-        <v>248</v>
       </c>
       <c r="H250" s="3">
         <v>146</v>
@@ -30002,16 +29999,16 @@
         <v>4431</v>
       </c>
       <c r="D251" s="4" t="s">
-        <v>224</v>
+        <v>223</v>
       </c>
       <c r="E251" s="4" t="s">
+        <v>248</v>
+      </c>
+      <c r="F251" s="4" t="s">
         <v>249</v>
       </c>
-      <c r="F251" s="4" t="s">
+      <c r="G251" s="4" t="s">
         <v>250</v>
-      </c>
-      <c r="G251" s="4" t="s">
-        <v>251</v>
       </c>
       <c r="H251" s="3">
         <v>178</v>
@@ -30117,16 +30114,16 @@
         <v>4431</v>
       </c>
       <c r="D252" s="4" t="s">
-        <v>224</v>
+        <v>223</v>
       </c>
       <c r="E252" s="4" t="s">
+        <v>248</v>
+      </c>
+      <c r="F252" s="4" t="s">
         <v>249</v>
       </c>
-      <c r="F252" s="4" t="s">
+      <c r="G252" s="4" t="s">
         <v>250</v>
-      </c>
-      <c r="G252" s="4" t="s">
-        <v>251</v>
       </c>
       <c r="H252" s="3">
         <v>178</v>
@@ -30232,16 +30229,16 @@
         <v>4431</v>
       </c>
       <c r="D253" s="4" t="s">
-        <v>224</v>
+        <v>223</v>
       </c>
       <c r="E253" s="4" t="s">
+        <v>248</v>
+      </c>
+      <c r="F253" s="4" t="s">
         <v>249</v>
       </c>
-      <c r="F253" s="4" t="s">
+      <c r="G253" s="4" t="s">
         <v>250</v>
-      </c>
-      <c r="G253" s="4" t="s">
-        <v>251</v>
       </c>
       <c r="H253" s="3">
         <v>1777</v>
@@ -30250,7 +30247,7 @@
         <v>2025</v>
       </c>
       <c r="J253" s="4" t="s">
-        <v>252</v>
+        <v>251</v>
       </c>
       <c r="K253" s="3">
         <v>0</v>
@@ -30347,16 +30344,16 @@
         <v>4431</v>
       </c>
       <c r="D254" s="4" t="s">
-        <v>224</v>
+        <v>223</v>
       </c>
       <c r="E254" s="4" t="s">
+        <v>248</v>
+      </c>
+      <c r="F254" s="4" t="s">
         <v>249</v>
       </c>
-      <c r="F254" s="4" t="s">
+      <c r="G254" s="4" t="s">
         <v>250</v>
-      </c>
-      <c r="G254" s="4" t="s">
-        <v>251</v>
       </c>
       <c r="H254" s="3">
         <v>1777</v>
@@ -30365,7 +30362,7 @@
         <v>2025</v>
       </c>
       <c r="J254" s="4" t="s">
-        <v>252</v>
+        <v>251</v>
       </c>
       <c r="K254" s="3">
         <v>0</v>
@@ -30419,7 +30416,7 @@
         <v>0</v>
       </c>
       <c r="AB254" s="4" t="s">
-        <v>253</v>
+        <v>252</v>
       </c>
       <c r="AC254" s="4" t="s">
         <v>153</v>
@@ -30466,16 +30463,16 @@
         <v>4431</v>
       </c>
       <c r="D255" s="4" t="s">
-        <v>224</v>
+        <v>223</v>
       </c>
       <c r="E255" s="4" t="s">
+        <v>253</v>
+      </c>
+      <c r="F255" s="4" t="s">
         <v>254</v>
       </c>
-      <c r="F255" s="4" t="s">
+      <c r="G255" s="4" t="s">
         <v>255</v>
-      </c>
-      <c r="G255" s="4" t="s">
-        <v>256</v>
       </c>
       <c r="H255" s="3">
         <v>179</v>
@@ -30581,16 +30578,16 @@
         <v>4431</v>
       </c>
       <c r="D256" s="4" t="s">
-        <v>224</v>
+        <v>223</v>
       </c>
       <c r="E256" s="4" t="s">
+        <v>253</v>
+      </c>
+      <c r="F256" s="4" t="s">
         <v>254</v>
       </c>
-      <c r="F256" s="4" t="s">
+      <c r="G256" s="4" t="s">
         <v>255</v>
-      </c>
-      <c r="G256" s="4" t="s">
-        <v>256</v>
       </c>
       <c r="H256" s="3">
         <v>179</v>
@@ -30696,13 +30693,13 @@
         <v>4431</v>
       </c>
       <c r="D257" s="4" t="s">
-        <v>224</v>
+        <v>223</v>
       </c>
       <c r="E257" s="4" t="s">
+        <v>210</v>
+      </c>
+      <c r="F257" s="4" t="s">
         <v>211</v>
-      </c>
-      <c r="F257" s="4" t="s">
-        <v>212</v>
       </c>
       <c r="G257" s="4" t="s">
         <v>96</v>
@@ -30811,13 +30808,13 @@
         <v>4431</v>
       </c>
       <c r="D258" s="4" t="s">
-        <v>224</v>
+        <v>223</v>
       </c>
       <c r="E258" s="4" t="s">
+        <v>210</v>
+      </c>
+      <c r="F258" s="4" t="s">
         <v>211</v>
-      </c>
-      <c r="F258" s="4" t="s">
-        <v>212</v>
       </c>
       <c r="G258" s="4" t="s">
         <v>96</v>
@@ -30926,16 +30923,16 @@
         <v>4431</v>
       </c>
       <c r="D259" s="4" t="s">
-        <v>224</v>
+        <v>223</v>
       </c>
       <c r="E259" s="4" t="s">
+        <v>256</v>
+      </c>
+      <c r="F259" s="4" t="s">
         <v>257</v>
       </c>
-      <c r="F259" s="4" t="s">
+      <c r="G259" s="4" t="s">
         <v>258</v>
-      </c>
-      <c r="G259" s="4" t="s">
-        <v>259</v>
       </c>
       <c r="H259" s="3">
         <v>190</v>
@@ -31041,16 +31038,16 @@
         <v>4431</v>
       </c>
       <c r="D260" s="4" t="s">
-        <v>224</v>
+        <v>223</v>
       </c>
       <c r="E260" s="4" t="s">
+        <v>256</v>
+      </c>
+      <c r="F260" s="4" t="s">
         <v>257</v>
       </c>
-      <c r="F260" s="4" t="s">
+      <c r="G260" s="4" t="s">
         <v>258</v>
-      </c>
-      <c r="G260" s="4" t="s">
-        <v>259</v>
       </c>
       <c r="H260" s="3">
         <v>190</v>
@@ -31156,16 +31153,16 @@
         <v>4431</v>
       </c>
       <c r="D261" s="4" t="s">
-        <v>224</v>
+        <v>223</v>
       </c>
       <c r="E261" s="4" t="s">
+        <v>259</v>
+      </c>
+      <c r="F261" s="4" t="s">
         <v>260</v>
       </c>
-      <c r="F261" s="4" t="s">
+      <c r="G261" s="4" t="s">
         <v>261</v>
-      </c>
-      <c r="G261" s="4" t="s">
-        <v>262</v>
       </c>
       <c r="H261" s="3">
         <v>191</v>
@@ -31271,16 +31268,16 @@
         <v>4431</v>
       </c>
       <c r="D262" s="4" t="s">
-        <v>224</v>
+        <v>223</v>
       </c>
       <c r="E262" s="4" t="s">
+        <v>259</v>
+      </c>
+      <c r="F262" s="4" t="s">
         <v>260</v>
       </c>
-      <c r="F262" s="4" t="s">
+      <c r="G262" s="4" t="s">
         <v>261</v>
-      </c>
-      <c r="G262" s="4" t="s">
-        <v>262</v>
       </c>
       <c r="H262" s="3">
         <v>191</v>
@@ -31343,7 +31340,7 @@
         <v>0</v>
       </c>
       <c r="AB262" s="4" t="s">
-        <v>263</v>
+        <v>262</v>
       </c>
       <c r="AC262" s="4" t="s">
         <v>153</v>
@@ -31390,16 +31387,16 @@
         <v>4431</v>
       </c>
       <c r="D263" s="4" t="s">
-        <v>224</v>
+        <v>223</v>
       </c>
       <c r="E263" s="4" t="s">
+        <v>263</v>
+      </c>
+      <c r="F263" s="4" t="s">
         <v>264</v>
       </c>
-      <c r="F263" s="4" t="s">
+      <c r="G263" s="4" t="s">
         <v>265</v>
-      </c>
-      <c r="G263" s="4" t="s">
-        <v>266</v>
       </c>
       <c r="H263" s="3">
         <v>220</v>
@@ -31505,16 +31502,16 @@
         <v>4431</v>
       </c>
       <c r="D264" s="4" t="s">
-        <v>224</v>
+        <v>223</v>
       </c>
       <c r="E264" s="4" t="s">
+        <v>263</v>
+      </c>
+      <c r="F264" s="4" t="s">
         <v>264</v>
       </c>
-      <c r="F264" s="4" t="s">
+      <c r="G264" s="4" t="s">
         <v>265</v>
-      </c>
-      <c r="G264" s="4" t="s">
-        <v>266</v>
       </c>
       <c r="H264" s="3">
         <v>220</v>
@@ -31620,16 +31617,16 @@
         <v>4431</v>
       </c>
       <c r="D265" s="4" t="s">
-        <v>224</v>
+        <v>223</v>
       </c>
       <c r="E265" s="4" t="s">
+        <v>263</v>
+      </c>
+      <c r="F265" s="4" t="s">
         <v>264</v>
       </c>
-      <c r="F265" s="4" t="s">
+      <c r="G265" s="4" t="s">
         <v>265</v>
-      </c>
-      <c r="G265" s="4" t="s">
-        <v>266</v>
       </c>
       <c r="H265" s="3">
         <v>220</v>
@@ -31692,7 +31689,7 @@
         <v>0</v>
       </c>
       <c r="AB265" s="4" t="s">
-        <v>267</v>
+        <v>266</v>
       </c>
       <c r="AC265" s="4" t="s">
         <v>153</v>
@@ -31739,16 +31736,16 @@
         <v>4431</v>
       </c>
       <c r="D266" s="4" t="s">
-        <v>224</v>
+        <v>223</v>
       </c>
       <c r="E266" s="4" t="s">
+        <v>267</v>
+      </c>
+      <c r="F266" s="4" t="s">
         <v>268</v>
       </c>
-      <c r="F266" s="4" t="s">
+      <c r="G266" s="4" t="s">
         <v>269</v>
-      </c>
-      <c r="G266" s="4" t="s">
-        <v>270</v>
       </c>
       <c r="H266" s="3">
         <v>259</v>
@@ -31854,16 +31851,16 @@
         <v>4431</v>
       </c>
       <c r="D267" s="4" t="s">
-        <v>224</v>
+        <v>223</v>
       </c>
       <c r="E267" s="4" t="s">
+        <v>267</v>
+      </c>
+      <c r="F267" s="4" t="s">
         <v>268</v>
       </c>
-      <c r="F267" s="4" t="s">
+      <c r="G267" s="4" t="s">
         <v>269</v>
-      </c>
-      <c r="G267" s="4" t="s">
-        <v>270</v>
       </c>
       <c r="H267" s="3">
         <v>259</v>
@@ -31926,7 +31923,7 @@
         <v>0</v>
       </c>
       <c r="AB267" s="4" t="s">
-        <v>271</v>
+        <v>270</v>
       </c>
       <c r="AC267" s="4" t="s">
         <v>153</v>
@@ -31973,16 +31970,16 @@
         <v>4431</v>
       </c>
       <c r="D268" s="4" t="s">
-        <v>224</v>
+        <v>223</v>
       </c>
       <c r="E268" s="4" t="s">
+        <v>271</v>
+      </c>
+      <c r="F268" s="4" t="s">
         <v>272</v>
       </c>
-      <c r="F268" s="4" t="s">
+      <c r="G268" s="4" t="s">
         <v>273</v>
-      </c>
-      <c r="G268" s="4" t="s">
-        <v>274</v>
       </c>
       <c r="H268" s="3">
         <v>1780</v>
@@ -31991,7 +31988,7 @@
         <v>2025</v>
       </c>
       <c r="J268" s="4" t="s">
-        <v>252</v>
+        <v>251</v>
       </c>
       <c r="K268" s="3">
         <v>0</v>
@@ -32088,16 +32085,16 @@
         <v>4431</v>
       </c>
       <c r="D269" s="4" t="s">
-        <v>224</v>
+        <v>223</v>
       </c>
       <c r="E269" s="4" t="s">
+        <v>271</v>
+      </c>
+      <c r="F269" s="4" t="s">
         <v>272</v>
       </c>
-      <c r="F269" s="4" t="s">
+      <c r="G269" s="4" t="s">
         <v>273</v>
-      </c>
-      <c r="G269" s="4" t="s">
-        <v>274</v>
       </c>
       <c r="H269" s="3">
         <v>1780</v>
@@ -32106,7 +32103,7 @@
         <v>2025</v>
       </c>
       <c r="J269" s="4" t="s">
-        <v>252</v>
+        <v>251</v>
       </c>
       <c r="K269" s="3">
         <v>0</v>
@@ -32160,7 +32157,7 @@
         <v>0</v>
       </c>
       <c r="AB269" s="4" t="s">
-        <v>275</v>
+        <v>274</v>
       </c>
       <c r="AC269" s="4" t="s">
         <v>153</v>
@@ -32207,16 +32204,16 @@
         <v>4431</v>
       </c>
       <c r="D270" s="4" t="s">
-        <v>224</v>
+        <v>223</v>
       </c>
       <c r="E270" s="4" t="s">
+        <v>275</v>
+      </c>
+      <c r="F270" s="4" t="s">
         <v>276</v>
       </c>
-      <c r="F270" s="4" t="s">
+      <c r="G270" s="4" t="s">
         <v>277</v>
-      </c>
-      <c r="G270" s="4" t="s">
-        <v>278</v>
       </c>
       <c r="H270" s="3">
         <v>267</v>
@@ -32322,16 +32319,16 @@
         <v>4431</v>
       </c>
       <c r="D271" s="4" t="s">
-        <v>224</v>
+        <v>223</v>
       </c>
       <c r="E271" s="4" t="s">
+        <v>275</v>
+      </c>
+      <c r="F271" s="4" t="s">
         <v>276</v>
       </c>
-      <c r="F271" s="4" t="s">
+      <c r="G271" s="4" t="s">
         <v>277</v>
-      </c>
-      <c r="G271" s="4" t="s">
-        <v>278</v>
       </c>
       <c r="H271" s="3">
         <v>267</v>
@@ -32394,7 +32391,7 @@
         <v>0</v>
       </c>
       <c r="AB271" s="4" t="s">
-        <v>279</v>
+        <v>278</v>
       </c>
       <c r="AC271" s="4" t="s">
         <v>153</v>
@@ -32441,16 +32438,16 @@
         <v>4431</v>
       </c>
       <c r="D272" s="4" t="s">
-        <v>224</v>
+        <v>223</v>
       </c>
       <c r="E272" s="4" t="s">
+        <v>279</v>
+      </c>
+      <c r="F272" s="4" t="s">
         <v>280</v>
       </c>
-      <c r="F272" s="4" t="s">
+      <c r="G272" s="4" t="s">
         <v>281</v>
-      </c>
-      <c r="G272" s="4" t="s">
-        <v>282</v>
       </c>
       <c r="H272" s="3">
         <v>273</v>
@@ -32556,16 +32553,16 @@
         <v>4431</v>
       </c>
       <c r="D273" s="4" t="s">
-        <v>224</v>
+        <v>223</v>
       </c>
       <c r="E273" s="4" t="s">
+        <v>282</v>
+      </c>
+      <c r="F273" s="4" t="s">
         <v>283</v>
       </c>
-      <c r="F273" s="4" t="s">
+      <c r="G273" s="4" t="s">
         <v>284</v>
-      </c>
-      <c r="G273" s="4" t="s">
-        <v>285</v>
       </c>
       <c r="H273" s="3">
         <v>278</v>
@@ -32671,16 +32668,16 @@
         <v>4431</v>
       </c>
       <c r="D274" s="4" t="s">
-        <v>224</v>
+        <v>223</v>
       </c>
       <c r="E274" s="4" t="s">
+        <v>282</v>
+      </c>
+      <c r="F274" s="4" t="s">
         <v>283</v>
       </c>
-      <c r="F274" s="4" t="s">
+      <c r="G274" s="4" t="s">
         <v>284</v>
-      </c>
-      <c r="G274" s="4" t="s">
-        <v>285</v>
       </c>
       <c r="H274" s="3">
         <v>278</v>
@@ -32786,16 +32783,16 @@
         <v>4431</v>
       </c>
       <c r="D275" s="4" t="s">
-        <v>224</v>
+        <v>223</v>
       </c>
       <c r="E275" s="4" t="s">
+        <v>285</v>
+      </c>
+      <c r="F275" s="4" t="s">
         <v>286</v>
       </c>
-      <c r="F275" s="4" t="s">
+      <c r="G275" s="4" t="s">
         <v>287</v>
-      </c>
-      <c r="G275" s="4" t="s">
-        <v>288</v>
       </c>
       <c r="H275" s="3">
         <v>282</v>
@@ -32901,16 +32898,16 @@
         <v>4431</v>
       </c>
       <c r="D276" s="4" t="s">
-        <v>224</v>
+        <v>223</v>
       </c>
       <c r="E276" s="4" t="s">
+        <v>285</v>
+      </c>
+      <c r="F276" s="4" t="s">
         <v>286</v>
       </c>
-      <c r="F276" s="4" t="s">
+      <c r="G276" s="4" t="s">
         <v>287</v>
-      </c>
-      <c r="G276" s="4" t="s">
-        <v>288</v>
       </c>
       <c r="H276" s="3">
         <v>282</v>
@@ -33016,16 +33013,16 @@
         <v>4431</v>
       </c>
       <c r="D277" s="4" t="s">
-        <v>224</v>
+        <v>223</v>
       </c>
       <c r="E277" s="4" t="s">
+        <v>288</v>
+      </c>
+      <c r="F277" s="4" t="s">
         <v>289</v>
       </c>
-      <c r="F277" s="4" t="s">
+      <c r="G277" s="4" t="s">
         <v>290</v>
-      </c>
-      <c r="G277" s="4" t="s">
-        <v>291</v>
       </c>
       <c r="H277" s="3">
         <v>298</v>
@@ -33131,16 +33128,16 @@
         <v>4431</v>
       </c>
       <c r="D278" s="4" t="s">
-        <v>224</v>
+        <v>223</v>
       </c>
       <c r="E278" s="4" t="s">
+        <v>288</v>
+      </c>
+      <c r="F278" s="4" t="s">
         <v>289</v>
       </c>
-      <c r="F278" s="4" t="s">
+      <c r="G278" s="4" t="s">
         <v>290</v>
-      </c>
-      <c r="G278" s="4" t="s">
-        <v>291</v>
       </c>
       <c r="H278" s="3">
         <v>298</v>
@@ -33246,16 +33243,16 @@
         <v>4431</v>
       </c>
       <c r="D279" s="4" t="s">
-        <v>224</v>
+        <v>223</v>
       </c>
       <c r="E279" s="4" t="s">
+        <v>291</v>
+      </c>
+      <c r="F279" s="4" t="s">
         <v>292</v>
       </c>
-      <c r="F279" s="4" t="s">
+      <c r="G279" s="4" t="s">
         <v>293</v>
-      </c>
-      <c r="G279" s="4" t="s">
-        <v>294</v>
       </c>
       <c r="H279" s="3">
         <v>314</v>
@@ -33361,16 +33358,16 @@
         <v>4431</v>
       </c>
       <c r="D280" s="4" t="s">
-        <v>224</v>
+        <v>223</v>
       </c>
       <c r="E280" s="4" t="s">
+        <v>291</v>
+      </c>
+      <c r="F280" s="4" t="s">
         <v>292</v>
       </c>
-      <c r="F280" s="4" t="s">
+      <c r="G280" s="4" t="s">
         <v>293</v>
-      </c>
-      <c r="G280" s="4" t="s">
-        <v>294</v>
       </c>
       <c r="H280" s="3">
         <v>314</v>
@@ -33476,16 +33473,16 @@
         <v>4431</v>
       </c>
       <c r="D281" s="4" t="s">
-        <v>224</v>
+        <v>223</v>
       </c>
       <c r="E281" s="4" t="s">
+        <v>291</v>
+      </c>
+      <c r="F281" s="4" t="s">
         <v>292</v>
       </c>
-      <c r="F281" s="4" t="s">
+      <c r="G281" s="4" t="s">
         <v>293</v>
-      </c>
-      <c r="G281" s="4" t="s">
-        <v>294</v>
       </c>
       <c r="H281" s="3">
         <v>314</v>
@@ -33548,7 +33545,7 @@
         <v>0</v>
       </c>
       <c r="AB281" s="4" t="s">
-        <v>295</v>
+        <v>294</v>
       </c>
       <c r="AC281" s="4" t="s">
         <v>153</v>
@@ -33595,16 +33592,16 @@
         <v>4431</v>
       </c>
       <c r="D282" s="4" t="s">
-        <v>224</v>
+        <v>223</v>
       </c>
       <c r="E282" s="4" t="s">
+        <v>295</v>
+      </c>
+      <c r="F282" s="4" t="s">
         <v>296</v>
       </c>
-      <c r="F282" s="4" t="s">
+      <c r="G282" s="4" t="s">
         <v>297</v>
-      </c>
-      <c r="G282" s="4" t="s">
-        <v>298</v>
       </c>
       <c r="H282" s="3">
         <v>322</v>
@@ -33710,16 +33707,16 @@
         <v>4431</v>
       </c>
       <c r="D283" s="4" t="s">
-        <v>224</v>
+        <v>223</v>
       </c>
       <c r="E283" s="4" t="s">
+        <v>295</v>
+      </c>
+      <c r="F283" s="4" t="s">
         <v>296</v>
       </c>
-      <c r="F283" s="4" t="s">
+      <c r="G283" s="4" t="s">
         <v>297</v>
-      </c>
-      <c r="G283" s="4" t="s">
-        <v>298</v>
       </c>
       <c r="H283" s="3">
         <v>322</v>
@@ -33825,16 +33822,16 @@
         <v>4431</v>
       </c>
       <c r="D284" s="4" t="s">
-        <v>224</v>
+        <v>223</v>
       </c>
       <c r="E284" s="4" t="s">
+        <v>295</v>
+      </c>
+      <c r="F284" s="4" t="s">
         <v>296</v>
       </c>
-      <c r="F284" s="4" t="s">
+      <c r="G284" s="4" t="s">
         <v>297</v>
-      </c>
-      <c r="G284" s="4" t="s">
-        <v>298</v>
       </c>
       <c r="H284" s="3">
         <v>322</v>
@@ -33897,7 +33894,7 @@
         <v>0</v>
       </c>
       <c r="AB284" s="4" t="s">
-        <v>299</v>
+        <v>298</v>
       </c>
       <c r="AC284" s="4" t="s">
         <v>153</v>
@@ -33944,16 +33941,16 @@
         <v>4431</v>
       </c>
       <c r="D285" s="4" t="s">
-        <v>224</v>
+        <v>223</v>
       </c>
       <c r="E285" s="4" t="s">
+        <v>299</v>
+      </c>
+      <c r="F285" s="4" t="s">
         <v>300</v>
       </c>
-      <c r="F285" s="4" t="s">
+      <c r="G285" s="4" t="s">
         <v>301</v>
-      </c>
-      <c r="G285" s="4" t="s">
-        <v>302</v>
       </c>
       <c r="H285" s="3">
         <v>535</v>
@@ -34059,16 +34056,16 @@
         <v>4431</v>
       </c>
       <c r="D286" s="4" t="s">
-        <v>224</v>
+        <v>223</v>
       </c>
       <c r="E286" s="4" t="s">
+        <v>299</v>
+      </c>
+      <c r="F286" s="4" t="s">
         <v>300</v>
       </c>
-      <c r="F286" s="4" t="s">
+      <c r="G286" s="4" t="s">
         <v>301</v>
-      </c>
-      <c r="G286" s="4" t="s">
-        <v>302</v>
       </c>
       <c r="H286" s="3">
         <v>535</v>
@@ -34174,16 +34171,16 @@
         <v>4431</v>
       </c>
       <c r="D287" s="4" t="s">
-        <v>224</v>
+        <v>223</v>
       </c>
       <c r="E287" s="4" t="s">
+        <v>302</v>
+      </c>
+      <c r="F287" s="4" t="s">
         <v>303</v>
       </c>
-      <c r="F287" s="4" t="s">
+      <c r="G287" s="4" t="s">
         <v>304</v>
-      </c>
-      <c r="G287" s="4" t="s">
-        <v>305</v>
       </c>
       <c r="H287" s="3">
         <v>537</v>
@@ -34289,16 +34286,16 @@
         <v>4431</v>
       </c>
       <c r="D288" s="4" t="s">
-        <v>224</v>
+        <v>223</v>
       </c>
       <c r="E288" s="4" t="s">
+        <v>302</v>
+      </c>
+      <c r="F288" s="4" t="s">
         <v>303</v>
       </c>
-      <c r="F288" s="4" t="s">
+      <c r="G288" s="4" t="s">
         <v>304</v>
-      </c>
-      <c r="G288" s="4" t="s">
-        <v>305</v>
       </c>
       <c r="H288" s="3">
         <v>537</v>
@@ -34404,13 +34401,13 @@
         <v>4431</v>
       </c>
       <c r="D289" s="4" t="s">
-        <v>224</v>
+        <v>223</v>
       </c>
       <c r="E289" s="4" t="s">
+        <v>305</v>
+      </c>
+      <c r="F289" s="4" t="s">
         <v>306</v>
-      </c>
-      <c r="F289" s="4" t="s">
-        <v>307</v>
       </c>
       <c r="G289" s="4" t="s">
         <v>111</v>
@@ -34519,13 +34516,13 @@
         <v>4431</v>
       </c>
       <c r="D290" s="4" t="s">
-        <v>224</v>
+        <v>223</v>
       </c>
       <c r="E290" s="4" t="s">
+        <v>305</v>
+      </c>
+      <c r="F290" s="4" t="s">
         <v>306</v>
-      </c>
-      <c r="F290" s="4" t="s">
-        <v>307</v>
       </c>
       <c r="G290" s="4" t="s">
         <v>111</v>
@@ -34591,7 +34588,7 @@
         <v>0</v>
       </c>
       <c r="AB290" s="4" t="s">
-        <v>308</v>
+        <v>307</v>
       </c>
       <c r="AC290" s="4" t="s">
         <v>153</v>
@@ -34638,16 +34635,16 @@
         <v>4431</v>
       </c>
       <c r="D291" s="4" t="s">
-        <v>224</v>
+        <v>223</v>
       </c>
       <c r="E291" s="4" t="s">
+        <v>308</v>
+      </c>
+      <c r="F291" s="4" t="s">
         <v>309</v>
       </c>
-      <c r="F291" s="4" t="s">
+      <c r="G291" s="4" t="s">
         <v>310</v>
-      </c>
-      <c r="G291" s="4" t="s">
-        <v>311</v>
       </c>
       <c r="H291" s="3">
         <v>366</v>
@@ -34753,16 +34750,16 @@
         <v>4431</v>
       </c>
       <c r="D292" s="4" t="s">
-        <v>224</v>
+        <v>223</v>
       </c>
       <c r="E292" s="4" t="s">
+        <v>311</v>
+      </c>
+      <c r="F292" s="4" t="s">
         <v>312</v>
       </c>
-      <c r="F292" s="4" t="s">
+      <c r="G292" s="4" t="s">
         <v>313</v>
-      </c>
-      <c r="G292" s="4" t="s">
-        <v>314</v>
       </c>
       <c r="H292" s="3">
         <v>475</v>
@@ -34868,16 +34865,16 @@
         <v>4431</v>
       </c>
       <c r="D293" s="4" t="s">
-        <v>224</v>
+        <v>223</v>
       </c>
       <c r="E293" s="4" t="s">
+        <v>311</v>
+      </c>
+      <c r="F293" s="4" t="s">
         <v>312</v>
       </c>
-      <c r="F293" s="4" t="s">
+      <c r="G293" s="4" t="s">
         <v>313</v>
-      </c>
-      <c r="G293" s="4" t="s">
-        <v>314</v>
       </c>
       <c r="H293" s="3">
         <v>475</v>
@@ -34983,16 +34980,16 @@
         <v>4431</v>
       </c>
       <c r="D294" s="4" t="s">
-        <v>224</v>
+        <v>223</v>
       </c>
       <c r="E294" s="4" t="s">
+        <v>314</v>
+      </c>
+      <c r="F294" s="4" t="s">
         <v>315</v>
       </c>
-      <c r="F294" s="4" t="s">
+      <c r="G294" s="4" t="s">
         <v>316</v>
-      </c>
-      <c r="G294" s="4" t="s">
-        <v>317</v>
       </c>
       <c r="H294" s="3">
         <v>507</v>
@@ -35098,16 +35095,16 @@
         <v>4431</v>
       </c>
       <c r="D295" s="4" t="s">
-        <v>224</v>
+        <v>223</v>
       </c>
       <c r="E295" s="4" t="s">
+        <v>314</v>
+      </c>
+      <c r="F295" s="4" t="s">
         <v>315</v>
       </c>
-      <c r="F295" s="4" t="s">
+      <c r="G295" s="4" t="s">
         <v>316</v>
-      </c>
-      <c r="G295" s="4" t="s">
-        <v>317</v>
       </c>
       <c r="H295" s="3">
         <v>507</v>
@@ -35213,16 +35210,16 @@
         <v>4431</v>
       </c>
       <c r="D296" s="4" t="s">
-        <v>224</v>
+        <v>223</v>
       </c>
       <c r="E296" s="4" t="s">
+        <v>314</v>
+      </c>
+      <c r="F296" s="4" t="s">
         <v>315</v>
       </c>
-      <c r="F296" s="4" t="s">
+      <c r="G296" s="4" t="s">
         <v>316</v>
-      </c>
-      <c r="G296" s="4" t="s">
-        <v>317</v>
       </c>
       <c r="H296" s="3">
         <v>507</v>
@@ -35285,7 +35282,7 @@
         <v>0</v>
       </c>
       <c r="AB296" s="4" t="s">
-        <v>318</v>
+        <v>317</v>
       </c>
       <c r="AC296" s="4" t="s">
         <v>153</v>
@@ -35332,16 +35329,16 @@
         <v>4431</v>
       </c>
       <c r="D297" s="4" t="s">
-        <v>224</v>
+        <v>223</v>
       </c>
       <c r="E297" s="4" t="s">
+        <v>318</v>
+      </c>
+      <c r="F297" s="4" t="s">
         <v>319</v>
       </c>
-      <c r="F297" s="4" t="s">
+      <c r="G297" s="4" t="s">
         <v>320</v>
-      </c>
-      <c r="G297" s="4" t="s">
-        <v>321</v>
       </c>
       <c r="H297" s="3">
         <v>508</v>
@@ -35447,16 +35444,16 @@
         <v>4431</v>
       </c>
       <c r="D298" s="4" t="s">
-        <v>224</v>
+        <v>223</v>
       </c>
       <c r="E298" s="4" t="s">
+        <v>318</v>
+      </c>
+      <c r="F298" s="4" t="s">
         <v>319</v>
       </c>
-      <c r="F298" s="4" t="s">
+      <c r="G298" s="4" t="s">
         <v>320</v>
-      </c>
-      <c r="G298" s="4" t="s">
-        <v>321</v>
       </c>
       <c r="H298" s="3">
         <v>508</v>
@@ -35562,16 +35559,16 @@
         <v>4431</v>
       </c>
       <c r="D299" s="4" t="s">
-        <v>224</v>
+        <v>223</v>
       </c>
       <c r="E299" s="4" t="s">
+        <v>318</v>
+      </c>
+      <c r="F299" s="4" t="s">
         <v>319</v>
       </c>
-      <c r="F299" s="4" t="s">
+      <c r="G299" s="4" t="s">
         <v>320</v>
-      </c>
-      <c r="G299" s="4" t="s">
-        <v>321</v>
       </c>
       <c r="H299" s="3">
         <v>508</v>
@@ -35634,7 +35631,7 @@
         <v>0</v>
       </c>
       <c r="AB299" s="4" t="s">
-        <v>322</v>
+        <v>321</v>
       </c>
       <c r="AC299" s="4" t="s">
         <v>153</v>
@@ -35681,16 +35678,16 @@
         <v>4431</v>
       </c>
       <c r="D300" s="4" t="s">
-        <v>224</v>
+        <v>223</v>
       </c>
       <c r="E300" s="4" t="s">
+        <v>322</v>
+      </c>
+      <c r="F300" s="4" t="s">
         <v>323</v>
       </c>
-      <c r="F300" s="4" t="s">
+      <c r="G300" s="4" t="s">
         <v>324</v>
-      </c>
-      <c r="G300" s="4" t="s">
-        <v>325</v>
       </c>
       <c r="H300" s="3">
         <v>518</v>
@@ -35796,16 +35793,16 @@
         <v>4431</v>
       </c>
       <c r="D301" s="4" t="s">
-        <v>224</v>
+        <v>223</v>
       </c>
       <c r="E301" s="4" t="s">
+        <v>322</v>
+      </c>
+      <c r="F301" s="4" t="s">
         <v>323</v>
       </c>
-      <c r="F301" s="4" t="s">
+      <c r="G301" s="4" t="s">
         <v>324</v>
-      </c>
-      <c r="G301" s="4" t="s">
-        <v>325</v>
       </c>
       <c r="H301" s="3">
         <v>518</v>
@@ -35911,16 +35908,16 @@
         <v>4431</v>
       </c>
       <c r="D302" s="4" t="s">
-        <v>224</v>
+        <v>223</v>
       </c>
       <c r="E302" s="4" t="s">
+        <v>325</v>
+      </c>
+      <c r="F302" s="4" t="s">
         <v>326</v>
       </c>
-      <c r="F302" s="4" t="s">
+      <c r="G302" s="4" t="s">
         <v>327</v>
-      </c>
-      <c r="G302" s="4" t="s">
-        <v>328</v>
       </c>
       <c r="H302" s="3">
         <v>521</v>
@@ -36026,16 +36023,16 @@
         <v>4431</v>
       </c>
       <c r="D303" s="4" t="s">
-        <v>224</v>
+        <v>223</v>
       </c>
       <c r="E303" s="4" t="s">
+        <v>325</v>
+      </c>
+      <c r="F303" s="4" t="s">
         <v>326</v>
       </c>
-      <c r="F303" s="4" t="s">
+      <c r="G303" s="4" t="s">
         <v>327</v>
-      </c>
-      <c r="G303" s="4" t="s">
-        <v>328</v>
       </c>
       <c r="H303" s="3">
         <v>521</v>
@@ -36141,16 +36138,16 @@
         <v>4431</v>
       </c>
       <c r="D304" s="4" t="s">
-        <v>224</v>
+        <v>223</v>
       </c>
       <c r="E304" s="4" t="s">
+        <v>328</v>
+      </c>
+      <c r="F304" s="4" t="s">
         <v>329</v>
       </c>
-      <c r="F304" s="4" t="s">
+      <c r="G304" s="4" t="s">
         <v>330</v>
-      </c>
-      <c r="G304" s="4" t="s">
-        <v>331</v>
       </c>
       <c r="H304" s="3">
         <v>544</v>
@@ -36256,16 +36253,16 @@
         <v>4431</v>
       </c>
       <c r="D305" s="4" t="s">
-        <v>224</v>
+        <v>223</v>
       </c>
       <c r="E305" s="4" t="s">
+        <v>328</v>
+      </c>
+      <c r="F305" s="4" t="s">
         <v>329</v>
       </c>
-      <c r="F305" s="4" t="s">
+      <c r="G305" s="4" t="s">
         <v>330</v>
-      </c>
-      <c r="G305" s="4" t="s">
-        <v>331</v>
       </c>
       <c r="H305" s="3">
         <v>544</v>
@@ -36371,16 +36368,16 @@
         <v>4431</v>
       </c>
       <c r="D306" s="4" t="s">
-        <v>224</v>
+        <v>223</v>
       </c>
       <c r="E306" s="4" t="s">
+        <v>331</v>
+      </c>
+      <c r="F306" s="4" t="s">
         <v>332</v>
       </c>
-      <c r="F306" s="4" t="s">
+      <c r="G306" s="4" t="s">
         <v>333</v>
-      </c>
-      <c r="G306" s="4" t="s">
-        <v>334</v>
       </c>
       <c r="H306" s="3">
         <v>618</v>
@@ -36486,16 +36483,16 @@
         <v>4431</v>
       </c>
       <c r="D307" s="4" t="s">
-        <v>224</v>
+        <v>223</v>
       </c>
       <c r="E307" s="4" t="s">
+        <v>331</v>
+      </c>
+      <c r="F307" s="4" t="s">
         <v>332</v>
       </c>
-      <c r="F307" s="4" t="s">
+      <c r="G307" s="4" t="s">
         <v>333</v>
-      </c>
-      <c r="G307" s="4" t="s">
-        <v>334</v>
       </c>
       <c r="H307" s="3">
         <v>618</v>
@@ -36601,16 +36598,16 @@
         <v>4431</v>
       </c>
       <c r="D308" s="4" t="s">
-        <v>224</v>
+        <v>223</v>
       </c>
       <c r="E308" s="4" t="s">
+        <v>331</v>
+      </c>
+      <c r="F308" s="4" t="s">
         <v>332</v>
       </c>
-      <c r="F308" s="4" t="s">
+      <c r="G308" s="4" t="s">
         <v>333</v>
-      </c>
-      <c r="G308" s="4" t="s">
-        <v>334</v>
       </c>
       <c r="H308" s="3">
         <v>618</v>
@@ -36673,7 +36670,7 @@
         <v>0</v>
       </c>
       <c r="AB308" s="4" t="s">
-        <v>335</v>
+        <v>334</v>
       </c>
       <c r="AC308" s="4" t="s">
         <v>153</v>
@@ -36720,16 +36717,16 @@
         <v>4431</v>
       </c>
       <c r="D309" s="4" t="s">
-        <v>224</v>
+        <v>223</v>
       </c>
       <c r="E309" s="4" t="s">
+        <v>335</v>
+      </c>
+      <c r="F309" s="4" t="s">
         <v>336</v>
       </c>
-      <c r="F309" s="4" t="s">
+      <c r="G309" s="4" t="s">
         <v>337</v>
-      </c>
-      <c r="G309" s="4" t="s">
-        <v>338</v>
       </c>
       <c r="H309" s="3">
         <v>631</v>
@@ -36835,16 +36832,16 @@
         <v>4431</v>
       </c>
       <c r="D310" s="4" t="s">
-        <v>224</v>
+        <v>223</v>
       </c>
       <c r="E310" s="4" t="s">
+        <v>335</v>
+      </c>
+      <c r="F310" s="4" t="s">
         <v>336</v>
       </c>
-      <c r="F310" s="4" t="s">
+      <c r="G310" s="4" t="s">
         <v>337</v>
-      </c>
-      <c r="G310" s="4" t="s">
-        <v>338</v>
       </c>
       <c r="H310" s="3">
         <v>631</v>
@@ -36950,16 +36947,16 @@
         <v>4431</v>
       </c>
       <c r="D311" s="4" t="s">
-        <v>224</v>
+        <v>223</v>
       </c>
       <c r="E311" s="4" t="s">
+        <v>338</v>
+      </c>
+      <c r="F311" s="4" t="s">
         <v>339</v>
       </c>
-      <c r="F311" s="4" t="s">
+      <c r="G311" s="4" t="s">
         <v>340</v>
-      </c>
-      <c r="G311" s="4" t="s">
-        <v>341</v>
       </c>
       <c r="H311" s="3">
         <v>673</v>
@@ -37065,16 +37062,16 @@
         <v>4431</v>
       </c>
       <c r="D312" s="4" t="s">
-        <v>224</v>
+        <v>223</v>
       </c>
       <c r="E312" s="4" t="s">
+        <v>338</v>
+      </c>
+      <c r="F312" s="4" t="s">
         <v>339</v>
       </c>
-      <c r="F312" s="4" t="s">
+      <c r="G312" s="4" t="s">
         <v>340</v>
-      </c>
-      <c r="G312" s="4" t="s">
-        <v>341</v>
       </c>
       <c r="H312" s="3">
         <v>673</v>
@@ -37180,16 +37177,16 @@
         <v>4431</v>
       </c>
       <c r="D313" s="4" t="s">
-        <v>224</v>
+        <v>223</v>
       </c>
       <c r="E313" s="4" t="s">
+        <v>341</v>
+      </c>
+      <c r="F313" s="4" t="s">
         <v>342</v>
       </c>
-      <c r="F313" s="4" t="s">
+      <c r="G313" s="4" t="s">
         <v>343</v>
-      </c>
-      <c r="G313" s="4" t="s">
-        <v>344</v>
       </c>
       <c r="H313" s="3">
         <v>674</v>
@@ -37295,16 +37292,16 @@
         <v>4431</v>
       </c>
       <c r="D314" s="4" t="s">
-        <v>224</v>
+        <v>223</v>
       </c>
       <c r="E314" s="4" t="s">
+        <v>341</v>
+      </c>
+      <c r="F314" s="4" t="s">
         <v>342</v>
       </c>
-      <c r="F314" s="4" t="s">
+      <c r="G314" s="4" t="s">
         <v>343</v>
-      </c>
-      <c r="G314" s="4" t="s">
-        <v>344</v>
       </c>
       <c r="H314" s="3">
         <v>674</v>
@@ -37410,16 +37407,16 @@
         <v>4431</v>
       </c>
       <c r="D315" s="4" t="s">
-        <v>224</v>
+        <v>223</v>
       </c>
       <c r="E315" s="4" t="s">
+        <v>344</v>
+      </c>
+      <c r="F315" s="4" t="s">
         <v>345</v>
       </c>
-      <c r="F315" s="4" t="s">
+      <c r="G315" s="4" t="s">
         <v>346</v>
-      </c>
-      <c r="G315" s="4" t="s">
-        <v>347</v>
       </c>
       <c r="H315" s="3">
         <v>683</v>
@@ -37525,16 +37522,16 @@
         <v>4431</v>
       </c>
       <c r="D316" s="4" t="s">
-        <v>224</v>
+        <v>223</v>
       </c>
       <c r="E316" s="4" t="s">
+        <v>347</v>
+      </c>
+      <c r="F316" s="4" t="s">
         <v>348</v>
       </c>
-      <c r="F316" s="4" t="s">
+      <c r="G316" s="4" t="s">
         <v>349</v>
-      </c>
-      <c r="G316" s="4" t="s">
-        <v>350</v>
       </c>
       <c r="H316" s="3">
         <v>687</v>
@@ -37640,16 +37637,16 @@
         <v>4431</v>
       </c>
       <c r="D317" s="4" t="s">
-        <v>224</v>
+        <v>223</v>
       </c>
       <c r="E317" s="4" t="s">
+        <v>347</v>
+      </c>
+      <c r="F317" s="4" t="s">
         <v>348</v>
       </c>
-      <c r="F317" s="4" t="s">
+      <c r="G317" s="4" t="s">
         <v>349</v>
-      </c>
-      <c r="G317" s="4" t="s">
-        <v>350</v>
       </c>
       <c r="H317" s="3">
         <v>687</v>
@@ -37755,16 +37752,16 @@
         <v>4431</v>
       </c>
       <c r="D318" s="4" t="s">
-        <v>224</v>
+        <v>223</v>
       </c>
       <c r="E318" s="4" t="s">
+        <v>350</v>
+      </c>
+      <c r="F318" s="4" t="s">
         <v>351</v>
       </c>
-      <c r="F318" s="4" t="s">
+      <c r="G318" s="4" t="s">
         <v>352</v>
-      </c>
-      <c r="G318" s="4" t="s">
-        <v>353</v>
       </c>
       <c r="H318" s="3">
         <v>688</v>
@@ -37870,16 +37867,16 @@
         <v>4431</v>
       </c>
       <c r="D319" s="4" t="s">
-        <v>224</v>
+        <v>223</v>
       </c>
       <c r="E319" s="4" t="s">
+        <v>350</v>
+      </c>
+      <c r="F319" s="4" t="s">
         <v>351</v>
       </c>
-      <c r="F319" s="4" t="s">
+      <c r="G319" s="4" t="s">
         <v>352</v>
-      </c>
-      <c r="G319" s="4" t="s">
-        <v>353</v>
       </c>
       <c r="H319" s="3">
         <v>688</v>
@@ -37985,16 +37982,16 @@
         <v>4431</v>
       </c>
       <c r="D320" s="4" t="s">
-        <v>224</v>
+        <v>223</v>
       </c>
       <c r="E320" s="4" t="s">
+        <v>350</v>
+      </c>
+      <c r="F320" s="4" t="s">
         <v>351</v>
       </c>
-      <c r="F320" s="4" t="s">
+      <c r="G320" s="4" t="s">
         <v>352</v>
-      </c>
-      <c r="G320" s="4" t="s">
-        <v>353</v>
       </c>
       <c r="H320" s="3">
         <v>688</v>
@@ -38057,7 +38054,7 @@
         <v>0</v>
       </c>
       <c r="AB320" s="4" t="s">
-        <v>354</v>
+        <v>353</v>
       </c>
       <c r="AC320" s="4" t="s">
         <v>153</v>
@@ -38104,16 +38101,16 @@
         <v>4431</v>
       </c>
       <c r="D321" s="4" t="s">
-        <v>224</v>
+        <v>223</v>
       </c>
       <c r="E321" s="4" t="s">
+        <v>354</v>
+      </c>
+      <c r="F321" s="4" t="s">
         <v>355</v>
       </c>
-      <c r="F321" s="4" t="s">
+      <c r="G321" s="4" t="s">
         <v>356</v>
-      </c>
-      <c r="G321" s="4" t="s">
-        <v>357</v>
       </c>
       <c r="H321" s="3">
         <v>719</v>
@@ -38219,16 +38216,16 @@
         <v>4431</v>
       </c>
       <c r="D322" s="4" t="s">
-        <v>224</v>
+        <v>223</v>
       </c>
       <c r="E322" s="4" t="s">
+        <v>354</v>
+      </c>
+      <c r="F322" s="4" t="s">
         <v>355</v>
       </c>
-      <c r="F322" s="4" t="s">
+      <c r="G322" s="4" t="s">
         <v>356</v>
-      </c>
-      <c r="G322" s="4" t="s">
-        <v>357</v>
       </c>
       <c r="H322" s="3">
         <v>719</v>
@@ -38334,16 +38331,16 @@
         <v>4431</v>
       </c>
       <c r="D323" s="4" t="s">
-        <v>224</v>
+        <v>223</v>
       </c>
       <c r="E323" s="4" t="s">
+        <v>357</v>
+      </c>
+      <c r="F323" s="4" t="s">
         <v>358</v>
       </c>
-      <c r="F323" s="4" t="s">
+      <c r="G323" s="4" t="s">
         <v>359</v>
-      </c>
-      <c r="G323" s="4" t="s">
-        <v>360</v>
       </c>
       <c r="H323" s="3">
         <v>722</v>
@@ -38449,16 +38446,16 @@
         <v>4431</v>
       </c>
       <c r="D324" s="4" t="s">
-        <v>224</v>
+        <v>223</v>
       </c>
       <c r="E324" s="4" t="s">
+        <v>357</v>
+      </c>
+      <c r="F324" s="4" t="s">
         <v>358</v>
       </c>
-      <c r="F324" s="4" t="s">
+      <c r="G324" s="4" t="s">
         <v>359</v>
-      </c>
-      <c r="G324" s="4" t="s">
-        <v>360</v>
       </c>
       <c r="H324" s="3">
         <v>722</v>
@@ -38564,16 +38561,16 @@
         <v>4431</v>
       </c>
       <c r="D325" s="4" t="s">
-        <v>224</v>
+        <v>223</v>
       </c>
       <c r="E325" s="4" t="s">
+        <v>360</v>
+      </c>
+      <c r="F325" s="4" t="s">
         <v>361</v>
       </c>
-      <c r="F325" s="4" t="s">
+      <c r="G325" s="4" t="s">
         <v>362</v>
-      </c>
-      <c r="G325" s="4" t="s">
-        <v>363</v>
       </c>
       <c r="H325" s="3">
         <v>932</v>
@@ -38679,16 +38676,16 @@
         <v>4431</v>
       </c>
       <c r="D326" s="4" t="s">
-        <v>224</v>
+        <v>223</v>
       </c>
       <c r="E326" s="4" t="s">
+        <v>360</v>
+      </c>
+      <c r="F326" s="4" t="s">
         <v>361</v>
       </c>
-      <c r="F326" s="4" t="s">
+      <c r="G326" s="4" t="s">
         <v>362</v>
-      </c>
-      <c r="G326" s="4" t="s">
-        <v>363</v>
       </c>
       <c r="H326" s="3">
         <v>932</v>
@@ -38794,16 +38791,16 @@
         <v>4431</v>
       </c>
       <c r="D327" s="4" t="s">
-        <v>224</v>
+        <v>223</v>
       </c>
       <c r="E327" s="4" t="s">
+        <v>363</v>
+      </c>
+      <c r="F327" s="4" t="s">
         <v>364</v>
       </c>
-      <c r="F327" s="4" t="s">
+      <c r="G327" s="4" t="s">
         <v>365</v>
-      </c>
-      <c r="G327" s="4" t="s">
-        <v>366</v>
       </c>
       <c r="H327" s="3">
         <v>934</v>
@@ -38909,16 +38906,16 @@
         <v>4431</v>
       </c>
       <c r="D328" s="4" t="s">
-        <v>224</v>
+        <v>223</v>
       </c>
       <c r="E328" s="4" t="s">
+        <v>363</v>
+      </c>
+      <c r="F328" s="4" t="s">
         <v>364</v>
       </c>
-      <c r="F328" s="4" t="s">
+      <c r="G328" s="4" t="s">
         <v>365</v>
-      </c>
-      <c r="G328" s="4" t="s">
-        <v>366</v>
       </c>
       <c r="H328" s="3">
         <v>934</v>
@@ -39024,16 +39021,16 @@
         <v>4431</v>
       </c>
       <c r="D329" s="4" t="s">
-        <v>224</v>
+        <v>223</v>
       </c>
       <c r="E329" s="4" t="s">
+        <v>366</v>
+      </c>
+      <c r="F329" s="4" t="s">
         <v>367</v>
       </c>
-      <c r="F329" s="4" t="s">
+      <c r="G329" s="4" t="s">
         <v>368</v>
-      </c>
-      <c r="G329" s="4" t="s">
-        <v>369</v>
       </c>
       <c r="H329" s="3">
         <v>331</v>
@@ -39139,16 +39136,16 @@
         <v>4431</v>
       </c>
       <c r="D330" s="4" t="s">
-        <v>224</v>
+        <v>223</v>
       </c>
       <c r="E330" s="4" t="s">
+        <v>366</v>
+      </c>
+      <c r="F330" s="4" t="s">
         <v>367</v>
       </c>
-      <c r="F330" s="4" t="s">
+      <c r="G330" s="4" t="s">
         <v>368</v>
-      </c>
-      <c r="G330" s="4" t="s">
-        <v>369</v>
       </c>
       <c r="H330" s="3">
         <v>331</v>
@@ -39254,16 +39251,16 @@
         <v>4431</v>
       </c>
       <c r="D331" s="4" t="s">
-        <v>224</v>
+        <v>223</v>
       </c>
       <c r="E331" s="4" t="s">
+        <v>366</v>
+      </c>
+      <c r="F331" s="4" t="s">
         <v>367</v>
       </c>
-      <c r="F331" s="4" t="s">
+      <c r="G331" s="4" t="s">
         <v>368</v>
-      </c>
-      <c r="G331" s="4" t="s">
-        <v>369</v>
       </c>
       <c r="H331" s="3">
         <v>331</v>
@@ -39326,7 +39323,7 @@
         <v>0</v>
       </c>
       <c r="AB331" s="4" t="s">
-        <v>370</v>
+        <v>369</v>
       </c>
       <c r="AC331" s="4" t="s">
         <v>153</v>
@@ -39373,16 +39370,16 @@
         <v>4431</v>
       </c>
       <c r="D332" s="4" t="s">
-        <v>224</v>
+        <v>223</v>
       </c>
       <c r="E332" s="4" t="s">
+        <v>370</v>
+      </c>
+      <c r="F332" s="4" t="s">
         <v>371</v>
       </c>
-      <c r="F332" s="4" t="s">
+      <c r="G332" s="4" t="s">
         <v>372</v>
-      </c>
-      <c r="G332" s="4" t="s">
-        <v>373</v>
       </c>
       <c r="H332" s="3">
         <v>1778</v>
@@ -39391,7 +39388,7 @@
         <v>2025</v>
       </c>
       <c r="J332" s="4" t="s">
-        <v>252</v>
+        <v>251</v>
       </c>
       <c r="K332" s="3">
         <v>0</v>
@@ -39488,16 +39485,16 @@
         <v>4431</v>
       </c>
       <c r="D333" s="4" t="s">
-        <v>224</v>
+        <v>223</v>
       </c>
       <c r="E333" s="4" t="s">
+        <v>370</v>
+      </c>
+      <c r="F333" s="4" t="s">
         <v>371</v>
       </c>
-      <c r="F333" s="4" t="s">
+      <c r="G333" s="4" t="s">
         <v>372</v>
-      </c>
-      <c r="G333" s="4" t="s">
-        <v>373</v>
       </c>
       <c r="H333" s="3">
         <v>1778</v>
@@ -39506,7 +39503,7 @@
         <v>2025</v>
       </c>
       <c r="J333" s="4" t="s">
-        <v>252</v>
+        <v>251</v>
       </c>
       <c r="K333" s="3">
         <v>0</v>
@@ -39560,7 +39557,7 @@
         <v>0</v>
       </c>
       <c r="AB333" s="4" t="s">
-        <v>374</v>
+        <v>373</v>
       </c>
       <c r="AC333" s="4" t="s">
         <v>153</v>
@@ -39607,16 +39604,16 @@
         <v>4431</v>
       </c>
       <c r="D334" s="4" t="s">
-        <v>224</v>
+        <v>223</v>
       </c>
       <c r="E334" s="4" t="s">
+        <v>374</v>
+      </c>
+      <c r="F334" s="4" t="s">
         <v>375</v>
       </c>
-      <c r="F334" s="4" t="s">
+      <c r="G334" s="4" t="s">
         <v>376</v>
-      </c>
-      <c r="G334" s="4" t="s">
-        <v>377</v>
       </c>
       <c r="H334" s="3">
         <v>565</v>
@@ -39722,16 +39719,16 @@
         <v>4431</v>
       </c>
       <c r="D335" s="4" t="s">
-        <v>224</v>
+        <v>223</v>
       </c>
       <c r="E335" s="4" t="s">
+        <v>374</v>
+      </c>
+      <c r="F335" s="4" t="s">
         <v>375</v>
       </c>
-      <c r="F335" s="4" t="s">
+      <c r="G335" s="4" t="s">
         <v>376</v>
-      </c>
-      <c r="G335" s="4" t="s">
-        <v>377</v>
       </c>
       <c r="H335" s="3">
         <v>565</v>
@@ -39794,7 +39791,7 @@
         <v>0</v>
       </c>
       <c r="AB335" s="4" t="s">
-        <v>378</v>
+        <v>377</v>
       </c>
       <c r="AC335" s="4" t="s">
         <v>153</v>
@@ -39841,16 +39838,16 @@
         <v>4431</v>
       </c>
       <c r="D336" s="4" t="s">
-        <v>224</v>
+        <v>223</v>
       </c>
       <c r="E336" s="4" t="s">
+        <v>378</v>
+      </c>
+      <c r="F336" s="4" t="s">
         <v>379</v>
       </c>
-      <c r="F336" s="4" t="s">
+      <c r="G336" s="4" t="s">
         <v>380</v>
-      </c>
-      <c r="G336" s="4" t="s">
-        <v>381</v>
       </c>
       <c r="H336" s="3">
         <v>570</v>
@@ -39956,16 +39953,16 @@
         <v>4431</v>
       </c>
       <c r="D337" s="4" t="s">
-        <v>224</v>
+        <v>223</v>
       </c>
       <c r="E337" s="4" t="s">
+        <v>378</v>
+      </c>
+      <c r="F337" s="4" t="s">
         <v>379</v>
       </c>
-      <c r="F337" s="4" t="s">
+      <c r="G337" s="4" t="s">
         <v>380</v>
-      </c>
-      <c r="G337" s="4" t="s">
-        <v>381</v>
       </c>
       <c r="H337" s="3">
         <v>570</v>
@@ -40071,16 +40068,16 @@
         <v>4431</v>
       </c>
       <c r="D338" s="4" t="s">
-        <v>224</v>
+        <v>223</v>
       </c>
       <c r="E338" s="4" t="s">
+        <v>378</v>
+      </c>
+      <c r="F338" s="4" t="s">
         <v>379</v>
       </c>
-      <c r="F338" s="4" t="s">
+      <c r="G338" s="4" t="s">
         <v>380</v>
-      </c>
-      <c r="G338" s="4" t="s">
-        <v>381</v>
       </c>
       <c r="H338" s="3">
         <v>570</v>
@@ -40143,7 +40140,7 @@
         <v>0</v>
       </c>
       <c r="AB338" s="4" t="s">
-        <v>382</v>
+        <v>381</v>
       </c>
       <c r="AC338" s="4" t="s">
         <v>153</v>
@@ -40190,16 +40187,16 @@
         <v>4431</v>
       </c>
       <c r="D339" s="4" t="s">
-        <v>224</v>
+        <v>223</v>
       </c>
       <c r="E339" s="4" t="s">
+        <v>378</v>
+      </c>
+      <c r="F339" s="4" t="s">
         <v>379</v>
       </c>
-      <c r="F339" s="4" t="s">
+      <c r="G339" s="4" t="s">
         <v>380</v>
-      </c>
-      <c r="G339" s="4" t="s">
-        <v>381</v>
       </c>
       <c r="H339" s="3">
         <v>1779</v>
@@ -40208,7 +40205,7 @@
         <v>2025</v>
       </c>
       <c r="J339" s="4" t="s">
-        <v>252</v>
+        <v>251</v>
       </c>
       <c r="K339" s="3">
         <v>0</v>
@@ -40305,16 +40302,16 @@
         <v>4431</v>
       </c>
       <c r="D340" s="4" t="s">
-        <v>224</v>
+        <v>223</v>
       </c>
       <c r="E340" s="4" t="s">
+        <v>378</v>
+      </c>
+      <c r="F340" s="4" t="s">
         <v>379</v>
       </c>
-      <c r="F340" s="4" t="s">
+      <c r="G340" s="4" t="s">
         <v>380</v>
-      </c>
-      <c r="G340" s="4" t="s">
-        <v>381</v>
       </c>
       <c r="H340" s="3">
         <v>1779</v>
@@ -40323,7 +40320,7 @@
         <v>2025</v>
       </c>
       <c r="J340" s="4" t="s">
-        <v>252</v>
+        <v>251</v>
       </c>
       <c r="K340" s="3">
         <v>0</v>
@@ -40377,7 +40374,7 @@
         <v>0</v>
       </c>
       <c r="AB340" s="4" t="s">
-        <v>382</v>
+        <v>381</v>
       </c>
       <c r="AC340" s="4" t="s">
         <v>153</v>
@@ -40424,16 +40421,16 @@
         <v>4431</v>
       </c>
       <c r="D341" s="4" t="s">
-        <v>224</v>
+        <v>223</v>
       </c>
       <c r="E341" s="4" t="s">
+        <v>382</v>
+      </c>
+      <c r="F341" s="4" t="s">
         <v>383</v>
       </c>
-      <c r="F341" s="4" t="s">
+      <c r="G341" s="4" t="s">
         <v>384</v>
-      </c>
-      <c r="G341" s="4" t="s">
-        <v>385</v>
       </c>
       <c r="H341" s="3">
         <v>573</v>
@@ -40539,16 +40536,16 @@
         <v>4431</v>
       </c>
       <c r="D342" s="4" t="s">
-        <v>224</v>
+        <v>223</v>
       </c>
       <c r="E342" s="4" t="s">
+        <v>382</v>
+      </c>
+      <c r="F342" s="4" t="s">
         <v>383</v>
       </c>
-      <c r="F342" s="4" t="s">
+      <c r="G342" s="4" t="s">
         <v>384</v>
-      </c>
-      <c r="G342" s="4" t="s">
-        <v>385</v>
       </c>
       <c r="H342" s="3">
         <v>573</v>
@@ -40654,16 +40651,16 @@
         <v>4431</v>
       </c>
       <c r="D343" s="4" t="s">
-        <v>224</v>
+        <v>223</v>
       </c>
       <c r="E343" s="4" t="s">
+        <v>382</v>
+      </c>
+      <c r="F343" s="4" t="s">
         <v>383</v>
       </c>
-      <c r="F343" s="4" t="s">
+      <c r="G343" s="4" t="s">
         <v>384</v>
-      </c>
-      <c r="G343" s="4" t="s">
-        <v>385</v>
       </c>
       <c r="H343" s="3">
         <v>573</v>
@@ -40726,7 +40723,7 @@
         <v>0</v>
       </c>
       <c r="AB343" s="4" t="s">
-        <v>386</v>
+        <v>385</v>
       </c>
       <c r="AC343" s="4" t="s">
         <v>153</v>
@@ -40773,16 +40770,16 @@
         <v>4431</v>
       </c>
       <c r="D344" s="4" t="s">
-        <v>224</v>
+        <v>223</v>
       </c>
       <c r="E344" s="4" t="s">
+        <v>386</v>
+      </c>
+      <c r="F344" s="4" t="s">
         <v>387</v>
       </c>
-      <c r="F344" s="4" t="s">
+      <c r="G344" s="4" t="s">
         <v>388</v>
-      </c>
-      <c r="G344" s="4" t="s">
-        <v>389</v>
       </c>
       <c r="H344" s="3">
         <v>577</v>
@@ -40888,16 +40885,16 @@
         <v>4431</v>
       </c>
       <c r="D345" s="4" t="s">
-        <v>224</v>
+        <v>223</v>
       </c>
       <c r="E345" s="4" t="s">
+        <v>386</v>
+      </c>
+      <c r="F345" s="4" t="s">
         <v>387</v>
       </c>
-      <c r="F345" s="4" t="s">
+      <c r="G345" s="4" t="s">
         <v>388</v>
-      </c>
-      <c r="G345" s="4" t="s">
-        <v>389</v>
       </c>
       <c r="H345" s="3">
         <v>577</v>
@@ -40960,7 +40957,7 @@
         <v>0</v>
       </c>
       <c r="AB345" s="4" t="s">
-        <v>390</v>
+        <v>389</v>
       </c>
       <c r="AC345" s="4" t="s">
         <v>153</v>
@@ -41007,16 +41004,16 @@
         <v>4431</v>
       </c>
       <c r="D346" s="4" t="s">
-        <v>224</v>
+        <v>223</v>
       </c>
       <c r="E346" s="4" t="s">
+        <v>390</v>
+      </c>
+      <c r="F346" s="4" t="s">
         <v>391</v>
       </c>
-      <c r="F346" s="4" t="s">
+      <c r="G346" s="4" t="s">
         <v>392</v>
-      </c>
-      <c r="G346" s="4" t="s">
-        <v>393</v>
       </c>
       <c r="H346" s="3">
         <v>582</v>
@@ -41122,16 +41119,16 @@
         <v>4431</v>
       </c>
       <c r="D347" s="4" t="s">
-        <v>224</v>
+        <v>223</v>
       </c>
       <c r="E347" s="4" t="s">
+        <v>390</v>
+      </c>
+      <c r="F347" s="4" t="s">
         <v>391</v>
       </c>
-      <c r="F347" s="4" t="s">
+      <c r="G347" s="4" t="s">
         <v>392</v>
-      </c>
-      <c r="G347" s="4" t="s">
-        <v>393</v>
       </c>
       <c r="H347" s="3">
         <v>582</v>
@@ -41194,7 +41191,7 @@
         <v>0</v>
       </c>
       <c r="AB347" s="4" t="s">
-        <v>394</v>
+        <v>393</v>
       </c>
       <c r="AC347" s="4" t="s">
         <v>153</v>
@@ -41241,16 +41238,16 @@
         <v>4431</v>
       </c>
       <c r="D348" s="4" t="s">
-        <v>224</v>
+        <v>223</v>
       </c>
       <c r="E348" s="4" t="s">
+        <v>394</v>
+      </c>
+      <c r="F348" s="4" t="s">
         <v>395</v>
       </c>
-      <c r="F348" s="4" t="s">
+      <c r="G348" s="4" t="s">
         <v>396</v>
-      </c>
-      <c r="G348" s="4" t="s">
-        <v>397</v>
       </c>
       <c r="H348" s="3">
         <v>623</v>
@@ -41356,16 +41353,16 @@
         <v>4431</v>
       </c>
       <c r="D349" s="4" t="s">
-        <v>224</v>
+        <v>223</v>
       </c>
       <c r="E349" s="4" t="s">
+        <v>394</v>
+      </c>
+      <c r="F349" s="4" t="s">
         <v>395</v>
       </c>
-      <c r="F349" s="4" t="s">
+      <c r="G349" s="4" t="s">
         <v>396</v>
-      </c>
-      <c r="G349" s="4" t="s">
-        <v>397</v>
       </c>
       <c r="H349" s="3">
         <v>623</v>
@@ -41428,7 +41425,7 @@
         <v>0</v>
       </c>
       <c r="AB349" s="4" t="s">
-        <v>398</v>
+        <v>397</v>
       </c>
       <c r="AC349" s="4" t="s">
         <v>153</v>
@@ -41475,7 +41472,7 @@
         <v>4433</v>
       </c>
       <c r="D350" s="4" t="s">
-        <v>399</v>
+        <v>398</v>
       </c>
       <c r="E350" s="4" t="s">
         <v>128</v>
@@ -41588,7 +41585,7 @@
         <v>4433</v>
       </c>
       <c r="D351" s="4" t="s">
-        <v>399</v>
+        <v>398</v>
       </c>
       <c r="E351" s="4" t="s">
         <v>100</v>
@@ -41606,7 +41603,7 @@
         <v>2025</v>
       </c>
       <c r="J351" s="4" t="s">
-        <v>400</v>
+        <v>399</v>
       </c>
       <c r="K351" s="3">
         <v>9.443968e6</v>
@@ -41703,7 +41700,7 @@
         <v>4433</v>
       </c>
       <c r="D352" s="4" t="s">
-        <v>399</v>
+        <v>398</v>
       </c>
       <c r="E352" s="4" t="s">
         <v>100</v>
@@ -41721,7 +41718,7 @@
         <v>2025</v>
       </c>
       <c r="J352" s="4" t="s">
-        <v>400</v>
+        <v>399</v>
       </c>
       <c r="K352" s="3">
         <v>9.443968e6</v>
@@ -41818,7 +41815,7 @@
         <v>4433</v>
       </c>
       <c r="D353" s="4" t="s">
-        <v>399</v>
+        <v>398</v>
       </c>
       <c r="E353" s="4" t="s">
         <v>100</v>
@@ -41836,7 +41833,7 @@
         <v>2025</v>
       </c>
       <c r="J353" s="4" t="s">
-        <v>400</v>
+        <v>399</v>
       </c>
       <c r="K353" s="3">
         <v>9.443968e6</v>
@@ -41937,7 +41934,7 @@
         <v>4433</v>
       </c>
       <c r="D354" s="4" t="s">
-        <v>399</v>
+        <v>398</v>
       </c>
       <c r="E354" s="4" t="s">
         <v>100</v>
@@ -41955,7 +41952,7 @@
         <v>2025</v>
       </c>
       <c r="J354" s="4" t="s">
-        <v>400</v>
+        <v>399</v>
       </c>
       <c r="K354" s="3">
         <v>9.443968e6</v>
@@ -42056,7 +42053,7 @@
         <v>4433</v>
       </c>
       <c r="D355" s="4" t="s">
-        <v>399</v>
+        <v>398</v>
       </c>
       <c r="E355" s="4" t="s">
         <v>100</v>
@@ -42169,7 +42166,7 @@
         <v>4433</v>
       </c>
       <c r="D356" s="4" t="s">
-        <v>399</v>
+        <v>398</v>
       </c>
       <c r="E356" s="4" t="s">
         <v>100</v>
@@ -42282,7 +42279,7 @@
         <v>4433</v>
       </c>
       <c r="D357" s="4" t="s">
-        <v>399</v>
+        <v>398</v>
       </c>
       <c r="E357" s="4" t="s">
         <v>100</v>
@@ -42355,7 +42352,7 @@
         <v>140</v>
       </c>
       <c r="AC357" s="4" t="s">
-        <v>401</v>
+        <v>400</v>
       </c>
       <c r="AD357" s="3">
         <v>1</v>
@@ -42399,7 +42396,7 @@
         <v>4433</v>
       </c>
       <c r="D358" s="4" t="s">
-        <v>399</v>
+        <v>398</v>
       </c>
       <c r="E358" s="4" t="s">
         <v>100</v>
@@ -42472,7 +42469,7 @@
         <v>140</v>
       </c>
       <c r="AC358" s="4" t="s">
-        <v>401</v>
+        <v>400</v>
       </c>
       <c r="AD358" s="3">
         <v>2</v>
@@ -42516,7 +42513,7 @@
         <v>4433</v>
       </c>
       <c r="D359" s="4" t="s">
-        <v>399</v>
+        <v>398</v>
       </c>
       <c r="E359" s="4" t="s">
         <v>100</v>
@@ -42534,7 +42531,7 @@
         <v>2025</v>
       </c>
       <c r="J359" s="4" t="s">
-        <v>252</v>
+        <v>251</v>
       </c>
       <c r="K359" s="3">
         <v>9.26316e6</v>
@@ -42631,7 +42628,7 @@
         <v>4433</v>
       </c>
       <c r="D360" s="4" t="s">
-        <v>399</v>
+        <v>398</v>
       </c>
       <c r="E360" s="4" t="s">
         <v>100</v>
@@ -42649,7 +42646,7 @@
         <v>2025</v>
       </c>
       <c r="J360" s="4" t="s">
-        <v>252</v>
+        <v>251</v>
       </c>
       <c r="K360" s="3">
         <v>9.26316e6</v>
@@ -42750,7 +42747,7 @@
         <v>4433</v>
       </c>
       <c r="D361" s="4" t="s">
-        <v>399</v>
+        <v>398</v>
       </c>
       <c r="E361" s="4" t="s">
         <v>100</v>
@@ -42768,7 +42765,7 @@
         <v>2024</v>
       </c>
       <c r="J361" s="4" t="s">
-        <v>402</v>
+        <v>401</v>
       </c>
       <c r="K361" s="3">
         <v>9.443968e6</v>
@@ -42865,13 +42862,13 @@
         <v>4433</v>
       </c>
       <c r="D362" s="4" t="s">
-        <v>399</v>
+        <v>398</v>
       </c>
       <c r="E362" s="4" t="s">
+        <v>402</v>
+      </c>
+      <c r="F362" s="4" t="s">
         <v>403</v>
-      </c>
-      <c r="F362" s="4" t="s">
-        <v>404</v>
       </c>
       <c r="G362" s="4" t="s">
         <v>106</v>
@@ -42978,13 +42975,13 @@
         <v>4433</v>
       </c>
       <c r="D363" s="4" t="s">
-        <v>399</v>
+        <v>398</v>
       </c>
       <c r="E363" s="4" t="s">
+        <v>402</v>
+      </c>
+      <c r="F363" s="4" t="s">
         <v>403</v>
-      </c>
-      <c r="F363" s="4" t="s">
-        <v>404</v>
       </c>
       <c r="G363" s="4" t="s">
         <v>106</v>
@@ -43091,13 +43088,13 @@
         <v>4433</v>
       </c>
       <c r="D364" s="4" t="s">
-        <v>399</v>
+        <v>398</v>
       </c>
       <c r="E364" s="4" t="s">
+        <v>402</v>
+      </c>
+      <c r="F364" s="4" t="s">
         <v>403</v>
-      </c>
-      <c r="F364" s="4" t="s">
-        <v>404</v>
       </c>
       <c r="G364" s="4" t="s">
         <v>106</v>
@@ -43161,10 +43158,10 @@
         <v>0</v>
       </c>
       <c r="AB364" s="4" t="s">
-        <v>405</v>
+        <v>404</v>
       </c>
       <c r="AC364" s="4" t="s">
-        <v>401</v>
+        <v>400</v>
       </c>
       <c r="AD364" s="3">
         <v>1</v>
@@ -43208,7 +43205,7 @@
         <v>4433</v>
       </c>
       <c r="D365" s="4" t="s">
-        <v>399</v>
+        <v>398</v>
       </c>
       <c r="E365" s="4" t="s">
         <v>173</v>
@@ -43323,7 +43320,7 @@
         <v>4433</v>
       </c>
       <c r="D366" s="4" t="s">
-        <v>399</v>
+        <v>398</v>
       </c>
       <c r="E366" s="4" t="s">
         <v>173</v>
@@ -43442,7 +43439,7 @@
         <v>4433</v>
       </c>
       <c r="D367" s="4" t="s">
-        <v>399</v>
+        <v>398</v>
       </c>
       <c r="E367" s="4" t="s">
         <v>173</v>
@@ -43561,7 +43558,7 @@
         <v>4433</v>
       </c>
       <c r="D368" s="4" t="s">
-        <v>399</v>
+        <v>398</v>
       </c>
       <c r="E368" s="4" t="s">
         <v>173</v>
@@ -43674,7 +43671,7 @@
         <v>4433</v>
       </c>
       <c r="D369" s="4" t="s">
-        <v>399</v>
+        <v>398</v>
       </c>
       <c r="E369" s="4" t="s">
         <v>173</v>
@@ -43747,7 +43744,7 @@
         <v>47</v>
       </c>
       <c r="AC369" s="4" t="s">
-        <v>401</v>
+        <v>400</v>
       </c>
       <c r="AD369" s="3">
         <v>5</v>
@@ -43791,7 +43788,7 @@
         <v>4433</v>
       </c>
       <c r="D370" s="4" t="s">
-        <v>399</v>
+        <v>398</v>
       </c>
       <c r="E370" s="4" t="s">
         <v>173</v>
@@ -43864,7 +43861,7 @@
         <v>47</v>
       </c>
       <c r="AC370" s="4" t="s">
-        <v>401</v>
+        <v>400</v>
       </c>
       <c r="AD370" s="3">
         <v>8</v>
@@ -43908,7 +43905,7 @@
         <v>4433</v>
       </c>
       <c r="D371" s="4" t="s">
-        <v>399</v>
+        <v>398</v>
       </c>
       <c r="E371" s="4" t="s">
         <v>173</v>
@@ -44021,7 +44018,7 @@
         <v>4433</v>
       </c>
       <c r="D372" s="4" t="s">
-        <v>399</v>
+        <v>398</v>
       </c>
       <c r="E372" s="4" t="s">
         <v>173</v>
@@ -44134,7 +44131,7 @@
         <v>4433</v>
       </c>
       <c r="D373" s="4" t="s">
-        <v>399</v>
+        <v>398</v>
       </c>
       <c r="E373" s="4" t="s">
         <v>173</v>
@@ -44207,7 +44204,7 @@
         <v>47</v>
       </c>
       <c r="AC373" s="4" t="s">
-        <v>401</v>
+        <v>400</v>
       </c>
       <c r="AD373" s="3">
         <v>1</v>
@@ -44251,7 +44248,7 @@
         <v>4433</v>
       </c>
       <c r="D374" s="4" t="s">
-        <v>399</v>
+        <v>398</v>
       </c>
       <c r="E374" s="4" t="s">
         <v>173</v>
@@ -44366,7 +44363,7 @@
         <v>4433</v>
       </c>
       <c r="D375" s="4" t="s">
-        <v>399</v>
+        <v>398</v>
       </c>
       <c r="E375" s="4" t="s">
         <v>173</v>
@@ -44485,7 +44482,7 @@
         <v>4433</v>
       </c>
       <c r="D376" s="4" t="s">
-        <v>399</v>
+        <v>398</v>
       </c>
       <c r="E376" s="4" t="s">
         <v>173</v>
@@ -44604,7 +44601,7 @@
         <v>4433</v>
       </c>
       <c r="D377" s="4" t="s">
-        <v>399</v>
+        <v>398</v>
       </c>
       <c r="E377" s="4" t="s">
         <v>173</v>
@@ -44622,7 +44619,7 @@
         <v>2024</v>
       </c>
       <c r="J377" s="4" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="K377" s="3">
         <v>9.287509e6</v>
@@ -44719,7 +44716,7 @@
         <v>4433</v>
       </c>
       <c r="D378" s="4" t="s">
-        <v>399</v>
+        <v>398</v>
       </c>
       <c r="E378" s="4" t="s">
         <v>173</v>
@@ -44737,7 +44734,7 @@
         <v>2024</v>
       </c>
       <c r="J378" s="4" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="K378" s="3">
         <v>9.287509e6</v>
@@ -44838,7 +44835,7 @@
         <v>4433</v>
       </c>
       <c r="D379" s="4" t="s">
-        <v>399</v>
+        <v>398</v>
       </c>
       <c r="E379" s="4" t="s">
         <v>173</v>
@@ -44856,7 +44853,7 @@
         <v>2024</v>
       </c>
       <c r="J379" s="4" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="K379" s="3">
         <v>9.287509e6</v>
@@ -44957,7 +44954,7 @@
         <v>4433</v>
       </c>
       <c r="D380" s="4" t="s">
-        <v>399</v>
+        <v>398</v>
       </c>
       <c r="E380" s="4" t="s">
         <v>173</v>
@@ -44975,7 +44972,7 @@
         <v>2024</v>
       </c>
       <c r="J380" s="4" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="K380" s="3">
         <v>9.287509e6</v>
@@ -45076,7 +45073,7 @@
         <v>4433</v>
       </c>
       <c r="D381" s="4" t="s">
-        <v>399</v>
+        <v>398</v>
       </c>
       <c r="E381" s="4" t="s">
         <v>173</v>
@@ -45191,7 +45188,7 @@
         <v>4433</v>
       </c>
       <c r="D382" s="4" t="s">
-        <v>399</v>
+        <v>398</v>
       </c>
       <c r="E382" s="4" t="s">
         <v>173</v>
@@ -45310,7 +45307,7 @@
         <v>4433</v>
       </c>
       <c r="D383" s="4" t="s">
-        <v>399</v>
+        <v>398</v>
       </c>
       <c r="E383" s="4" t="s">
         <v>173</v>
@@ -45429,7 +45426,7 @@
         <v>4433</v>
       </c>
       <c r="D384" s="4" t="s">
-        <v>399</v>
+        <v>398</v>
       </c>
       <c r="E384" s="4" t="s">
         <v>173</v>
@@ -45486,7 +45483,7 @@
         <v>46311</v>
       </c>
       <c r="W384" s="4" t="s">
-        <v>177</v>
+        <v>135</v>
       </c>
       <c r="X384" s="5">
         <v>165.76</v>
@@ -45548,7 +45545,7 @@
         <v>4433</v>
       </c>
       <c r="D385" s="4" t="s">
-        <v>399</v>
+        <v>398</v>
       </c>
       <c r="E385" s="4" t="s">
         <v>173</v>
@@ -45661,7 +45658,7 @@
         <v>4433</v>
       </c>
       <c r="D386" s="4" t="s">
-        <v>399</v>
+        <v>398</v>
       </c>
       <c r="E386" s="4" t="s">
         <v>173</v>
@@ -45734,7 +45731,7 @@
         <v>47</v>
       </c>
       <c r="AC386" s="4" t="s">
-        <v>401</v>
+        <v>400</v>
       </c>
       <c r="AD386" s="3">
         <v>1</v>
@@ -45778,7 +45775,7 @@
         <v>4433</v>
       </c>
       <c r="D387" s="4" t="s">
-        <v>399</v>
+        <v>398</v>
       </c>
       <c r="E387" s="4" t="s">
         <v>173</v>
@@ -45851,7 +45848,7 @@
         <v>47</v>
       </c>
       <c r="AC387" s="4" t="s">
-        <v>401</v>
+        <v>400</v>
       </c>
       <c r="AD387" s="3">
         <v>1</v>
@@ -45895,7 +45892,7 @@
         <v>4433</v>
       </c>
       <c r="D388" s="4" t="s">
-        <v>399</v>
+        <v>398</v>
       </c>
       <c r="E388" s="4" t="s">
         <v>173</v>
@@ -46008,7 +46005,7 @@
         <v>4433</v>
       </c>
       <c r="D389" s="4" t="s">
-        <v>399</v>
+        <v>398</v>
       </c>
       <c r="E389" s="4" t="s">
         <v>173</v>
@@ -46081,7 +46078,7 @@
         <v>47</v>
       </c>
       <c r="AC389" s="4" t="s">
-        <v>406</v>
+        <v>405</v>
       </c>
       <c r="AD389" s="3">
         <v>8</v>
@@ -46125,7 +46122,7 @@
         <v>4433</v>
       </c>
       <c r="D390" s="4" t="s">
-        <v>399</v>
+        <v>398</v>
       </c>
       <c r="E390" s="4" t="s">
         <v>173</v>
@@ -46198,7 +46195,7 @@
         <v>47</v>
       </c>
       <c r="AC390" s="4" t="s">
-        <v>406</v>
+        <v>405</v>
       </c>
       <c r="AD390" s="3">
         <v>8</v>
@@ -46242,7 +46239,7 @@
         <v>4433</v>
       </c>
       <c r="D391" s="4" t="s">
-        <v>399</v>
+        <v>398</v>
       </c>
       <c r="E391" s="4" t="s">
         <v>173</v>
@@ -46315,7 +46312,7 @@
         <v>47</v>
       </c>
       <c r="AC391" s="4" t="s">
-        <v>406</v>
+        <v>405</v>
       </c>
       <c r="AD391" s="3">
         <v>8</v>
@@ -46359,7 +46356,7 @@
         <v>4433</v>
       </c>
       <c r="D392" s="4" t="s">
-        <v>399</v>
+        <v>398</v>
       </c>
       <c r="E392" s="4" t="s">
         <v>173</v>
@@ -46432,7 +46429,7 @@
         <v>47</v>
       </c>
       <c r="AC392" s="4" t="s">
-        <v>406</v>
+        <v>405</v>
       </c>
       <c r="AD392" s="3">
         <v>9</v>
@@ -46476,7 +46473,7 @@
         <v>4433</v>
       </c>
       <c r="D393" s="4" t="s">
-        <v>399</v>
+        <v>398</v>
       </c>
       <c r="E393" s="4" t="s">
         <v>173</v>
@@ -46549,7 +46546,7 @@
         <v>47</v>
       </c>
       <c r="AC393" s="4" t="s">
-        <v>406</v>
+        <v>405</v>
       </c>
       <c r="AD393" s="3">
         <v>9</v>
@@ -46593,7 +46590,7 @@
         <v>4433</v>
       </c>
       <c r="D394" s="4" t="s">
-        <v>399</v>
+        <v>398</v>
       </c>
       <c r="E394" s="4" t="s">
         <v>173</v>
@@ -46648,7 +46645,7 @@
         <v>46311</v>
       </c>
       <c r="W394" s="4" t="s">
-        <v>177</v>
+        <v>135</v>
       </c>
       <c r="X394" s="5">
         <v>2133.67</v>
@@ -46666,7 +46663,7 @@
         <v>47</v>
       </c>
       <c r="AC394" s="4" t="s">
-        <v>406</v>
+        <v>405</v>
       </c>
       <c r="AD394" s="3">
         <v>10</v>
@@ -46710,7 +46707,7 @@
         <v>4433</v>
       </c>
       <c r="D395" s="4" t="s">
-        <v>399</v>
+        <v>398</v>
       </c>
       <c r="E395" s="4" t="s">
         <v>173</v>
@@ -46823,7 +46820,7 @@
         <v>4433</v>
       </c>
       <c r="D396" s="4" t="s">
-        <v>399</v>
+        <v>398</v>
       </c>
       <c r="E396" s="4" t="s">
         <v>173</v>
@@ -46896,7 +46893,7 @@
         <v>47</v>
       </c>
       <c r="AC396" s="4" t="s">
-        <v>407</v>
+        <v>406</v>
       </c>
       <c r="AD396" s="3">
         <v>9</v>
@@ -46940,7 +46937,7 @@
         <v>4433</v>
       </c>
       <c r="D397" s="4" t="s">
-        <v>399</v>
+        <v>398</v>
       </c>
       <c r="E397" s="4" t="s">
         <v>173</v>
@@ -46958,7 +46955,7 @@
         <v>2025</v>
       </c>
       <c r="J397" s="4" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="K397" s="3">
         <v>9.287509e6</v>
@@ -47055,7 +47052,7 @@
         <v>4433</v>
       </c>
       <c r="D398" s="4" t="s">
-        <v>399</v>
+        <v>398</v>
       </c>
       <c r="E398" s="4" t="s">
         <v>173</v>
@@ -47073,7 +47070,7 @@
         <v>2025</v>
       </c>
       <c r="J398" s="4" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="K398" s="3">
         <v>9.287509e6</v>
@@ -47174,7 +47171,7 @@
         <v>4433</v>
       </c>
       <c r="D399" s="4" t="s">
-        <v>399</v>
+        <v>398</v>
       </c>
       <c r="E399" s="4" t="s">
         <v>173</v>
@@ -47289,7 +47286,7 @@
         <v>4433</v>
       </c>
       <c r="D400" s="4" t="s">
-        <v>399</v>
+        <v>398</v>
       </c>
       <c r="E400" s="4" t="s">
         <v>173</v>
@@ -47408,7 +47405,7 @@
         <v>4433</v>
       </c>
       <c r="D401" s="4" t="s">
-        <v>399</v>
+        <v>398</v>
       </c>
       <c r="E401" s="4" t="s">
         <v>173</v>
@@ -47523,7 +47520,7 @@
         <v>4433</v>
       </c>
       <c r="D402" s="4" t="s">
-        <v>399</v>
+        <v>398</v>
       </c>
       <c r="E402" s="4" t="s">
         <v>173</v>
@@ -47541,7 +47538,7 @@
         <v>2024</v>
       </c>
       <c r="J402" s="4" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="K402" s="3">
         <v>9.287509e6</v>
@@ -47638,7 +47635,7 @@
         <v>4433</v>
       </c>
       <c r="D403" s="4" t="s">
-        <v>399</v>
+        <v>398</v>
       </c>
       <c r="E403" s="4" t="s">
         <v>173</v>
@@ -47656,7 +47653,7 @@
         <v>2024</v>
       </c>
       <c r="J403" s="4" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="K403" s="3">
         <v>9.287509e6</v>
@@ -47757,7 +47754,7 @@
         <v>4433</v>
       </c>
       <c r="D404" s="4" t="s">
-        <v>399</v>
+        <v>398</v>
       </c>
       <c r="E404" s="4" t="s">
         <v>173</v>
@@ -47775,7 +47772,7 @@
         <v>2024</v>
       </c>
       <c r="J404" s="4" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="K404" s="3">
         <v>9.287509e6</v>
@@ -47876,7 +47873,7 @@
         <v>4433</v>
       </c>
       <c r="D405" s="4" t="s">
-        <v>399</v>
+        <v>398</v>
       </c>
       <c r="E405" s="4" t="s">
         <v>173</v>
@@ -47894,7 +47891,7 @@
         <v>2024</v>
       </c>
       <c r="J405" s="4" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="K405" s="3">
         <v>9.287509e6</v>
@@ -47995,7 +47992,7 @@
         <v>4433</v>
       </c>
       <c r="D406" s="4" t="s">
-        <v>399</v>
+        <v>398</v>
       </c>
       <c r="E406" s="4" t="s">
         <v>173</v>
@@ -48013,7 +48010,7 @@
         <v>2025</v>
       </c>
       <c r="J406" s="4" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="K406" s="3">
         <v>9.479358e6</v>
@@ -48108,7 +48105,7 @@
         <v>4433</v>
       </c>
       <c r="D407" s="4" t="s">
-        <v>399</v>
+        <v>398</v>
       </c>
       <c r="E407" s="4" t="s">
         <v>173</v>
@@ -48126,7 +48123,7 @@
         <v>2025</v>
       </c>
       <c r="J407" s="4" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="K407" s="3">
         <v>9.479358e6</v>
@@ -48225,7 +48222,7 @@
         <v>4433</v>
       </c>
       <c r="D408" s="4" t="s">
-        <v>399</v>
+        <v>398</v>
       </c>
       <c r="E408" s="4" t="s">
         <v>173</v>
@@ -48338,7 +48335,7 @@
         <v>4433</v>
       </c>
       <c r="D409" s="4" t="s">
-        <v>399</v>
+        <v>398</v>
       </c>
       <c r="E409" s="4" t="s">
         <v>173</v>
@@ -48455,7 +48452,7 @@
         <v>4433</v>
       </c>
       <c r="D410" s="4" t="s">
-        <v>399</v>
+        <v>398</v>
       </c>
       <c r="E410" s="4" t="s">
         <v>173</v>
@@ -48568,7 +48565,7 @@
         <v>4433</v>
       </c>
       <c r="D411" s="4" t="s">
-        <v>399</v>
+        <v>398</v>
       </c>
       <c r="E411" s="4" t="s">
         <v>173</v>
@@ -48681,7 +48678,7 @@
         <v>4433</v>
       </c>
       <c r="D412" s="4" t="s">
-        <v>399</v>
+        <v>398</v>
       </c>
       <c r="E412" s="4" t="s">
         <v>173</v>
@@ -48699,7 +48696,7 @@
         <v>2025</v>
       </c>
       <c r="J412" s="4" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="K412" s="3">
         <v>9.287509e6</v>
@@ -48794,7 +48791,7 @@
         <v>4433</v>
       </c>
       <c r="D413" s="4" t="s">
-        <v>399</v>
+        <v>398</v>
       </c>
       <c r="E413" s="4" t="s">
         <v>173</v>
@@ -48812,7 +48809,7 @@
         <v>2025</v>
       </c>
       <c r="J413" s="4" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="K413" s="3">
         <v>9.287509e6</v>
@@ -48867,7 +48864,7 @@
         <v>47</v>
       </c>
       <c r="AC413" s="4" t="s">
-        <v>401</v>
+        <v>400</v>
       </c>
       <c r="AD413" s="3">
         <v>1</v>
@@ -48911,7 +48908,7 @@
         <v>4433</v>
       </c>
       <c r="D414" s="4" t="s">
-        <v>399</v>
+        <v>398</v>
       </c>
       <c r="E414" s="4" t="s">
         <v>173</v>
@@ -48929,7 +48926,7 @@
         <v>2025</v>
       </c>
       <c r="J414" s="4" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="K414" s="3">
         <v>9.287509e6</v>
@@ -49026,7 +49023,7 @@
         <v>4433</v>
       </c>
       <c r="D415" s="4" t="s">
-        <v>399</v>
+        <v>398</v>
       </c>
       <c r="E415" s="4" t="s">
         <v>173</v>
@@ -49044,7 +49041,7 @@
         <v>2025</v>
       </c>
       <c r="J415" s="4" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="K415" s="3">
         <v>9.287509e6</v>
@@ -49145,7 +49142,7 @@
         <v>4433</v>
       </c>
       <c r="D416" s="4" t="s">
-        <v>399</v>
+        <v>398</v>
       </c>
       <c r="E416" s="4" t="s">
         <v>173</v>
@@ -49163,7 +49160,7 @@
         <v>2024</v>
       </c>
       <c r="J416" s="4" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="K416" s="3">
         <v>9.287509e6</v>
@@ -49258,7 +49255,7 @@
         <v>4433</v>
       </c>
       <c r="D417" s="4" t="s">
-        <v>399</v>
+        <v>398</v>
       </c>
       <c r="E417" s="4" t="s">
         <v>173</v>
@@ -49276,7 +49273,7 @@
         <v>2024</v>
       </c>
       <c r="J417" s="4" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="K417" s="3">
         <v>9.287509e6</v>
@@ -49371,7 +49368,7 @@
         <v>4433</v>
       </c>
       <c r="D418" s="4" t="s">
-        <v>399</v>
+        <v>398</v>
       </c>
       <c r="E418" s="4" t="s">
         <v>173</v>
@@ -49486,7 +49483,7 @@
         <v>4433</v>
       </c>
       <c r="D419" s="4" t="s">
-        <v>399</v>
+        <v>398</v>
       </c>
       <c r="E419" s="4" t="s">
         <v>173</v>
@@ -49605,16 +49602,16 @@
         <v>4433</v>
       </c>
       <c r="D420" s="4" t="s">
-        <v>399</v>
+        <v>398</v>
       </c>
       <c r="E420" s="4" t="s">
+        <v>200</v>
+      </c>
+      <c r="F420" s="4" t="s">
         <v>201</v>
       </c>
-      <c r="F420" s="4" t="s">
+      <c r="G420" s="4" t="s">
         <v>202</v>
-      </c>
-      <c r="G420" s="4" t="s">
-        <v>203</v>
       </c>
       <c r="H420" s="3">
         <v>20</v>
@@ -49623,7 +49620,7 @@
         <v>2025</v>
       </c>
       <c r="J420" s="4" t="s">
-        <v>204</v>
+        <v>203</v>
       </c>
       <c r="K420" s="3">
         <v>9.396057e6</v>
@@ -49718,16 +49715,16 @@
         <v>4433</v>
       </c>
       <c r="D421" s="4" t="s">
-        <v>399</v>
+        <v>398</v>
       </c>
       <c r="E421" s="4" t="s">
+        <v>200</v>
+      </c>
+      <c r="F421" s="4" t="s">
         <v>201</v>
       </c>
-      <c r="F421" s="4" t="s">
+      <c r="G421" s="4" t="s">
         <v>202</v>
-      </c>
-      <c r="G421" s="4" t="s">
-        <v>203</v>
       </c>
       <c r="H421" s="3">
         <v>20</v>
@@ -49736,7 +49733,7 @@
         <v>2025</v>
       </c>
       <c r="J421" s="4" t="s">
-        <v>204</v>
+        <v>203</v>
       </c>
       <c r="K421" s="3">
         <v>9.396057e6</v>
@@ -49831,16 +49828,16 @@
         <v>4433</v>
       </c>
       <c r="D422" s="4" t="s">
-        <v>399</v>
+        <v>398</v>
       </c>
       <c r="E422" s="4" t="s">
+        <v>200</v>
+      </c>
+      <c r="F422" s="4" t="s">
         <v>201</v>
       </c>
-      <c r="F422" s="4" t="s">
+      <c r="G422" s="4" t="s">
         <v>202</v>
-      </c>
-      <c r="G422" s="4" t="s">
-        <v>203</v>
       </c>
       <c r="H422" s="3">
         <v>1128</v>
@@ -49849,7 +49846,7 @@
         <v>2025</v>
       </c>
       <c r="J422" s="4" t="s">
-        <v>204</v>
+        <v>203</v>
       </c>
       <c r="K422" s="3">
         <v>9.396057e6</v>
@@ -49946,16 +49943,16 @@
         <v>4433</v>
       </c>
       <c r="D423" s="4" t="s">
-        <v>399</v>
+        <v>398</v>
       </c>
       <c r="E423" s="4" t="s">
+        <v>200</v>
+      </c>
+      <c r="F423" s="4" t="s">
         <v>201</v>
       </c>
-      <c r="F423" s="4" t="s">
+      <c r="G423" s="4" t="s">
         <v>202</v>
-      </c>
-      <c r="G423" s="4" t="s">
-        <v>203</v>
       </c>
       <c r="H423" s="3">
         <v>1128</v>
@@ -49964,7 +49961,7 @@
         <v>2025</v>
       </c>
       <c r="J423" s="4" t="s">
-        <v>204</v>
+        <v>203</v>
       </c>
       <c r="K423" s="3">
         <v>9.396057e6</v>
@@ -50061,16 +50058,16 @@
         <v>4433</v>
       </c>
       <c r="D424" s="4" t="s">
-        <v>399</v>
+        <v>398</v>
       </c>
       <c r="E424" s="4" t="s">
+        <v>200</v>
+      </c>
+      <c r="F424" s="4" t="s">
         <v>201</v>
       </c>
-      <c r="F424" s="4" t="s">
+      <c r="G424" s="4" t="s">
         <v>202</v>
-      </c>
-      <c r="G424" s="4" t="s">
-        <v>203</v>
       </c>
       <c r="H424" s="3">
         <v>1655</v>
@@ -50079,7 +50076,7 @@
         <v>2025</v>
       </c>
       <c r="J424" s="4" t="s">
-        <v>204</v>
+        <v>203</v>
       </c>
       <c r="K424" s="3">
         <v>9.479122e6</v>
@@ -50176,16 +50173,16 @@
         <v>4433</v>
       </c>
       <c r="D425" s="4" t="s">
-        <v>399</v>
+        <v>398</v>
       </c>
       <c r="E425" s="4" t="s">
+        <v>200</v>
+      </c>
+      <c r="F425" s="4" t="s">
         <v>201</v>
       </c>
-      <c r="F425" s="4" t="s">
+      <c r="G425" s="4" t="s">
         <v>202</v>
-      </c>
-      <c r="G425" s="4" t="s">
-        <v>203</v>
       </c>
       <c r="H425" s="3">
         <v>1655</v>
@@ -50194,7 +50191,7 @@
         <v>2025</v>
       </c>
       <c r="J425" s="4" t="s">
-        <v>204</v>
+        <v>203</v>
       </c>
       <c r="K425" s="3">
         <v>9.479122e6</v>
@@ -50291,16 +50288,16 @@
         <v>4433</v>
       </c>
       <c r="D426" s="4" t="s">
-        <v>399</v>
+        <v>398</v>
       </c>
       <c r="E426" s="4" t="s">
+        <v>200</v>
+      </c>
+      <c r="F426" s="4" t="s">
         <v>201</v>
       </c>
-      <c r="F426" s="4" t="s">
+      <c r="G426" s="4" t="s">
         <v>202</v>
-      </c>
-      <c r="G426" s="4" t="s">
-        <v>203</v>
       </c>
       <c r="H426" s="3">
         <v>1655</v>
@@ -50309,7 +50306,7 @@
         <v>2025</v>
       </c>
       <c r="J426" s="4" t="s">
-        <v>204</v>
+        <v>203</v>
       </c>
       <c r="K426" s="3">
         <v>9.479122e6</v>
@@ -50363,7 +50360,7 @@
         <v>0</v>
       </c>
       <c r="AB426" s="4" t="s">
-        <v>205</v>
+        <v>204</v>
       </c>
       <c r="AC426" s="4" t="s">
         <v>153</v>
@@ -50410,7 +50407,7 @@
         <v>4434</v>
       </c>
       <c r="D427" s="4" t="s">
-        <v>408</v>
+        <v>407</v>
       </c>
       <c r="E427" s="4" t="s">
         <v>128</v>
@@ -50525,13 +50522,13 @@
         <v>4434</v>
       </c>
       <c r="D428" s="4" t="s">
+        <v>407</v>
+      </c>
+      <c r="E428" s="4" t="s">
         <v>408</v>
       </c>
-      <c r="E428" s="4" t="s">
+      <c r="F428" s="4" t="s">
         <v>409</v>
-      </c>
-      <c r="F428" s="4" t="s">
-        <v>410</v>
       </c>
       <c r="G428" s="4" t="s">
         <v>96</v>
@@ -50543,7 +50540,7 @@
         <v>2025</v>
       </c>
       <c r="J428" s="4" t="s">
-        <v>411</v>
+        <v>410</v>
       </c>
       <c r="K428" s="3">
         <v>9.47884e6</v>
@@ -50640,13 +50637,13 @@
         <v>4434</v>
       </c>
       <c r="D429" s="4" t="s">
+        <v>407</v>
+      </c>
+      <c r="E429" s="4" t="s">
         <v>408</v>
       </c>
-      <c r="E429" s="4" t="s">
+      <c r="F429" s="4" t="s">
         <v>409</v>
-      </c>
-      <c r="F429" s="4" t="s">
-        <v>410</v>
       </c>
       <c r="G429" s="4" t="s">
         <v>96</v>
@@ -50658,7 +50655,7 @@
         <v>2025</v>
       </c>
       <c r="J429" s="4" t="s">
-        <v>411</v>
+        <v>410</v>
       </c>
       <c r="K429" s="3">
         <v>9.47884e6</v>
@@ -50755,7 +50752,7 @@
         <v>4434</v>
       </c>
       <c r="D430" s="4" t="s">
-        <v>408</v>
+        <v>407</v>
       </c>
       <c r="E430" s="4" t="s">
         <v>125</v>
@@ -50870,13 +50867,13 @@
         <v>4434</v>
       </c>
       <c r="D431" s="4" t="s">
-        <v>408</v>
+        <v>407</v>
       </c>
       <c r="E431" s="4" t="s">
+        <v>411</v>
+      </c>
+      <c r="F431" s="4" t="s">
         <v>412</v>
-      </c>
-      <c r="F431" s="4" t="s">
-        <v>413</v>
       </c>
       <c r="G431" s="4" t="s">
         <v>96</v>
@@ -50888,7 +50885,7 @@
         <v>2025</v>
       </c>
       <c r="J431" s="4" t="s">
-        <v>414</v>
+        <v>413</v>
       </c>
       <c r="K431" s="3">
         <v>9.470167e6</v>
@@ -50985,13 +50982,13 @@
         <v>4434</v>
       </c>
       <c r="D432" s="4" t="s">
-        <v>408</v>
+        <v>407</v>
       </c>
       <c r="E432" s="4" t="s">
+        <v>411</v>
+      </c>
+      <c r="F432" s="4" t="s">
         <v>412</v>
-      </c>
-      <c r="F432" s="4" t="s">
-        <v>413</v>
       </c>
       <c r="G432" s="4" t="s">
         <v>96</v>
@@ -51003,7 +51000,7 @@
         <v>2025</v>
       </c>
       <c r="J432" s="4" t="s">
-        <v>414</v>
+        <v>413</v>
       </c>
       <c r="K432" s="3">
         <v>9.470167e6</v>
@@ -51042,22 +51039,22 @@
         <v>46042</v>
       </c>
       <c r="W432" s="4" t="s">
+        <v>414</v>
+      </c>
+      <c r="X432" s="5">
+        <v>0</v>
+      </c>
+      <c r="Y432" s="5">
+        <v>0</v>
+      </c>
+      <c r="Z432" s="5">
+        <v>0</v>
+      </c>
+      <c r="AA432" s="5">
+        <v>0</v>
+      </c>
+      <c r="AB432" s="4" t="s">
         <v>415</v>
-      </c>
-      <c r="X432" s="5">
-        <v>0</v>
-      </c>
-      <c r="Y432" s="5">
-        <v>0</v>
-      </c>
-      <c r="Z432" s="5">
-        <v>0</v>
-      </c>
-      <c r="AA432" s="5">
-        <v>0</v>
-      </c>
-      <c r="AB432" s="4" t="s">
-        <v>416</v>
       </c>
       <c r="AC432" s="4" t="s">
         <v>153</v>
@@ -51104,13 +51101,13 @@
         <v>4434</v>
       </c>
       <c r="D433" s="4" t="s">
-        <v>408</v>
+        <v>407</v>
       </c>
       <c r="E433" s="4" t="s">
+        <v>411</v>
+      </c>
+      <c r="F433" s="4" t="s">
         <v>412</v>
-      </c>
-      <c r="F433" s="4" t="s">
-        <v>413</v>
       </c>
       <c r="G433" s="4" t="s">
         <v>96</v>
@@ -51122,7 +51119,7 @@
         <v>2025</v>
       </c>
       <c r="J433" s="4" t="s">
-        <v>414</v>
+        <v>413</v>
       </c>
       <c r="K433" s="3">
         <v>9.470167e6</v>
@@ -51176,7 +51173,7 @@
         <v>0</v>
       </c>
       <c r="AB433" s="4" t="s">
-        <v>417</v>
+        <v>416</v>
       </c>
       <c r="AC433" s="4" t="s">
         <v>153</v>
@@ -51223,13 +51220,13 @@
         <v>4434</v>
       </c>
       <c r="D434" s="4" t="s">
-        <v>408</v>
+        <v>407</v>
       </c>
       <c r="E434" s="4" t="s">
+        <v>402</v>
+      </c>
+      <c r="F434" s="4" t="s">
         <v>403</v>
-      </c>
-      <c r="F434" s="4" t="s">
-        <v>404</v>
       </c>
       <c r="G434" s="4" t="s">
         <v>106</v>
@@ -51338,13 +51335,13 @@
         <v>4434</v>
       </c>
       <c r="D435" s="4" t="s">
-        <v>408</v>
+        <v>407</v>
       </c>
       <c r="E435" s="4" t="s">
+        <v>402</v>
+      </c>
+      <c r="F435" s="4" t="s">
         <v>403</v>
-      </c>
-      <c r="F435" s="4" t="s">
-        <v>404</v>
       </c>
       <c r="G435" s="4" t="s">
         <v>106</v>
@@ -51410,7 +51407,7 @@
         <v>0</v>
       </c>
       <c r="AB435" s="4" t="s">
-        <v>405</v>
+        <v>404</v>
       </c>
       <c r="AC435" s="4" t="s">
         <v>153</v>
@@ -51457,7 +51454,7 @@
         <v>4434</v>
       </c>
       <c r="D436" s="4" t="s">
-        <v>408</v>
+        <v>407</v>
       </c>
       <c r="E436" s="4" t="s">
         <v>173</v>
@@ -51570,7 +51567,7 @@
         <v>4434</v>
       </c>
       <c r="D437" s="4" t="s">
-        <v>408</v>
+        <v>407</v>
       </c>
       <c r="E437" s="4" t="s">
         <v>173</v>
@@ -51643,7 +51640,7 @@
         <v>47</v>
       </c>
       <c r="AC437" s="4" t="s">
-        <v>401</v>
+        <v>400</v>
       </c>
       <c r="AD437" s="3">
         <v>9</v>
@@ -51687,7 +51684,7 @@
         <v>4434</v>
       </c>
       <c r="D438" s="4" t="s">
-        <v>408</v>
+        <v>407</v>
       </c>
       <c r="E438" s="4" t="s">
         <v>173</v>
@@ -51800,7 +51797,7 @@
         <v>4434</v>
       </c>
       <c r="D439" s="4" t="s">
-        <v>408</v>
+        <v>407</v>
       </c>
       <c r="E439" s="4" t="s">
         <v>173</v>
@@ -51873,7 +51870,7 @@
         <v>47</v>
       </c>
       <c r="AC439" s="4" t="s">
-        <v>401</v>
+        <v>400</v>
       </c>
       <c r="AD439" s="3">
         <v>1</v>
@@ -51917,7 +51914,7 @@
         <v>4434</v>
       </c>
       <c r="D440" s="4" t="s">
-        <v>408</v>
+        <v>407</v>
       </c>
       <c r="E440" s="4" t="s">
         <v>173</v>
@@ -51935,7 +51932,7 @@
         <v>2024</v>
       </c>
       <c r="J440" s="4" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="K440" s="3">
         <v>9.287509e6</v>
@@ -52030,7 +52027,7 @@
         <v>4434</v>
       </c>
       <c r="D441" s="4" t="s">
-        <v>408</v>
+        <v>407</v>
       </c>
       <c r="E441" s="4" t="s">
         <v>173</v>
@@ -52143,7 +52140,7 @@
         <v>4434</v>
       </c>
       <c r="D442" s="4" t="s">
-        <v>408</v>
+        <v>407</v>
       </c>
       <c r="E442" s="4" t="s">
         <v>173</v>
@@ -52216,7 +52213,7 @@
         <v>47</v>
       </c>
       <c r="AC442" s="4" t="s">
-        <v>401</v>
+        <v>400</v>
       </c>
       <c r="AD442" s="3">
         <v>1</v>
@@ -52260,7 +52257,7 @@
         <v>4434</v>
       </c>
       <c r="D443" s="4" t="s">
-        <v>408</v>
+        <v>407</v>
       </c>
       <c r="E443" s="4" t="s">
         <v>173</v>
@@ -52333,7 +52330,7 @@
         <v>47</v>
       </c>
       <c r="AC443" s="4" t="s">
-        <v>401</v>
+        <v>400</v>
       </c>
       <c r="AD443" s="3">
         <v>1</v>
@@ -52377,7 +52374,7 @@
         <v>4434</v>
       </c>
       <c r="D444" s="4" t="s">
-        <v>408</v>
+        <v>407</v>
       </c>
       <c r="E444" s="4" t="s">
         <v>173</v>
@@ -52492,7 +52489,7 @@
         <v>4434</v>
       </c>
       <c r="D445" s="4" t="s">
-        <v>408</v>
+        <v>407</v>
       </c>
       <c r="E445" s="4" t="s">
         <v>173</v>
@@ -52607,7 +52604,7 @@
         <v>4434</v>
       </c>
       <c r="D446" s="4" t="s">
-        <v>408</v>
+        <v>407</v>
       </c>
       <c r="E446" s="4" t="s">
         <v>173</v>
@@ -52726,7 +52723,7 @@
         <v>4434</v>
       </c>
       <c r="D447" s="4" t="s">
-        <v>408</v>
+        <v>407</v>
       </c>
       <c r="E447" s="4" t="s">
         <v>173</v>
@@ -52841,7 +52838,7 @@
         <v>4434</v>
       </c>
       <c r="D448" s="4" t="s">
-        <v>408</v>
+        <v>407</v>
       </c>
       <c r="E448" s="4" t="s">
         <v>173</v>
@@ -52960,7 +52957,7 @@
         <v>4434</v>
       </c>
       <c r="D449" s="4" t="s">
-        <v>408</v>
+        <v>407</v>
       </c>
       <c r="E449" s="4" t="s">
         <v>173</v>
@@ -53075,7 +53072,7 @@
         <v>4434</v>
       </c>
       <c r="D450" s="4" t="s">
-        <v>408</v>
+        <v>407</v>
       </c>
       <c r="E450" s="4" t="s">
         <v>173</v>
@@ -53190,7 +53187,7 @@
         <v>4434</v>
       </c>
       <c r="D451" s="4" t="s">
-        <v>408</v>
+        <v>407</v>
       </c>
       <c r="E451" s="4" t="s">
         <v>173</v>
@@ -53305,7 +53302,7 @@
         <v>4434</v>
       </c>
       <c r="D452" s="4" t="s">
-        <v>408</v>
+        <v>407</v>
       </c>
       <c r="E452" s="4" t="s">
         <v>173</v>
@@ -53420,7 +53417,7 @@
         <v>4434</v>
       </c>
       <c r="D453" s="4" t="s">
-        <v>408</v>
+        <v>407</v>
       </c>
       <c r="E453" s="4" t="s">
         <v>173</v>
@@ -53539,7 +53536,7 @@
         <v>4434</v>
       </c>
       <c r="D454" s="4" t="s">
-        <v>408</v>
+        <v>407</v>
       </c>
       <c r="E454" s="4" t="s">
         <v>173</v>
@@ -53658,7 +53655,7 @@
         <v>4434</v>
       </c>
       <c r="D455" s="4" t="s">
-        <v>408</v>
+        <v>407</v>
       </c>
       <c r="E455" s="4" t="s">
         <v>173</v>
@@ -53777,7 +53774,7 @@
         <v>4434</v>
       </c>
       <c r="D456" s="4" t="s">
-        <v>408</v>
+        <v>407</v>
       </c>
       <c r="E456" s="4" t="s">
         <v>173</v>
@@ -53795,7 +53792,7 @@
         <v>2025</v>
       </c>
       <c r="J456" s="4" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="K456" s="3">
         <v>9.287509e6</v>
@@ -53890,7 +53887,7 @@
         <v>4434</v>
       </c>
       <c r="D457" s="4" t="s">
-        <v>408</v>
+        <v>407</v>
       </c>
       <c r="E457" s="4" t="s">
         <v>173</v>
@@ -53908,7 +53905,7 @@
         <v>2025</v>
       </c>
       <c r="J457" s="4" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="K457" s="3">
         <v>9.287509e6</v>
@@ -53963,7 +53960,7 @@
         <v>47</v>
       </c>
       <c r="AC457" s="4" t="s">
-        <v>401</v>
+        <v>400</v>
       </c>
       <c r="AD457" s="3">
         <v>1</v>
@@ -54007,7 +54004,7 @@
         <v>4434</v>
       </c>
       <c r="D458" s="4" t="s">
-        <v>408</v>
+        <v>407</v>
       </c>
       <c r="E458" s="4" t="s">
         <v>173</v>
@@ -54120,7 +54117,7 @@
         <v>4434</v>
       </c>
       <c r="D459" s="4" t="s">
-        <v>408</v>
+        <v>407</v>
       </c>
       <c r="E459" s="4" t="s">
         <v>173</v>
@@ -54193,7 +54190,7 @@
         <v>47</v>
       </c>
       <c r="AC459" s="4" t="s">
-        <v>401</v>
+        <v>400</v>
       </c>
       <c r="AD459" s="3">
         <v>9</v>
@@ -54237,7 +54234,7 @@
         <v>4434</v>
       </c>
       <c r="D460" s="4" t="s">
-        <v>408</v>
+        <v>407</v>
       </c>
       <c r="E460" s="4" t="s">
         <v>173</v>
@@ -54310,7 +54307,7 @@
         <v>47</v>
       </c>
       <c r="AC460" s="4" t="s">
-        <v>401</v>
+        <v>400</v>
       </c>
       <c r="AD460" s="3">
         <v>9</v>
@@ -54354,7 +54351,7 @@
         <v>4434</v>
       </c>
       <c r="D461" s="4" t="s">
-        <v>408</v>
+        <v>407</v>
       </c>
       <c r="E461" s="4" t="s">
         <v>173</v>
@@ -54372,7 +54369,7 @@
         <v>2024</v>
       </c>
       <c r="J461" s="4" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="K461" s="3">
         <v>9.287509e6</v>
@@ -54467,16 +54464,16 @@
         <v>4434</v>
       </c>
       <c r="D462" s="4" t="s">
-        <v>408</v>
+        <v>407</v>
       </c>
       <c r="E462" s="4" t="s">
+        <v>194</v>
+      </c>
+      <c r="F462" s="4" t="s">
         <v>195</v>
       </c>
-      <c r="F462" s="4" t="s">
+      <c r="G462" s="4" t="s">
         <v>196</v>
-      </c>
-      <c r="G462" s="4" t="s">
-        <v>197</v>
       </c>
       <c r="H462" s="3">
         <v>42</v>
@@ -54582,16 +54579,16 @@
         <v>4434</v>
       </c>
       <c r="D463" s="4" t="s">
-        <v>408</v>
+        <v>407</v>
       </c>
       <c r="E463" s="4" t="s">
+        <v>194</v>
+      </c>
+      <c r="F463" s="4" t="s">
         <v>195</v>
       </c>
-      <c r="F463" s="4" t="s">
+      <c r="G463" s="4" t="s">
         <v>196</v>
-      </c>
-      <c r="G463" s="4" t="s">
-        <v>197</v>
       </c>
       <c r="H463" s="3">
         <v>42</v>
@@ -54697,16 +54694,16 @@
         <v>4434</v>
       </c>
       <c r="D464" s="4" t="s">
-        <v>408</v>
+        <v>407</v>
       </c>
       <c r="E464" s="4" t="s">
+        <v>194</v>
+      </c>
+      <c r="F464" s="4" t="s">
         <v>195</v>
       </c>
-      <c r="F464" s="4" t="s">
+      <c r="G464" s="4" t="s">
         <v>196</v>
-      </c>
-      <c r="G464" s="4" t="s">
-        <v>197</v>
       </c>
       <c r="H464" s="3">
         <v>42</v>
@@ -54769,7 +54766,7 @@
         <v>0</v>
       </c>
       <c r="AB464" s="4" t="s">
-        <v>198</v>
+        <v>197</v>
       </c>
       <c r="AC464" s="4" t="s">
         <v>153</v>
@@ -54816,13 +54813,13 @@
         <v>4434</v>
       </c>
       <c r="D465" s="4" t="s">
-        <v>408</v>
+        <v>407</v>
       </c>
       <c r="E465" s="4" t="s">
+        <v>417</v>
+      </c>
+      <c r="F465" s="4" t="s">
         <v>418</v>
-      </c>
-      <c r="F465" s="4" t="s">
-        <v>419</v>
       </c>
       <c r="G465" s="4" t="s">
         <v>106</v>
@@ -54834,7 +54831,7 @@
         <v>2025</v>
       </c>
       <c r="J465" s="4" t="s">
-        <v>420</v>
+        <v>419</v>
       </c>
       <c r="K465" s="3">
         <v>9.331944e6</v>
@@ -54929,13 +54926,13 @@
         <v>4434</v>
       </c>
       <c r="D466" s="4" t="s">
-        <v>408</v>
+        <v>407</v>
       </c>
       <c r="E466" s="4" t="s">
+        <v>417</v>
+      </c>
+      <c r="F466" s="4" t="s">
         <v>418</v>
-      </c>
-      <c r="F466" s="4" t="s">
-        <v>419</v>
       </c>
       <c r="G466" s="4" t="s">
         <v>106</v>
@@ -54947,7 +54944,7 @@
         <v>2025</v>
       </c>
       <c r="J466" s="4" t="s">
-        <v>420</v>
+        <v>419</v>
       </c>
       <c r="K466" s="3">
         <v>9.331944e6</v>
@@ -55042,16 +55039,16 @@
         <v>4434</v>
       </c>
       <c r="D467" s="4" t="s">
-        <v>408</v>
+        <v>407</v>
       </c>
       <c r="E467" s="4" t="s">
+        <v>200</v>
+      </c>
+      <c r="F467" s="4" t="s">
         <v>201</v>
       </c>
-      <c r="F467" s="4" t="s">
+      <c r="G467" s="4" t="s">
         <v>202</v>
-      </c>
-      <c r="G467" s="4" t="s">
-        <v>203</v>
       </c>
       <c r="H467" s="3">
         <v>18</v>
@@ -55060,7 +55057,7 @@
         <v>2025</v>
       </c>
       <c r="J467" s="4" t="s">
-        <v>204</v>
+        <v>203</v>
       </c>
       <c r="K467" s="3">
         <v>9.396057e6</v>
@@ -55157,16 +55154,16 @@
         <v>4434</v>
       </c>
       <c r="D468" s="4" t="s">
-        <v>408</v>
+        <v>407</v>
       </c>
       <c r="E468" s="4" t="s">
+        <v>200</v>
+      </c>
+      <c r="F468" s="4" t="s">
         <v>201</v>
       </c>
-      <c r="F468" s="4" t="s">
+      <c r="G468" s="4" t="s">
         <v>202</v>
-      </c>
-      <c r="G468" s="4" t="s">
-        <v>203</v>
       </c>
       <c r="H468" s="3">
         <v>18</v>
@@ -55175,7 +55172,7 @@
         <v>2025</v>
       </c>
       <c r="J468" s="4" t="s">
-        <v>204</v>
+        <v>203</v>
       </c>
       <c r="K468" s="3">
         <v>9.396057e6</v>
@@ -55272,16 +55269,16 @@
         <v>4434</v>
       </c>
       <c r="D469" s="4" t="s">
-        <v>408</v>
+        <v>407</v>
       </c>
       <c r="E469" s="4" t="s">
+        <v>200</v>
+      </c>
+      <c r="F469" s="4" t="s">
         <v>201</v>
       </c>
-      <c r="F469" s="4" t="s">
+      <c r="G469" s="4" t="s">
         <v>202</v>
-      </c>
-      <c r="G469" s="4" t="s">
-        <v>203</v>
       </c>
       <c r="H469" s="3">
         <v>90</v>
@@ -55290,7 +55287,7 @@
         <v>2025</v>
       </c>
       <c r="J469" s="4" t="s">
-        <v>204</v>
+        <v>203</v>
       </c>
       <c r="K469" s="3">
         <v>9.396057e6</v>
@@ -55385,16 +55382,16 @@
         <v>4434</v>
       </c>
       <c r="D470" s="4" t="s">
-        <v>408</v>
+        <v>407</v>
       </c>
       <c r="E470" s="4" t="s">
+        <v>200</v>
+      </c>
+      <c r="F470" s="4" t="s">
         <v>201</v>
       </c>
-      <c r="F470" s="4" t="s">
+      <c r="G470" s="4" t="s">
         <v>202</v>
-      </c>
-      <c r="G470" s="4" t="s">
-        <v>203</v>
       </c>
       <c r="H470" s="3">
         <v>90</v>
@@ -55403,7 +55400,7 @@
         <v>2025</v>
       </c>
       <c r="J470" s="4" t="s">
-        <v>204</v>
+        <v>203</v>
       </c>
       <c r="K470" s="3">
         <v>9.396057e6</v>
@@ -55498,16 +55495,16 @@
         <v>4434</v>
       </c>
       <c r="D471" s="4" t="s">
-        <v>408</v>
+        <v>407</v>
       </c>
       <c r="E471" s="4" t="s">
+        <v>200</v>
+      </c>
+      <c r="F471" s="4" t="s">
         <v>201</v>
       </c>
-      <c r="F471" s="4" t="s">
+      <c r="G471" s="4" t="s">
         <v>202</v>
-      </c>
-      <c r="G471" s="4" t="s">
-        <v>203</v>
       </c>
       <c r="H471" s="3">
         <v>1033</v>
@@ -55516,7 +55513,7 @@
         <v>2024</v>
       </c>
       <c r="J471" s="4" t="s">
-        <v>204</v>
+        <v>203</v>
       </c>
       <c r="K471" s="3">
         <v>9.396057e6</v>
@@ -55613,16 +55610,16 @@
         <v>4434</v>
       </c>
       <c r="D472" s="4" t="s">
-        <v>408</v>
+        <v>407</v>
       </c>
       <c r="E472" s="4" t="s">
+        <v>200</v>
+      </c>
+      <c r="F472" s="4" t="s">
         <v>201</v>
       </c>
-      <c r="F472" s="4" t="s">
+      <c r="G472" s="4" t="s">
         <v>202</v>
-      </c>
-      <c r="G472" s="4" t="s">
-        <v>203</v>
       </c>
       <c r="H472" s="3">
         <v>1033</v>
@@ -55631,7 +55628,7 @@
         <v>2024</v>
       </c>
       <c r="J472" s="4" t="s">
-        <v>204</v>
+        <v>203</v>
       </c>
       <c r="K472" s="3">
         <v>9.396057e6</v>
@@ -55728,16 +55725,16 @@
         <v>4434</v>
       </c>
       <c r="D473" s="4" t="s">
-        <v>408</v>
+        <v>407</v>
       </c>
       <c r="E473" s="4" t="s">
+        <v>200</v>
+      </c>
+      <c r="F473" s="4" t="s">
         <v>201</v>
       </c>
-      <c r="F473" s="4" t="s">
+      <c r="G473" s="4" t="s">
         <v>202</v>
-      </c>
-      <c r="G473" s="4" t="s">
-        <v>203</v>
       </c>
       <c r="H473" s="3">
         <v>1656</v>
@@ -55746,7 +55743,7 @@
         <v>2025</v>
       </c>
       <c r="J473" s="4" t="s">
-        <v>204</v>
+        <v>203</v>
       </c>
       <c r="K473" s="3">
         <v>9.479122e6</v>
@@ -55843,16 +55840,16 @@
         <v>4434</v>
       </c>
       <c r="D474" s="4" t="s">
-        <v>408</v>
+        <v>407</v>
       </c>
       <c r="E474" s="4" t="s">
+        <v>200</v>
+      </c>
+      <c r="F474" s="4" t="s">
         <v>201</v>
       </c>
-      <c r="F474" s="4" t="s">
+      <c r="G474" s="4" t="s">
         <v>202</v>
-      </c>
-      <c r="G474" s="4" t="s">
-        <v>203</v>
       </c>
       <c r="H474" s="3">
         <v>1677</v>
@@ -55861,7 +55858,7 @@
         <v>2025</v>
       </c>
       <c r="J474" s="4" t="s">
-        <v>204</v>
+        <v>203</v>
       </c>
       <c r="K474" s="3">
         <v>9.479122e6</v>
@@ -55958,16 +55955,16 @@
         <v>4435</v>
       </c>
       <c r="D475" s="4" t="s">
+        <v>420</v>
+      </c>
+      <c r="E475" s="4" t="s">
         <v>421</v>
       </c>
-      <c r="E475" s="4" t="s">
+      <c r="F475" s="4" t="s">
         <v>422</v>
       </c>
-      <c r="F475" s="4" t="s">
+      <c r="G475" s="4" t="s">
         <v>423</v>
-      </c>
-      <c r="G475" s="4" t="s">
-        <v>424</v>
       </c>
       <c r="H475" s="3">
         <v>1422</v>
@@ -55976,7 +55973,7 @@
         <v>2025</v>
       </c>
       <c r="J475" s="4" t="s">
-        <v>414</v>
+        <v>413</v>
       </c>
       <c r="K475" s="3">
         <v>9.470154e6</v>
@@ -56073,16 +56070,16 @@
         <v>4435</v>
       </c>
       <c r="D476" s="4" t="s">
+        <v>420</v>
+      </c>
+      <c r="E476" s="4" t="s">
         <v>421</v>
       </c>
-      <c r="E476" s="4" t="s">
+      <c r="F476" s="4" t="s">
         <v>422</v>
       </c>
-      <c r="F476" s="4" t="s">
+      <c r="G476" s="4" t="s">
         <v>423</v>
-      </c>
-      <c r="G476" s="4" t="s">
-        <v>424</v>
       </c>
       <c r="H476" s="3">
         <v>1426</v>
@@ -56091,7 +56088,7 @@
         <v>2025</v>
       </c>
       <c r="J476" s="4" t="s">
-        <v>414</v>
+        <v>413</v>
       </c>
       <c r="K476" s="3">
         <v>9.470154e6</v>
@@ -56186,16 +56183,16 @@
         <v>4435</v>
       </c>
       <c r="D477" s="4" t="s">
+        <v>420</v>
+      </c>
+      <c r="E477" s="4" t="s">
         <v>421</v>
       </c>
-      <c r="E477" s="4" t="s">
+      <c r="F477" s="4" t="s">
         <v>422</v>
       </c>
-      <c r="F477" s="4" t="s">
+      <c r="G477" s="4" t="s">
         <v>423</v>
-      </c>
-      <c r="G477" s="4" t="s">
-        <v>424</v>
       </c>
       <c r="H477" s="3">
         <v>1582</v>
@@ -56204,7 +56201,7 @@
         <v>2025</v>
       </c>
       <c r="J477" s="4" t="s">
-        <v>414</v>
+        <v>413</v>
       </c>
       <c r="K477" s="3">
         <v>9.470154e6</v>
@@ -56301,13 +56298,13 @@
         <v>4435</v>
       </c>
       <c r="D478" s="4" t="s">
-        <v>421</v>
+        <v>420</v>
       </c>
       <c r="E478" s="4" t="s">
+        <v>411</v>
+      </c>
+      <c r="F478" s="4" t="s">
         <v>412</v>
-      </c>
-      <c r="F478" s="4" t="s">
-        <v>413</v>
       </c>
       <c r="G478" s="4" t="s">
         <v>96</v>
@@ -56319,7 +56316,7 @@
         <v>2025</v>
       </c>
       <c r="J478" s="4" t="s">
-        <v>414</v>
+        <v>413</v>
       </c>
       <c r="K478" s="3">
         <v>9.470167e6</v>
@@ -56416,13 +56413,13 @@
         <v>4435</v>
       </c>
       <c r="D479" s="4" t="s">
-        <v>421</v>
+        <v>420</v>
       </c>
       <c r="E479" s="4" t="s">
+        <v>411</v>
+      </c>
+      <c r="F479" s="4" t="s">
         <v>412</v>
-      </c>
-      <c r="F479" s="4" t="s">
-        <v>413</v>
       </c>
       <c r="G479" s="4" t="s">
         <v>96</v>
@@ -56434,7 +56431,7 @@
         <v>2025</v>
       </c>
       <c r="J479" s="4" t="s">
-        <v>414</v>
+        <v>413</v>
       </c>
       <c r="K479" s="3">
         <v>9.470167e6</v>
@@ -56473,22 +56470,22 @@
         <v>46042</v>
       </c>
       <c r="W479" s="4" t="s">
+        <v>414</v>
+      </c>
+      <c r="X479" s="5">
+        <v>0</v>
+      </c>
+      <c r="Y479" s="5">
+        <v>0</v>
+      </c>
+      <c r="Z479" s="5">
+        <v>0</v>
+      </c>
+      <c r="AA479" s="5">
+        <v>0</v>
+      </c>
+      <c r="AB479" s="4" t="s">
         <v>415</v>
-      </c>
-      <c r="X479" s="5">
-        <v>0</v>
-      </c>
-      <c r="Y479" s="5">
-        <v>0</v>
-      </c>
-      <c r="Z479" s="5">
-        <v>0</v>
-      </c>
-      <c r="AA479" s="5">
-        <v>0</v>
-      </c>
-      <c r="AB479" s="4" t="s">
-        <v>416</v>
       </c>
       <c r="AC479" s="4" t="s">
         <v>153</v>
@@ -56535,13 +56532,13 @@
         <v>4435</v>
       </c>
       <c r="D480" s="4" t="s">
-        <v>421</v>
+        <v>420</v>
       </c>
       <c r="E480" s="4" t="s">
+        <v>411</v>
+      </c>
+      <c r="F480" s="4" t="s">
         <v>412</v>
-      </c>
-      <c r="F480" s="4" t="s">
-        <v>413</v>
       </c>
       <c r="G480" s="4" t="s">
         <v>96</v>
@@ -56553,7 +56550,7 @@
         <v>2025</v>
       </c>
       <c r="J480" s="4" t="s">
-        <v>414</v>
+        <v>413</v>
       </c>
       <c r="K480" s="3">
         <v>9.470167e6</v>
@@ -56607,7 +56604,7 @@
         <v>0</v>
       </c>
       <c r="AB480" s="4" t="s">
-        <v>417</v>
+        <v>416</v>
       </c>
       <c r="AC480" s="4" t="s">
         <v>153</v>
@@ -56654,13 +56651,13 @@
         <v>4435</v>
       </c>
       <c r="D481" s="4" t="s">
-        <v>421</v>
+        <v>420</v>
       </c>
       <c r="E481" s="4" t="s">
+        <v>411</v>
+      </c>
+      <c r="F481" s="4" t="s">
         <v>412</v>
-      </c>
-      <c r="F481" s="4" t="s">
-        <v>413</v>
       </c>
       <c r="G481" s="4" t="s">
         <v>96</v>
@@ -56672,7 +56669,7 @@
         <v>2025</v>
       </c>
       <c r="J481" s="4" t="s">
-        <v>414</v>
+        <v>413</v>
       </c>
       <c r="K481" s="3">
         <v>9.470167e6</v>
@@ -56767,13 +56764,13 @@
         <v>4435</v>
       </c>
       <c r="D482" s="4" t="s">
-        <v>421</v>
+        <v>420</v>
       </c>
       <c r="E482" s="4" t="s">
+        <v>402</v>
+      </c>
+      <c r="F482" s="4" t="s">
         <v>403</v>
-      </c>
-      <c r="F482" s="4" t="s">
-        <v>404</v>
       </c>
       <c r="G482" s="4" t="s">
         <v>106</v>
@@ -56880,13 +56877,13 @@
         <v>4435</v>
       </c>
       <c r="D483" s="4" t="s">
-        <v>421</v>
+        <v>420</v>
       </c>
       <c r="E483" s="4" t="s">
+        <v>402</v>
+      </c>
+      <c r="F483" s="4" t="s">
         <v>403</v>
-      </c>
-      <c r="F483" s="4" t="s">
-        <v>404</v>
       </c>
       <c r="G483" s="4" t="s">
         <v>106</v>
@@ -56993,7 +56990,7 @@
         <v>4435</v>
       </c>
       <c r="D484" s="4" t="s">
-        <v>421</v>
+        <v>420</v>
       </c>
       <c r="E484" s="4" t="s">
         <v>173</v>
@@ -57108,7 +57105,7 @@
         <v>4435</v>
       </c>
       <c r="D485" s="4" t="s">
-        <v>421</v>
+        <v>420</v>
       </c>
       <c r="E485" s="4" t="s">
         <v>173</v>
@@ -57165,7 +57162,7 @@
         <v>46311</v>
       </c>
       <c r="W485" s="4" t="s">
-        <v>177</v>
+        <v>135</v>
       </c>
       <c r="X485" s="5">
         <v>211.49</v>
@@ -57227,7 +57224,7 @@
         <v>4435</v>
       </c>
       <c r="D486" s="4" t="s">
-        <v>421</v>
+        <v>420</v>
       </c>
       <c r="E486" s="4" t="s">
         <v>173</v>
@@ -57342,7 +57339,7 @@
         <v>4435</v>
       </c>
       <c r="D487" s="4" t="s">
-        <v>421</v>
+        <v>420</v>
       </c>
       <c r="E487" s="4" t="s">
         <v>173</v>
@@ -57461,7 +57458,7 @@
         <v>4435</v>
       </c>
       <c r="D488" s="4" t="s">
-        <v>421</v>
+        <v>420</v>
       </c>
       <c r="E488" s="4" t="s">
         <v>173</v>
@@ -57518,7 +57515,7 @@
         <v>46311</v>
       </c>
       <c r="W488" s="4" t="s">
-        <v>177</v>
+        <v>135</v>
       </c>
       <c r="X488" s="5">
         <v>537.57</v>
@@ -57580,7 +57577,7 @@
         <v>4435</v>
       </c>
       <c r="D489" s="4" t="s">
-        <v>421</v>
+        <v>420</v>
       </c>
       <c r="E489" s="4" t="s">
         <v>173</v>
@@ -57695,7 +57692,7 @@
         <v>4435</v>
       </c>
       <c r="D490" s="4" t="s">
-        <v>421</v>
+        <v>420</v>
       </c>
       <c r="E490" s="4" t="s">
         <v>173</v>
@@ -57810,7 +57807,7 @@
         <v>4435</v>
       </c>
       <c r="D491" s="4" t="s">
-        <v>421</v>
+        <v>420</v>
       </c>
       <c r="E491" s="4" t="s">
         <v>173</v>
@@ -57929,7 +57926,7 @@
         <v>4435</v>
       </c>
       <c r="D492" s="4" t="s">
-        <v>421</v>
+        <v>420</v>
       </c>
       <c r="E492" s="4" t="s">
         <v>173</v>
@@ -58048,7 +58045,7 @@
         <v>4435</v>
       </c>
       <c r="D493" s="4" t="s">
-        <v>421</v>
+        <v>420</v>
       </c>
       <c r="E493" s="4" t="s">
         <v>173</v>
@@ -58167,7 +58164,7 @@
         <v>4435</v>
       </c>
       <c r="D494" s="4" t="s">
-        <v>421</v>
+        <v>420</v>
       </c>
       <c r="E494" s="4" t="s">
         <v>173</v>
@@ -58286,7 +58283,7 @@
         <v>4435</v>
       </c>
       <c r="D495" s="4" t="s">
-        <v>421</v>
+        <v>420</v>
       </c>
       <c r="E495" s="4" t="s">
         <v>173</v>
@@ -58399,13 +58396,13 @@
         <v>4435</v>
       </c>
       <c r="D496" s="4" t="s">
-        <v>421</v>
+        <v>420</v>
       </c>
       <c r="E496" s="4" t="s">
+        <v>424</v>
+      </c>
+      <c r="F496" s="4" t="s">
         <v>425</v>
-      </c>
-      <c r="F496" s="4" t="s">
-        <v>426</v>
       </c>
       <c r="G496" s="4" t="s">
         <v>96</v>
@@ -58417,7 +58414,7 @@
         <v>2025</v>
       </c>
       <c r="J496" s="4" t="s">
-        <v>427</v>
+        <v>426</v>
       </c>
       <c r="K496" s="3">
         <v>9.445692e6</v>
@@ -58512,13 +58509,13 @@
         <v>4435</v>
       </c>
       <c r="D497" s="4" t="s">
-        <v>421</v>
+        <v>420</v>
       </c>
       <c r="E497" s="4" t="s">
+        <v>424</v>
+      </c>
+      <c r="F497" s="4" t="s">
         <v>425</v>
-      </c>
-      <c r="F497" s="4" t="s">
-        <v>426</v>
       </c>
       <c r="G497" s="4" t="s">
         <v>96</v>
@@ -58530,7 +58527,7 @@
         <v>2025</v>
       </c>
       <c r="J497" s="4" t="s">
-        <v>427</v>
+        <v>426</v>
       </c>
       <c r="K497" s="3">
         <v>9.445692e6</v>
@@ -58625,13 +58622,13 @@
         <v>4435</v>
       </c>
       <c r="D498" s="4" t="s">
-        <v>421</v>
+        <v>420</v>
       </c>
       <c r="E498" s="4" t="s">
+        <v>424</v>
+      </c>
+      <c r="F498" s="4" t="s">
         <v>425</v>
-      </c>
-      <c r="F498" s="4" t="s">
-        <v>426</v>
       </c>
       <c r="G498" s="4" t="s">
         <v>96</v>
@@ -58643,7 +58640,7 @@
         <v>2025</v>
       </c>
       <c r="J498" s="4" t="s">
-        <v>427</v>
+        <v>426</v>
       </c>
       <c r="K498" s="3">
         <v>9.445692e6</v>
@@ -58695,10 +58692,10 @@
         <v>0</v>
       </c>
       <c r="AB498" s="4" t="s">
-        <v>428</v>
+        <v>427</v>
       </c>
       <c r="AC498" s="4" t="s">
-        <v>401</v>
+        <v>400</v>
       </c>
       <c r="AD498" s="3">
         <v>1</v>
@@ -58742,13 +58739,13 @@
         <v>4435</v>
       </c>
       <c r="D499" s="4" t="s">
-        <v>421</v>
+        <v>420</v>
       </c>
       <c r="E499" s="4" t="s">
+        <v>424</v>
+      </c>
+      <c r="F499" s="4" t="s">
         <v>425</v>
-      </c>
-      <c r="F499" s="4" t="s">
-        <v>426</v>
       </c>
       <c r="G499" s="4" t="s">
         <v>96</v>
@@ -58760,7 +58757,7 @@
         <v>2025</v>
       </c>
       <c r="J499" s="4" t="s">
-        <v>427</v>
+        <v>426</v>
       </c>
       <c r="K499" s="3">
         <v>9.445692e6</v>
@@ -58812,10 +58809,10 @@
         <v>0</v>
       </c>
       <c r="AB499" s="4" t="s">
-        <v>428</v>
+        <v>427</v>
       </c>
       <c r="AC499" s="4" t="s">
-        <v>401</v>
+        <v>400</v>
       </c>
       <c r="AD499" s="3">
         <v>2</v>
@@ -58859,13 +58856,13 @@
         <v>4435</v>
       </c>
       <c r="D500" s="4" t="s">
-        <v>421</v>
+        <v>420</v>
       </c>
       <c r="E500" s="4" t="s">
+        <v>428</v>
+      </c>
+      <c r="F500" s="4" t="s">
         <v>429</v>
-      </c>
-      <c r="F500" s="4" t="s">
-        <v>430</v>
       </c>
       <c r="G500" s="4" t="s">
         <v>106</v>
@@ -58877,7 +58874,7 @@
         <v>2025</v>
       </c>
       <c r="J500" s="4" t="s">
-        <v>431</v>
+        <v>430</v>
       </c>
       <c r="K500" s="3">
         <v>9.433849e6</v>
@@ -58974,13 +58971,13 @@
         <v>4435</v>
       </c>
       <c r="D501" s="4" t="s">
-        <v>421</v>
+        <v>420</v>
       </c>
       <c r="E501" s="4" t="s">
+        <v>428</v>
+      </c>
+      <c r="F501" s="4" t="s">
         <v>429</v>
-      </c>
-      <c r="F501" s="4" t="s">
-        <v>430</v>
       </c>
       <c r="G501" s="4" t="s">
         <v>106</v>
@@ -58992,7 +58989,7 @@
         <v>2025</v>
       </c>
       <c r="J501" s="4" t="s">
-        <v>431</v>
+        <v>430</v>
       </c>
       <c r="K501" s="3">
         <v>9.433849e6</v>
@@ -59089,13 +59086,13 @@
         <v>4435</v>
       </c>
       <c r="D502" s="4" t="s">
-        <v>421</v>
+        <v>420</v>
       </c>
       <c r="E502" s="4" t="s">
+        <v>428</v>
+      </c>
+      <c r="F502" s="4" t="s">
         <v>429</v>
-      </c>
-      <c r="F502" s="4" t="s">
-        <v>430</v>
       </c>
       <c r="G502" s="4" t="s">
         <v>106</v>
@@ -59107,7 +59104,7 @@
         <v>2025</v>
       </c>
       <c r="J502" s="4" t="s">
-        <v>431</v>
+        <v>430</v>
       </c>
       <c r="K502" s="3">
         <v>9.433849e6</v>
@@ -59204,13 +59201,13 @@
         <v>4435</v>
       </c>
       <c r="D503" s="4" t="s">
-        <v>421</v>
+        <v>420</v>
       </c>
       <c r="E503" s="4" t="s">
+        <v>428</v>
+      </c>
+      <c r="F503" s="4" t="s">
         <v>429</v>
-      </c>
-      <c r="F503" s="4" t="s">
-        <v>430</v>
       </c>
       <c r="G503" s="4" t="s">
         <v>106</v>
@@ -59222,7 +59219,7 @@
         <v>2025</v>
       </c>
       <c r="J503" s="4" t="s">
-        <v>431</v>
+        <v>430</v>
       </c>
       <c r="K503" s="3">
         <v>9.433849e6</v>
@@ -59319,13 +59316,13 @@
         <v>4435</v>
       </c>
       <c r="D504" s="4" t="s">
-        <v>421</v>
+        <v>420</v>
       </c>
       <c r="E504" s="4" t="s">
+        <v>428</v>
+      </c>
+      <c r="F504" s="4" t="s">
         <v>429</v>
-      </c>
-      <c r="F504" s="4" t="s">
-        <v>430</v>
       </c>
       <c r="G504" s="4" t="s">
         <v>106</v>
@@ -59337,7 +59334,7 @@
         <v>2025</v>
       </c>
       <c r="J504" s="4" t="s">
-        <v>431</v>
+        <v>430</v>
       </c>
       <c r="K504" s="3">
         <v>9.433849e6</v>
@@ -59391,7 +59388,7 @@
         <v>0</v>
       </c>
       <c r="AB504" s="4" t="s">
-        <v>432</v>
+        <v>431</v>
       </c>
       <c r="AC504" s="4" t="s">
         <v>153</v>
@@ -59438,13 +59435,13 @@
         <v>4435</v>
       </c>
       <c r="D505" s="4" t="s">
-        <v>421</v>
+        <v>420</v>
       </c>
       <c r="E505" s="4" t="s">
+        <v>428</v>
+      </c>
+      <c r="F505" s="4" t="s">
         <v>429</v>
-      </c>
-      <c r="F505" s="4" t="s">
-        <v>430</v>
       </c>
       <c r="G505" s="4" t="s">
         <v>106</v>
@@ -59456,7 +59453,7 @@
         <v>2025</v>
       </c>
       <c r="J505" s="4" t="s">
-        <v>431</v>
+        <v>430</v>
       </c>
       <c r="K505" s="3">
         <v>9.433849e6</v>
@@ -59510,7 +59507,7 @@
         <v>0</v>
       </c>
       <c r="AB505" s="4" t="s">
-        <v>432</v>
+        <v>431</v>
       </c>
       <c r="AC505" s="4" t="s">
         <v>153</v>
@@ -59557,13 +59554,13 @@
         <v>4435</v>
       </c>
       <c r="D506" s="4" t="s">
-        <v>421</v>
+        <v>420</v>
       </c>
       <c r="E506" s="4" t="s">
+        <v>428</v>
+      </c>
+      <c r="F506" s="4" t="s">
         <v>429</v>
-      </c>
-      <c r="F506" s="4" t="s">
-        <v>430</v>
       </c>
       <c r="G506" s="4" t="s">
         <v>106</v>
@@ -59575,7 +59572,7 @@
         <v>2025</v>
       </c>
       <c r="J506" s="4" t="s">
-        <v>431</v>
+        <v>430</v>
       </c>
       <c r="K506" s="3">
         <v>9.433849e6</v>
@@ -59629,7 +59626,7 @@
         <v>0</v>
       </c>
       <c r="AB506" s="4" t="s">
-        <v>432</v>
+        <v>431</v>
       </c>
       <c r="AC506" s="4" t="s">
         <v>153</v>
@@ -59676,13 +59673,13 @@
         <v>4435</v>
       </c>
       <c r="D507" s="4" t="s">
-        <v>421</v>
+        <v>420</v>
       </c>
       <c r="E507" s="4" t="s">
+        <v>428</v>
+      </c>
+      <c r="F507" s="4" t="s">
         <v>429</v>
-      </c>
-      <c r="F507" s="4" t="s">
-        <v>430</v>
       </c>
       <c r="G507" s="4" t="s">
         <v>106</v>
@@ -59694,7 +59691,7 @@
         <v>2025</v>
       </c>
       <c r="J507" s="4" t="s">
-        <v>431</v>
+        <v>430</v>
       </c>
       <c r="K507" s="3">
         <v>9.433849e6</v>
@@ -59748,7 +59745,7 @@
         <v>0</v>
       </c>
       <c r="AB507" s="4" t="s">
-        <v>432</v>
+        <v>431</v>
       </c>
       <c r="AC507" s="4" t="s">
         <v>153</v>
@@ -59795,16 +59792,16 @@
         <v>4435</v>
       </c>
       <c r="D508" s="4" t="s">
-        <v>421</v>
+        <v>420</v>
       </c>
       <c r="E508" s="4" t="s">
+        <v>200</v>
+      </c>
+      <c r="F508" s="4" t="s">
         <v>201</v>
       </c>
-      <c r="F508" s="4" t="s">
+      <c r="G508" s="4" t="s">
         <v>202</v>
-      </c>
-      <c r="G508" s="4" t="s">
-        <v>203</v>
       </c>
       <c r="H508" s="3">
         <v>19</v>
@@ -59813,7 +59810,7 @@
         <v>2025</v>
       </c>
       <c r="J508" s="4" t="s">
-        <v>204</v>
+        <v>203</v>
       </c>
       <c r="K508" s="3">
         <v>9.396057e6</v>
@@ -59908,16 +59905,16 @@
         <v>4435</v>
       </c>
       <c r="D509" s="4" t="s">
-        <v>421</v>
+        <v>420</v>
       </c>
       <c r="E509" s="4" t="s">
+        <v>200</v>
+      </c>
+      <c r="F509" s="4" t="s">
         <v>201</v>
       </c>
-      <c r="F509" s="4" t="s">
+      <c r="G509" s="4" t="s">
         <v>202</v>
-      </c>
-      <c r="G509" s="4" t="s">
-        <v>203</v>
       </c>
       <c r="H509" s="3">
         <v>19</v>
@@ -59926,7 +59923,7 @@
         <v>2025</v>
       </c>
       <c r="J509" s="4" t="s">
-        <v>204</v>
+        <v>203</v>
       </c>
       <c r="K509" s="3">
         <v>9.396057e6</v>
@@ -60021,16 +60018,16 @@
         <v>4435</v>
       </c>
       <c r="D510" s="4" t="s">
-        <v>421</v>
+        <v>420</v>
       </c>
       <c r="E510" s="4" t="s">
+        <v>200</v>
+      </c>
+      <c r="F510" s="4" t="s">
         <v>201</v>
       </c>
-      <c r="F510" s="4" t="s">
+      <c r="G510" s="4" t="s">
         <v>202</v>
-      </c>
-      <c r="G510" s="4" t="s">
-        <v>203</v>
       </c>
       <c r="H510" s="3">
         <v>19</v>
@@ -60039,7 +60036,7 @@
         <v>2025</v>
       </c>
       <c r="J510" s="4" t="s">
-        <v>204</v>
+        <v>203</v>
       </c>
       <c r="K510" s="3">
         <v>9.396057e6</v>
@@ -60134,16 +60131,16 @@
         <v>4435</v>
       </c>
       <c r="D511" s="4" t="s">
-        <v>421</v>
+        <v>420</v>
       </c>
       <c r="E511" s="4" t="s">
+        <v>200</v>
+      </c>
+      <c r="F511" s="4" t="s">
         <v>201</v>
       </c>
-      <c r="F511" s="4" t="s">
+      <c r="G511" s="4" t="s">
         <v>202</v>
-      </c>
-      <c r="G511" s="4" t="s">
-        <v>203</v>
       </c>
       <c r="H511" s="3">
         <v>19</v>
@@ -60152,7 +60149,7 @@
         <v>2025</v>
       </c>
       <c r="J511" s="4" t="s">
-        <v>204</v>
+        <v>203</v>
       </c>
       <c r="K511" s="3">
         <v>9.396057e6</v>
@@ -60204,10 +60201,10 @@
         <v>0</v>
       </c>
       <c r="AB511" s="4" t="s">
-        <v>205</v>
+        <v>204</v>
       </c>
       <c r="AC511" s="4" t="s">
-        <v>401</v>
+        <v>400</v>
       </c>
       <c r="AD511" s="3">
         <v>2</v>
@@ -60251,16 +60248,16 @@
         <v>4435</v>
       </c>
       <c r="D512" s="4" t="s">
-        <v>421</v>
+        <v>420</v>
       </c>
       <c r="E512" s="4" t="s">
+        <v>200</v>
+      </c>
+      <c r="F512" s="4" t="s">
         <v>201</v>
       </c>
-      <c r="F512" s="4" t="s">
+      <c r="G512" s="4" t="s">
         <v>202</v>
-      </c>
-      <c r="G512" s="4" t="s">
-        <v>203</v>
       </c>
       <c r="H512" s="3">
         <v>98</v>
@@ -60269,7 +60266,7 @@
         <v>2025</v>
       </c>
       <c r="J512" s="4" t="s">
-        <v>204</v>
+        <v>203</v>
       </c>
       <c r="K512" s="3">
         <v>9.396057e6</v>
@@ -60364,16 +60361,16 @@
         <v>4435</v>
       </c>
       <c r="D513" s="4" t="s">
-        <v>421</v>
+        <v>420</v>
       </c>
       <c r="E513" s="4" t="s">
+        <v>200</v>
+      </c>
+      <c r="F513" s="4" t="s">
         <v>201</v>
       </c>
-      <c r="F513" s="4" t="s">
+      <c r="G513" s="4" t="s">
         <v>202</v>
-      </c>
-      <c r="G513" s="4" t="s">
-        <v>203</v>
       </c>
       <c r="H513" s="3">
         <v>98</v>
@@ -60382,7 +60379,7 @@
         <v>2025</v>
       </c>
       <c r="J513" s="4" t="s">
-        <v>204</v>
+        <v>203</v>
       </c>
       <c r="K513" s="3">
         <v>9.396057e6</v>
@@ -60477,16 +60474,16 @@
         <v>4435</v>
       </c>
       <c r="D514" s="4" t="s">
-        <v>421</v>
+        <v>420</v>
       </c>
       <c r="E514" s="4" t="s">
+        <v>200</v>
+      </c>
+      <c r="F514" s="4" t="s">
         <v>201</v>
       </c>
-      <c r="F514" s="4" t="s">
+      <c r="G514" s="4" t="s">
         <v>202</v>
-      </c>
-      <c r="G514" s="4" t="s">
-        <v>203</v>
       </c>
       <c r="H514" s="3">
         <v>1004</v>
@@ -60495,7 +60492,7 @@
         <v>2025</v>
       </c>
       <c r="J514" s="4" t="s">
-        <v>204</v>
+        <v>203</v>
       </c>
       <c r="K514" s="3">
         <v>9.396057e6</v>
@@ -60590,16 +60587,16 @@
         <v>4435</v>
       </c>
       <c r="D515" s="4" t="s">
-        <v>421</v>
+        <v>420</v>
       </c>
       <c r="E515" s="4" t="s">
+        <v>200</v>
+      </c>
+      <c r="F515" s="4" t="s">
         <v>201</v>
       </c>
-      <c r="F515" s="4" t="s">
+      <c r="G515" s="4" t="s">
         <v>202</v>
-      </c>
-      <c r="G515" s="4" t="s">
-        <v>203</v>
       </c>
       <c r="H515" s="3">
         <v>1004</v>
@@ -60608,7 +60605,7 @@
         <v>2025</v>
       </c>
       <c r="J515" s="4" t="s">
-        <v>204</v>
+        <v>203</v>
       </c>
       <c r="K515" s="3">
         <v>9.396057e6</v>
@@ -60703,16 +60700,16 @@
         <v>4435</v>
       </c>
       <c r="D516" s="4" t="s">
-        <v>421</v>
+        <v>420</v>
       </c>
       <c r="E516" s="4" t="s">
+        <v>200</v>
+      </c>
+      <c r="F516" s="4" t="s">
         <v>201</v>
       </c>
-      <c r="F516" s="4" t="s">
+      <c r="G516" s="4" t="s">
         <v>202</v>
-      </c>
-      <c r="G516" s="4" t="s">
-        <v>203</v>
       </c>
       <c r="H516" s="3">
         <v>1127</v>
@@ -60721,7 +60718,7 @@
         <v>2025</v>
       </c>
       <c r="J516" s="4" t="s">
-        <v>204</v>
+        <v>203</v>
       </c>
       <c r="K516" s="3">
         <v>9.396057e6</v>
@@ -60818,16 +60815,16 @@
         <v>4435</v>
       </c>
       <c r="D517" s="4" t="s">
-        <v>421</v>
+        <v>420</v>
       </c>
       <c r="E517" s="4" t="s">
+        <v>200</v>
+      </c>
+      <c r="F517" s="4" t="s">
         <v>201</v>
       </c>
-      <c r="F517" s="4" t="s">
+      <c r="G517" s="4" t="s">
         <v>202</v>
-      </c>
-      <c r="G517" s="4" t="s">
-        <v>203</v>
       </c>
       <c r="H517" s="3">
         <v>1127</v>
@@ -60836,7 +60833,7 @@
         <v>2025</v>
       </c>
       <c r="J517" s="4" t="s">
-        <v>204</v>
+        <v>203</v>
       </c>
       <c r="K517" s="3">
         <v>9.396057e6</v>
@@ -60933,7 +60930,7 @@
         <v>4447</v>
       </c>
       <c r="D518" s="4" t="s">
-        <v>433</v>
+        <v>432</v>
       </c>
       <c r="E518" s="4" t="s">
         <v>100</v>
@@ -61048,7 +61045,7 @@
         <v>4447</v>
       </c>
       <c r="D519" s="4" t="s">
-        <v>433</v>
+        <v>432</v>
       </c>
       <c r="E519" s="4" t="s">
         <v>100</v>
@@ -61163,7 +61160,7 @@
         <v>4447</v>
       </c>
       <c r="D520" s="4" t="s">
-        <v>433</v>
+        <v>432</v>
       </c>
       <c r="E520" s="4" t="s">
         <v>100</v>
@@ -61181,7 +61178,7 @@
         <v>2017</v>
       </c>
       <c r="J520" s="4" t="s">
-        <v>434</v>
+        <v>433</v>
       </c>
       <c r="K520" s="3">
         <v>9.043778e6</v>
@@ -61278,7 +61275,7 @@
         <v>4447</v>
       </c>
       <c r="D521" s="4" t="s">
-        <v>433</v>
+        <v>432</v>
       </c>
       <c r="E521" s="4" t="s">
         <v>100</v>
@@ -61393,7 +61390,7 @@
         <v>4447</v>
       </c>
       <c r="D522" s="4" t="s">
-        <v>433</v>
+        <v>432</v>
       </c>
       <c r="E522" s="4" t="s">
         <v>100</v>
@@ -61411,7 +61408,7 @@
         <v>2017</v>
       </c>
       <c r="J522" s="4" t="s">
-        <v>434</v>
+        <v>433</v>
       </c>
       <c r="K522" s="3">
         <v>9.043778e6</v>
@@ -61508,13 +61505,13 @@
         <v>4447</v>
       </c>
       <c r="D523" s="4" t="s">
-        <v>433</v>
+        <v>432</v>
       </c>
       <c r="E523" s="4" t="s">
+        <v>434</v>
+      </c>
+      <c r="F523" s="4" t="s">
         <v>435</v>
-      </c>
-      <c r="F523" s="4" t="s">
-        <v>436</v>
       </c>
       <c r="G523" s="4" t="s">
         <v>96</v>
@@ -61623,13 +61620,13 @@
         <v>4447</v>
       </c>
       <c r="D524" s="4" t="s">
-        <v>433</v>
+        <v>432</v>
       </c>
       <c r="E524" s="4" t="s">
+        <v>434</v>
+      </c>
+      <c r="F524" s="4" t="s">
         <v>435</v>
-      </c>
-      <c r="F524" s="4" t="s">
-        <v>436</v>
       </c>
       <c r="G524" s="4" t="s">
         <v>96</v>
@@ -61738,7 +61735,7 @@
         <v>4447</v>
       </c>
       <c r="D525" s="4" t="s">
-        <v>433</v>
+        <v>432</v>
       </c>
       <c r="E525" s="4" t="s">
         <v>173</v>
@@ -61756,7 +61753,7 @@
         <v>2016</v>
       </c>
       <c r="J525" s="4" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="K525" s="3">
         <v>9.074722e6</v>
@@ -61853,13 +61850,13 @@
         <v>4447</v>
       </c>
       <c r="D526" s="4" t="s">
-        <v>433</v>
+        <v>432</v>
       </c>
       <c r="E526" s="4" t="s">
+        <v>436</v>
+      </c>
+      <c r="F526" s="4" t="s">
         <v>437</v>
-      </c>
-      <c r="F526" s="4" t="s">
-        <v>438</v>
       </c>
       <c r="G526" s="4" t="s">
         <v>115</v>
@@ -61968,13 +61965,13 @@
         <v>4447</v>
       </c>
       <c r="D527" s="4" t="s">
-        <v>433</v>
+        <v>432</v>
       </c>
       <c r="E527" s="4" t="s">
+        <v>436</v>
+      </c>
+      <c r="F527" s="4" t="s">
         <v>437</v>
-      </c>
-      <c r="F527" s="4" t="s">
-        <v>438</v>
       </c>
       <c r="G527" s="4" t="s">
         <v>115</v>
@@ -62083,16 +62080,16 @@
         <v>4592</v>
       </c>
       <c r="D528" s="4" t="s">
+        <v>438</v>
+      </c>
+      <c r="E528" s="4" t="s">
         <v>439</v>
       </c>
-      <c r="E528" s="4" t="s">
+      <c r="F528" s="4" t="s">
         <v>440</v>
       </c>
-      <c r="F528" s="4" t="s">
-        <v>441</v>
-      </c>
       <c r="G528" s="4" t="s">
-        <v>298</v>
+        <v>297</v>
       </c>
       <c r="H528" s="3">
         <v>2496</v>
@@ -62101,7 +62098,7 @@
         <v>2012</v>
       </c>
       <c r="J528" s="4" t="s">
-        <v>442</v>
+        <v>441</v>
       </c>
       <c r="K528" s="3">
         <v>0</v>
@@ -62450,13 +62447,13 @@
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{B7D980F0-49E0-484D-BC39-FEED4E302613}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{0CC42C91-65DC-4F18-B675-92F96CFEAAEE}"/>
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{E5115218-B91C-40C4-ADB0-932021E03605}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{9D321869-A45F-4FF0-90FA-36603F419843}"/>
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{B4D43860-CBC4-42A4-9D22-EF79DAB11C93}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{0C364101-D2A2-49F7-A1B0-5C3E166CC5C2}"/>
 </file>
--- a/restos.xlsx
+++ b/restos.xlsx
@@ -63597,13 +63597,13 @@
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{4D10EEFD-7EB6-49AE-94B1-46BD17CAF209}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{46AEF257-1200-4E69-A4BE-45D862DED09C}"/>
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{673C6D4D-9773-4D86-8EE0-DD2C5B2AA078}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{0F1BEE0C-7E05-4121-BC54-AE9434A31050}"/>
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{35B5FFFB-200D-4769-8B38-5089D25A5BCC}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{2812DC98-4AD1-47E7-AF7A-AEA289269F81}"/>
 </file>
--- a/restos.xlsx
+++ b/restos.xlsx
@@ -16468,7 +16468,7 @@
         <v>0</v>
       </c>
       <c r="T134" s="5">
-        <v>-8261.32</v>
+        <v>-9124.46</v>
       </c>
       <c r="U134" s="3">
         <v>0</v>
@@ -16503,7 +16503,7 @@
         <v>1.480004e6</v>
       </c>
       <c r="AG134" s="5">
-        <v>8261.32</v>
+        <v>9124.46</v>
       </c>
       <c r="AH134" s="5">
         <v>0</v>
@@ -63597,13 +63597,13 @@
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{46AEF257-1200-4E69-A4BE-45D862DED09C}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{EC1955F1-D6FC-4442-B486-685DB3B5EEA0}"/>
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{0F1BEE0C-7E05-4121-BC54-AE9434A31050}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{21B73D30-43A5-4BFC-9147-90E10DCE6DC4}"/>
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{2812DC98-4AD1-47E7-AF7A-AEA289269F81}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{023155DB-4AD2-45AD-AF9D-067C3AC53BB2}"/>
 </file>
--- a/restos.xlsx
+++ b/restos.xlsx
@@ -63597,13 +63597,13 @@
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{EC1955F1-D6FC-4442-B486-685DB3B5EEA0}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{9E88B6E4-3DF9-4341-81D8-6CDBC66845C3}"/>
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{21B73D30-43A5-4BFC-9147-90E10DCE6DC4}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{C5E1B3DB-3BBC-4408-9A11-8FD8F5DBD629}"/>
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{023155DB-4AD2-45AD-AF9D-067C3AC53BB2}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{7C432ADD-149A-4D87-A8D1-DF556654FDEE}"/>
 </file>